--- a/DataAnalysis/LC/0.05/Results.xlsx
+++ b/DataAnalysis/LC/0.05/Results.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Utente\Desktop\CultureAwarenessTest\DataAnalysis\LC\0.05\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59251DE4-D436-4DCB-AC9D-CFA7E6FAFB49}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Foglio1" sheetId="1" r:id="rId1"/>
@@ -18,8 +24,88 @@
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="25">
+  <si>
+    <t>ERR_0</t>
+  </si>
+  <si>
+    <t>ERR0_STD</t>
+  </si>
+  <si>
+    <t>ERR_1</t>
+  </si>
+  <si>
+    <t>ERR1_STD</t>
+  </si>
+  <si>
+    <t>ERR_2</t>
+  </si>
+  <si>
+    <t>ERR2_STD</t>
+  </si>
+  <si>
+    <t>ERR</t>
+  </si>
+  <si>
+    <t>ERR_STD</t>
+  </si>
+  <si>
+    <t>CIC</t>
+  </si>
+  <si>
+    <t>CIC_STD</t>
+  </si>
+  <si>
+    <t>STD</t>
+  </si>
+  <si>
+    <t>BAL</t>
+  </si>
+  <si>
+    <t>NOAUG</t>
+  </si>
+  <si>
+    <t>g=0.0001</t>
+  </si>
+  <si>
+    <t>tau=10%</t>
+  </si>
+  <si>
+    <t>tau=20%</t>
+  </si>
+  <si>
+    <t>ADV</t>
+  </si>
+  <si>
+    <t>CLSDIV</t>
+  </si>
+  <si>
+    <t>NOCLSDIV</t>
+  </si>
+  <si>
+    <t>DIFF</t>
+  </si>
+  <si>
+    <t>IMB</t>
+  </si>
+  <si>
+    <t>MIT</t>
+  </si>
+  <si>
+    <t>STDAUG</t>
+  </si>
+  <si>
+    <t>ONLYMIN</t>
+  </si>
+  <si>
+    <t>PARBS</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -53,7 +139,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normale" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -330,10 +416,216 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:P38"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="G1" t="s">
+        <v>0</v>
+      </c>
+      <c r="H1" t="s">
+        <v>1</v>
+      </c>
+      <c r="I1" t="s">
+        <v>2</v>
+      </c>
+      <c r="J1" t="s">
+        <v>3</v>
+      </c>
+      <c r="K1" t="s">
+        <v>4</v>
+      </c>
+      <c r="L1" t="s">
+        <v>5</v>
+      </c>
+      <c r="M1" t="s">
+        <v>6</v>
+      </c>
+      <c r="N1" t="s">
+        <v>7</v>
+      </c>
+      <c r="O1" t="s">
+        <v>8</v>
+      </c>
+      <c r="P1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="B3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="C4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="C5" t="s">
+        <v>10</v>
+      </c>
+      <c r="E5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="E6" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="E7" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="C8" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="D9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="E10" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="E11" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="D12" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="E13" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="E14" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="C15" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B17" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="C18" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="C20" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="E21" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="E22" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="E23" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B25" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="C26" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="C27" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="C28" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="D29" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="D30" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="E31" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="33" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B33" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="34" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="C34" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="35" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="C35" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="36" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="C36" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="37" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="D37" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="38" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="E38" t="s">
+        <v>22</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/DataAnalysis/LC/0.05/Results.xlsx
+++ b/DataAnalysis/LC/0.05/Results.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29530"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Utente\Desktop\CultureAwarenessTest\DataAnalysis\LC\0.05\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5FA7BCAD-FF01-4D81-B655-5C5E8B1D2286}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1A18028-EF88-453F-86F8-89609E80CD7F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -52,7 +52,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="484" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="486" uniqueCount="76">
   <si>
     <t>Dati originali</t>
   </si>
@@ -277,6 +277,9 @@
   </si>
   <si>
     <t>ep=0.1</t>
+  </si>
+  <si>
+    <t>try3</t>
   </si>
 </sst>
 </file>
@@ -594,7 +597,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:P28"/>
+  <dimension ref="A1:P29"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9.88671875" customWidth="1"/>
@@ -840,366 +843,401 @@
       </c>
     </row>
     <row r="11" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="B11" t="s">
+      <c r="C11" t="s">
+        <v>75</v>
+      </c>
+      <c r="G11">
+        <v>12.3</v>
+      </c>
+      <c r="H11">
+        <v>2.7294688127912341</v>
+      </c>
+      <c r="I11">
+        <v>17.8</v>
+      </c>
+      <c r="J11">
+        <v>3.3652637340927662</v>
+      </c>
+      <c r="K11">
+        <v>34.6</v>
+      </c>
+      <c r="L11">
+        <v>3.5951356024495098</v>
+      </c>
+      <c r="M11">
+        <v>21.56666666666667</v>
+      </c>
+      <c r="N11">
+        <v>1.8050854088749744</v>
+      </c>
+      <c r="O11">
+        <v>9.4666666666666668</v>
+      </c>
+      <c r="P11">
+        <v>2.5149552679918559</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="B12" t="s">
         <v>60</v>
-      </c>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="C12" t="s">
-        <v>4</v>
-      </c>
-      <c r="G12">
-        <v>14.45</v>
-      </c>
-      <c r="H12">
-        <v>2.4318488622628007</v>
-      </c>
-      <c r="I12">
-        <v>17.850000000000001</v>
-      </c>
-      <c r="J12">
-        <v>2.333928495524709</v>
-      </c>
-      <c r="K12">
-        <v>31.6</v>
-      </c>
-      <c r="L12">
-        <v>3.7475918193480466</v>
-      </c>
-      <c r="M12">
-        <v>21.3</v>
-      </c>
-      <c r="N12">
-        <v>1.4072124621322282</v>
-      </c>
-      <c r="O12">
-        <v>6.95</v>
-      </c>
-      <c r="P12">
-        <v>1.8840624612853705</v>
       </c>
     </row>
     <row r="13" spans="1:16" x14ac:dyDescent="0.3">
       <c r="C13" t="s">
+        <v>4</v>
+      </c>
+      <c r="G13">
+        <v>14.45</v>
+      </c>
+      <c r="H13">
+        <v>2.4318488622628007</v>
+      </c>
+      <c r="I13">
+        <v>17.850000000000001</v>
+      </c>
+      <c r="J13">
+        <v>2.333928495524709</v>
+      </c>
+      <c r="K13">
+        <v>31.6</v>
+      </c>
+      <c r="L13">
+        <v>3.7475918193480466</v>
+      </c>
+      <c r="M13">
+        <v>21.3</v>
+      </c>
+      <c r="N13">
+        <v>1.4072124621322282</v>
+      </c>
+      <c r="O13">
+        <v>6.95</v>
+      </c>
+      <c r="P13">
+        <v>1.8840624612853705</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="C14" t="s">
         <v>2</v>
       </c>
-      <c r="F13" t="s">
+      <c r="F14" t="s">
         <v>22</v>
       </c>
-      <c r="G13">
+      <c r="G14">
         <v>11.5</v>
       </c>
-      <c r="H13">
+      <c r="H14">
         <v>2</v>
       </c>
-      <c r="I13">
+      <c r="I14">
         <v>16.375</v>
       </c>
-      <c r="J13">
+      <c r="J14">
         <v>1.685018016012207</v>
       </c>
-      <c r="K13">
+      <c r="K14">
         <v>29.0625</v>
       </c>
-      <c r="L13">
+      <c r="L14">
         <v>2.2903134532822609</v>
       </c>
-      <c r="M13">
+      <c r="M14">
         <v>18.979166666666668</v>
       </c>
-      <c r="N13">
+      <c r="N14">
         <v>0.56650908172997527</v>
       </c>
-      <c r="O13">
+      <c r="O14">
         <v>7.5416666666666661</v>
       </c>
-      <c r="P13">
+      <c r="P14">
         <v>1.8317092373405619</v>
       </c>
     </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A14" t="s">
+    <row r="15" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="B15" t="s">
+    <row r="16" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="B16" t="s">
         <v>3</v>
-      </c>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="C16" t="s">
-        <v>4</v>
-      </c>
-      <c r="G16">
-        <v>12.357142857142858</v>
-      </c>
-      <c r="H16">
-        <v>1.5197117521174255</v>
-      </c>
-      <c r="I16">
-        <v>16.428571428571427</v>
-      </c>
-      <c r="J16">
-        <v>1.3363062095621221</v>
-      </c>
-      <c r="K16">
-        <v>32.785714285714285</v>
-      </c>
-      <c r="L16">
-        <v>2.4976179127511156</v>
-      </c>
-      <c r="M16">
-        <v>20.523809523809526</v>
-      </c>
-      <c r="N16">
-        <v>1.5348681069786112</v>
-      </c>
-      <c r="O16">
-        <v>8.1666666666666679</v>
-      </c>
-      <c r="P16">
-        <v>0.98130676292531094</v>
       </c>
     </row>
     <row r="17" spans="2:16" x14ac:dyDescent="0.3">
       <c r="C17" t="s">
-        <v>69</v>
-      </c>
-      <c r="F17" t="s">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="G17">
-        <v>9.9166666666666661</v>
+        <v>12.357142857142858</v>
       </c>
       <c r="H17">
-        <v>2.3540744819709238</v>
+        <v>1.5197117521174255</v>
       </c>
       <c r="I17">
-        <v>14.083333333333334</v>
+        <v>16.428571428571427</v>
       </c>
       <c r="J17">
-        <v>2.1075261959621407</v>
+        <v>1.3363062095621221</v>
       </c>
       <c r="K17">
-        <v>25.75</v>
+        <v>32.785714285714285</v>
       </c>
       <c r="L17">
-        <v>4.5798471590217948</v>
+        <v>2.4976179127511156</v>
       </c>
       <c r="M17">
-        <v>16.583333333333332</v>
+        <v>20.523809523809526</v>
       </c>
       <c r="N17">
-        <v>1.4013882006385272</v>
+        <v>1.5348681069786112</v>
       </c>
       <c r="O17">
-        <v>6.75</v>
+        <v>8.1666666666666679</v>
       </c>
       <c r="P17">
-        <v>2.7381055900425419</v>
+        <v>0.98130676292531094</v>
       </c>
     </row>
     <row r="18" spans="2:16" x14ac:dyDescent="0.3">
       <c r="C18" t="s">
+        <v>69</v>
+      </c>
+      <c r="F18" t="s">
+        <v>22</v>
+      </c>
+      <c r="G18">
+        <v>9.9166666666666661</v>
+      </c>
+      <c r="H18">
+        <v>2.3540744819709238</v>
+      </c>
+      <c r="I18">
+        <v>14.083333333333334</v>
+      </c>
+      <c r="J18">
+        <v>2.1075261959621407</v>
+      </c>
+      <c r="K18">
+        <v>25.75</v>
+      </c>
+      <c r="L18">
+        <v>4.5798471590217948</v>
+      </c>
+      <c r="M18">
+        <v>16.583333333333332</v>
+      </c>
+      <c r="N18">
+        <v>1.4013882006385272</v>
+      </c>
+      <c r="O18">
+        <v>6.75</v>
+      </c>
+      <c r="P18">
+        <v>2.7381055900425419</v>
+      </c>
+    </row>
+    <row r="19" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="C19" t="s">
         <v>53</v>
-      </c>
-    </row>
-    <row r="19" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="D19" t="s">
-        <v>69</v>
-      </c>
-      <c r="G19">
-        <v>10.45</v>
-      </c>
-      <c r="H19">
-        <v>2.4432446550528732</v>
-      </c>
-      <c r="I19">
-        <v>16.05</v>
-      </c>
-      <c r="J19">
-        <v>2.4088955514462986</v>
-      </c>
-      <c r="K19">
-        <v>27.05</v>
-      </c>
-      <c r="L19">
-        <v>4.0514057916837869</v>
-      </c>
-      <c r="M19">
-        <v>17.850000000000001</v>
-      </c>
-      <c r="N19">
-        <v>1.8214259777966804</v>
-      </c>
-      <c r="O19">
-        <v>7.4</v>
-      </c>
-      <c r="P19">
-        <v>2.4434341346495017</v>
       </c>
     </row>
     <row r="20" spans="2:16" x14ac:dyDescent="0.3">
       <c r="D20" t="s">
+        <v>69</v>
+      </c>
+      <c r="G20">
+        <v>10.45</v>
+      </c>
+      <c r="H20">
+        <v>2.4432446550528732</v>
+      </c>
+      <c r="I20">
+        <v>16.05</v>
+      </c>
+      <c r="J20">
+        <v>2.4088955514462986</v>
+      </c>
+      <c r="K20">
+        <v>27.05</v>
+      </c>
+      <c r="L20">
+        <v>4.0514057916837869</v>
+      </c>
+      <c r="M20">
+        <v>17.850000000000001</v>
+      </c>
+      <c r="N20">
+        <v>1.8214259777966804</v>
+      </c>
+      <c r="O20">
+        <v>7.4</v>
+      </c>
+      <c r="P20">
+        <v>2.4434341346495017</v>
+      </c>
+    </row>
+    <row r="21" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="D21" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="21" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="E21" t="s">
+    <row r="22" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="E22" t="s">
         <v>69</v>
       </c>
-      <c r="G21">
+      <c r="G22">
         <v>8.625</v>
       </c>
-      <c r="H21">
+      <c r="H22">
         <v>1.7017148213885114</v>
       </c>
-      <c r="I21">
+      <c r="I22">
         <v>15.875</v>
       </c>
-      <c r="J21">
+      <c r="J22">
         <v>4.5711960506341587</v>
       </c>
-      <c r="K21">
+      <c r="K22">
         <v>26.75</v>
       </c>
-      <c r="L21">
+      <c r="L22">
         <v>1.5545631755148024</v>
       </c>
-      <c r="M21">
+      <c r="M22">
         <v>17.083333333333332</v>
       </c>
-      <c r="N21">
+      <c r="N22">
         <v>2.0389721448336333</v>
       </c>
-      <c r="O21">
+      <c r="O22">
         <v>8.4583333333333321</v>
       </c>
-      <c r="P21">
+      <c r="P22">
         <v>2.3028766229958482</v>
       </c>
     </row>
-    <row r="23" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B23" t="s">
+    <row r="24" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B24" t="s">
         <v>70</v>
-      </c>
-    </row>
-    <row r="24" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="C24" t="s">
-        <v>4</v>
-      </c>
-      <c r="G24">
-        <v>14.333333333333334</v>
-      </c>
-      <c r="H24">
-        <v>2.1602468994692834</v>
-      </c>
-      <c r="I24">
-        <v>16.166666666666668</v>
-      </c>
-      <c r="J24">
-        <v>2.6956755492207609</v>
-      </c>
-      <c r="K24">
-        <v>23.916666666666668</v>
-      </c>
-      <c r="L24">
-        <v>4.4879468208376423</v>
-      </c>
-      <c r="M24">
-        <v>18.138888888888889</v>
-      </c>
-      <c r="N24">
-        <v>1.8481722703094376</v>
-      </c>
-      <c r="O24">
-        <v>4.2222222222222223</v>
-      </c>
-      <c r="P24">
-        <v>1.6113026706042233</v>
       </c>
     </row>
     <row r="25" spans="2:16" x14ac:dyDescent="0.3">
       <c r="C25" t="s">
-        <v>69</v>
-      </c>
-      <c r="F25" t="s">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="G25">
-        <v>10.5</v>
+        <v>14.333333333333334</v>
       </c>
       <c r="H25">
-        <v>2.2638462845343543</v>
+        <v>2.1602468994692834</v>
       </c>
       <c r="I25">
-        <v>15.5</v>
+        <v>16.166666666666668</v>
       </c>
       <c r="J25">
-        <v>3.0207614933986431</v>
+        <v>2.6956755492207609</v>
       </c>
       <c r="K25">
-        <v>17.899999999999999</v>
+        <v>23.916666666666668</v>
       </c>
       <c r="L25">
-        <v>2.8591956910991616</v>
+        <v>4.4879468208376423</v>
       </c>
       <c r="M25">
-        <v>14.633333333333331</v>
+        <v>18.138888888888889</v>
       </c>
       <c r="N25">
-        <v>1.3091557924436987</v>
+        <v>1.8481722703094376</v>
       </c>
       <c r="O25">
-        <v>4.1333333333333329</v>
+        <v>4.2222222222222223</v>
       </c>
       <c r="P25">
-        <v>2.3816427570528349</v>
+        <v>1.6113026706042233</v>
       </c>
     </row>
     <row r="26" spans="2:16" x14ac:dyDescent="0.3">
       <c r="C26" t="s">
+        <v>69</v>
+      </c>
+      <c r="F26" t="s">
+        <v>22</v>
+      </c>
+      <c r="G26">
+        <v>10.5</v>
+      </c>
+      <c r="H26">
+        <v>2.2638462845343543</v>
+      </c>
+      <c r="I26">
+        <v>15.5</v>
+      </c>
+      <c r="J26">
+        <v>3.0207614933986431</v>
+      </c>
+      <c r="K26">
+        <v>17.899999999999999</v>
+      </c>
+      <c r="L26">
+        <v>2.8591956910991616</v>
+      </c>
+      <c r="M26">
+        <v>14.633333333333331</v>
+      </c>
+      <c r="N26">
+        <v>1.3091557924436987</v>
+      </c>
+      <c r="O26">
+        <v>4.1333333333333329</v>
+      </c>
+      <c r="P26">
+        <v>2.3816427570528349</v>
+      </c>
+    </row>
+    <row r="27" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="C27" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="27" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="D27" t="s">
+    <row r="28" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="D28" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="28" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="E28" t="s">
+    <row r="29" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="E29" t="s">
         <v>69</v>
       </c>
-      <c r="G28">
+      <c r="G29">
         <v>11.5</v>
       </c>
-      <c r="H28">
+      <c r="H29">
         <v>3.2787192621510002</v>
       </c>
-      <c r="I28">
+      <c r="I29">
         <v>13.833333333333334</v>
       </c>
-      <c r="J28">
+      <c r="J29">
         <v>1.4433756729740645</v>
       </c>
-      <c r="K28">
+      <c r="K29">
         <v>24.666666666666668</v>
       </c>
-      <c r="L28">
+      <c r="L29">
         <v>2.9297326385411577</v>
       </c>
-      <c r="M28">
+      <c r="M29">
         <v>16.666666666666668</v>
       </c>
-      <c r="N28">
+      <c r="N29">
         <v>1.5898986690282426</v>
       </c>
-      <c r="O28">
+      <c r="O29">
         <v>5.166666666666667</v>
       </c>
-      <c r="P28">
+      <c r="P29">
         <v>1.9649710204252651</v>
       </c>
     </row>
@@ -4670,23 +4708,23 @@
         <v>62</v>
       </c>
       <c r="R3">
-        <f t="shared" ref="R3:R34" si="0">AVERAGE(C3:D3)</f>
+        <f t="shared" ref="R3:R11" si="0">AVERAGE(C3:D3)</f>
         <v>11</v>
       </c>
       <c r="S3">
-        <f t="shared" ref="S3:S34" si="1">AVERAGE(H3,I3)</f>
+        <f t="shared" ref="S3:S11" si="1">AVERAGE(H3,I3)</f>
         <v>17</v>
       </c>
       <c r="T3">
-        <f t="shared" ref="T3:T34" si="2">AVERAGE(M3:N3)</f>
+        <f t="shared" ref="T3:T11" si="2">AVERAGE(M3:N3)</f>
         <v>28</v>
       </c>
       <c r="U3">
-        <f t="shared" ref="U3:U34" si="3">AVERAGE(R3:T3)</f>
+        <f t="shared" ref="U3:U11" si="3">AVERAGE(R3:T3)</f>
         <v>18.666666666666668</v>
       </c>
       <c r="AD3">
-        <f t="shared" ref="AD3:AD34" si="4">MIN(R3:T3)</f>
+        <f t="shared" ref="AD3:AD11" si="4">MIN(R3:T3)</f>
         <v>11</v>
       </c>
       <c r="AE3">
@@ -5197,7 +5235,7 @@
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F319F6D0-ABAC-48C6-A867-062B0035D0C5}">
-  <dimension ref="A1:AF6"/>
+  <dimension ref="A1:AF12"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="23" max="23" width="8.21875" customWidth="1"/>
@@ -5550,6 +5588,361 @@
       <c r="V6">
         <f t="shared" ref="V6" si="11">T6-U6</f>
         <v>5.3333333333333321</v>
+      </c>
+    </row>
+    <row r="7" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="8" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B8">
+        <v>91</v>
+      </c>
+      <c r="C8">
+        <v>9</v>
+      </c>
+      <c r="D8">
+        <v>11</v>
+      </c>
+      <c r="E8">
+        <v>89</v>
+      </c>
+      <c r="G8">
+        <v>96</v>
+      </c>
+      <c r="H8">
+        <v>4</v>
+      </c>
+      <c r="I8">
+        <v>40</v>
+      </c>
+      <c r="J8">
+        <v>60</v>
+      </c>
+      <c r="L8">
+        <v>80</v>
+      </c>
+      <c r="M8">
+        <v>20</v>
+      </c>
+      <c r="N8">
+        <v>48</v>
+      </c>
+      <c r="O8">
+        <v>52</v>
+      </c>
+      <c r="Q8">
+        <f t="shared" ref="Q7:Q12" si="12">AVERAGE(C8:D8)</f>
+        <v>10</v>
+      </c>
+      <c r="R8">
+        <f t="shared" ref="R7:R12" si="13">AVERAGE(H8:I8)</f>
+        <v>22</v>
+      </c>
+      <c r="S8">
+        <f t="shared" ref="S7:S12" si="14">AVERAGE(M8:N8)</f>
+        <v>34</v>
+      </c>
+      <c r="T8">
+        <f t="shared" ref="T7:T12" si="15">AVERAGE(Q8:S8)</f>
+        <v>22</v>
+      </c>
+      <c r="U8">
+        <f t="shared" ref="U7:U12" si="16">MIN(Q8:S8)</f>
+        <v>10</v>
+      </c>
+      <c r="V8">
+        <f t="shared" ref="V7:V12" si="17">T8-U8</f>
+        <v>12</v>
+      </c>
+      <c r="W8">
+        <f>AVERAGE(Q8:Q12)</f>
+        <v>12.3</v>
+      </c>
+      <c r="X8">
+        <f>_xlfn.STDEV.S(Q8:Q12)</f>
+        <v>2.7294688127912341</v>
+      </c>
+      <c r="Y8">
+        <f>AVERAGE(R8:R12)</f>
+        <v>17.8</v>
+      </c>
+      <c r="Z8">
+        <f>_xlfn.STDEV.S(R8:R12)</f>
+        <v>3.3652637340927662</v>
+      </c>
+      <c r="AA8">
+        <f>AVERAGE(S8:S12)</f>
+        <v>34.6</v>
+      </c>
+      <c r="AB8">
+        <f>_xlfn.STDEV.S(S8:S12)</f>
+        <v>3.5951356024495098</v>
+      </c>
+      <c r="AC8">
+        <f>AVERAGE(T8:T12)</f>
+        <v>21.56666666666667</v>
+      </c>
+      <c r="AD8">
+        <f>_xlfn.STDEV.S(T8:T12)</f>
+        <v>1.8050854088749744</v>
+      </c>
+      <c r="AE8">
+        <f>AVERAGE(V8:V12)</f>
+        <v>9.4666666666666668</v>
+      </c>
+      <c r="AF8">
+        <f>_xlfn.STDEV.S(V8:V12)</f>
+        <v>2.5149552679918559</v>
+      </c>
+    </row>
+    <row r="9" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B9">
+        <v>85</v>
+      </c>
+      <c r="C9">
+        <v>15</v>
+      </c>
+      <c r="D9">
+        <v>16</v>
+      </c>
+      <c r="E9">
+        <v>84</v>
+      </c>
+      <c r="G9">
+        <v>96</v>
+      </c>
+      <c r="H9">
+        <v>4</v>
+      </c>
+      <c r="I9">
+        <v>32</v>
+      </c>
+      <c r="J9">
+        <v>68</v>
+      </c>
+      <c r="L9">
+        <v>82</v>
+      </c>
+      <c r="M9">
+        <v>18</v>
+      </c>
+      <c r="N9">
+        <v>60</v>
+      </c>
+      <c r="O9">
+        <v>40</v>
+      </c>
+      <c r="Q9">
+        <f t="shared" si="12"/>
+        <v>15.5</v>
+      </c>
+      <c r="R9">
+        <f t="shared" si="13"/>
+        <v>18</v>
+      </c>
+      <c r="S9">
+        <f t="shared" si="14"/>
+        <v>39</v>
+      </c>
+      <c r="T9">
+        <f t="shared" si="15"/>
+        <v>24.166666666666668</v>
+      </c>
+      <c r="U9">
+        <f t="shared" si="16"/>
+        <v>15.5</v>
+      </c>
+      <c r="V9">
+        <f t="shared" si="17"/>
+        <v>8.6666666666666679</v>
+      </c>
+    </row>
+    <row r="10" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B10">
+        <v>90</v>
+      </c>
+      <c r="C10">
+        <v>10</v>
+      </c>
+      <c r="D10">
+        <v>18</v>
+      </c>
+      <c r="E10">
+        <v>82</v>
+      </c>
+      <c r="G10">
+        <v>96</v>
+      </c>
+      <c r="H10">
+        <v>4</v>
+      </c>
+      <c r="I10">
+        <v>22</v>
+      </c>
+      <c r="J10">
+        <v>78</v>
+      </c>
+      <c r="L10">
+        <v>88</v>
+      </c>
+      <c r="M10">
+        <v>12</v>
+      </c>
+      <c r="N10">
+        <v>49</v>
+      </c>
+      <c r="O10">
+        <v>51</v>
+      </c>
+      <c r="Q10">
+        <f t="shared" si="12"/>
+        <v>14</v>
+      </c>
+      <c r="R10">
+        <f t="shared" si="13"/>
+        <v>13</v>
+      </c>
+      <c r="S10">
+        <f t="shared" si="14"/>
+        <v>30.5</v>
+      </c>
+      <c r="T10">
+        <f t="shared" si="15"/>
+        <v>19.166666666666668</v>
+      </c>
+      <c r="U10">
+        <f t="shared" si="16"/>
+        <v>13</v>
+      </c>
+      <c r="V10">
+        <f t="shared" si="17"/>
+        <v>6.1666666666666679</v>
+      </c>
+    </row>
+    <row r="11" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B11">
+        <v>90</v>
+      </c>
+      <c r="C11">
+        <v>10</v>
+      </c>
+      <c r="D11">
+        <v>8</v>
+      </c>
+      <c r="E11">
+        <v>92</v>
+      </c>
+      <c r="G11">
+        <v>94</v>
+      </c>
+      <c r="H11">
+        <v>6</v>
+      </c>
+      <c r="I11">
+        <v>27</v>
+      </c>
+      <c r="J11">
+        <v>73</v>
+      </c>
+      <c r="L11">
+        <v>87</v>
+      </c>
+      <c r="M11">
+        <v>13</v>
+      </c>
+      <c r="N11">
+        <v>62</v>
+      </c>
+      <c r="O11">
+        <v>38</v>
+      </c>
+      <c r="Q11">
+        <f t="shared" si="12"/>
+        <v>9</v>
+      </c>
+      <c r="R11">
+        <f t="shared" si="13"/>
+        <v>16.5</v>
+      </c>
+      <c r="S11">
+        <f t="shared" si="14"/>
+        <v>37.5</v>
+      </c>
+      <c r="T11">
+        <f t="shared" si="15"/>
+        <v>21</v>
+      </c>
+      <c r="U11">
+        <f t="shared" si="16"/>
+        <v>9</v>
+      </c>
+      <c r="V11">
+        <f t="shared" si="17"/>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="12" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B12">
+        <v>94</v>
+      </c>
+      <c r="C12">
+        <v>6</v>
+      </c>
+      <c r="D12">
+        <v>20</v>
+      </c>
+      <c r="E12">
+        <v>80</v>
+      </c>
+      <c r="G12">
+        <v>99</v>
+      </c>
+      <c r="H12">
+        <v>1</v>
+      </c>
+      <c r="I12">
+        <v>38</v>
+      </c>
+      <c r="J12">
+        <v>62</v>
+      </c>
+      <c r="L12">
+        <v>90</v>
+      </c>
+      <c r="M12">
+        <v>10</v>
+      </c>
+      <c r="N12">
+        <v>54</v>
+      </c>
+      <c r="O12">
+        <v>46</v>
+      </c>
+      <c r="Q12">
+        <f t="shared" si="12"/>
+        <v>13</v>
+      </c>
+      <c r="R12">
+        <f t="shared" si="13"/>
+        <v>19.5</v>
+      </c>
+      <c r="S12">
+        <f t="shared" si="14"/>
+        <v>32</v>
+      </c>
+      <c r="T12">
+        <f t="shared" si="15"/>
+        <v>21.5</v>
+      </c>
+      <c r="U12">
+        <f t="shared" si="16"/>
+        <v>13</v>
+      </c>
+      <c r="V12">
+        <f t="shared" si="17"/>
+        <v>8.5</v>
       </c>
     </row>
   </sheetData>
@@ -5879,27 +6272,27 @@
         <v>50</v>
       </c>
       <c r="Q6">
-        <f t="shared" ref="Q6:Q15" si="6">AVERAGE(C6,D6)</f>
+        <f t="shared" ref="Q6:Q14" si="6">AVERAGE(C6,D6)</f>
         <v>13.5</v>
       </c>
       <c r="R6">
-        <f t="shared" ref="R6:R15" si="7">AVERAGE(H6,I6)</f>
+        <f t="shared" ref="R6:R14" si="7">AVERAGE(H6,I6)</f>
         <v>21</v>
       </c>
       <c r="S6">
-        <f t="shared" ref="S6:S15" si="8">AVERAGE(M6,N6)</f>
+        <f t="shared" ref="S6:S14" si="8">AVERAGE(M6,N6)</f>
         <v>32.5</v>
       </c>
       <c r="T6">
-        <f t="shared" ref="T6:T15" si="9">AVERAGE(Q6:S6)</f>
+        <f t="shared" ref="T6:T14" si="9">AVERAGE(Q6:S6)</f>
         <v>22.333333333333332</v>
       </c>
       <c r="U6">
-        <f t="shared" ref="U6:U15" si="10">MIN(Q6:S6)</f>
+        <f t="shared" ref="U6:U14" si="10">MIN(Q6:S6)</f>
         <v>13.5</v>
       </c>
       <c r="V6">
-        <f t="shared" ref="V6:V15" si="11">(1/3)*(T6-U6)</f>
+        <f t="shared" ref="V6:V14" si="11">(1/3)*(T6-U6)</f>
         <v>2.9444444444444438</v>
       </c>
       <c r="W6">
@@ -6818,27 +7211,27 @@
         <v>69</v>
       </c>
       <c r="Q6">
-        <f t="shared" ref="Q5:Q14" si="6">AVERAGE(C6,D6)</f>
+        <f t="shared" ref="Q6:Q14" si="6">AVERAGE(C6,D6)</f>
         <v>16.5</v>
       </c>
       <c r="R6">
-        <f t="shared" ref="R5:R14" si="7">AVERAGE(H6,I6)</f>
+        <f t="shared" ref="R6:R14" si="7">AVERAGE(H6,I6)</f>
         <v>21</v>
       </c>
       <c r="S6">
-        <f t="shared" ref="S5:S14" si="8">AVERAGE(M6,N6)</f>
+        <f t="shared" ref="S6:S14" si="8">AVERAGE(M6,N6)</f>
         <v>26</v>
       </c>
       <c r="T6">
-        <f t="shared" ref="T5:T14" si="9">AVERAGE(Q6:S6)</f>
+        <f t="shared" ref="T6:T14" si="9">AVERAGE(Q6:S6)</f>
         <v>21.166666666666668</v>
       </c>
       <c r="U6">
-        <f t="shared" ref="U5:U14" si="10">MIN(Q6:S6)</f>
+        <f t="shared" ref="U6:U14" si="10">MIN(Q6:S6)</f>
         <v>16.5</v>
       </c>
       <c r="V6">
-        <f t="shared" ref="V5:V14" si="11">(1/3)*(T6-U6)</f>
+        <f t="shared" ref="V6:V14" si="11">(1/3)*(T6-U6)</f>
         <v>1.5555555555555558</v>
       </c>
       <c r="W6">
@@ -10482,27 +10875,27 @@
         <v>74</v>
       </c>
       <c r="Q5">
-        <f t="shared" ref="Q5:Q13" si="0">AVERAGE(C5:D5)</f>
+        <f t="shared" ref="Q5:Q7" si="0">AVERAGE(C5:D5)</f>
         <v>8</v>
       </c>
       <c r="R5">
-        <f t="shared" ref="R5:R13" si="1">AVERAGE(H5:I5)</f>
+        <f t="shared" ref="R5:R7" si="1">AVERAGE(H5:I5)</f>
         <v>10</v>
       </c>
       <c r="S5">
-        <f t="shared" ref="S5:S13" si="2">AVERAGE(M5:N5)</f>
+        <f t="shared" ref="S5:S7" si="2">AVERAGE(M5:N5)</f>
         <v>24.5</v>
       </c>
       <c r="T5">
-        <f t="shared" ref="T5:T13" si="3">AVERAGE(Q5:S5)</f>
+        <f t="shared" ref="T5:T7" si="3">AVERAGE(Q5:S5)</f>
         <v>14.166666666666666</v>
       </c>
       <c r="AC5">
-        <f t="shared" ref="AC5:AC13" si="4">MIN(Q5:S5)</f>
+        <f t="shared" ref="AC5:AC7" si="4">MIN(Q5:S5)</f>
         <v>8</v>
       </c>
       <c r="AD5">
-        <f t="shared" ref="AD5:AD13" si="5">T5-AC5</f>
+        <f t="shared" ref="AD5:AD7" si="5">T5-AC5</f>
         <v>6.1666666666666661</v>
       </c>
     </row>
@@ -11010,27 +11403,27 @@
         <v>62</v>
       </c>
       <c r="Q5">
-        <f t="shared" ref="Q5:Q13" si="0">AVERAGE(C5:D5)</f>
+        <f t="shared" ref="Q5:Q6" si="0">AVERAGE(C5:D5)</f>
         <v>12</v>
       </c>
       <c r="R5">
-        <f t="shared" ref="R5:R13" si="1">AVERAGE(H5:I5)</f>
+        <f t="shared" ref="R5:R6" si="1">AVERAGE(H5:I5)</f>
         <v>13</v>
       </c>
       <c r="S5">
-        <f t="shared" ref="S5:S13" si="2">AVERAGE(M5:N5)</f>
+        <f t="shared" ref="S5:S6" si="2">AVERAGE(M5:N5)</f>
         <v>28</v>
       </c>
       <c r="T5">
-        <f t="shared" ref="T5:T7" si="3">AVERAGE(Q5:S5)</f>
+        <f t="shared" ref="T5:T6" si="3">AVERAGE(Q5:S5)</f>
         <v>17.666666666666668</v>
       </c>
       <c r="AC5">
-        <f t="shared" ref="AC5:AC13" si="4">MIN(Q5:S5)</f>
+        <f t="shared" ref="AC5:AC6" si="4">MIN(Q5:S5)</f>
         <v>12</v>
       </c>
       <c r="AD5">
-        <f t="shared" ref="AD5:AD7" si="5">T5-AC5</f>
+        <f t="shared" ref="AD5:AD6" si="5">T5-AC5</f>
         <v>5.6666666666666679</v>
       </c>
     </row>

--- a/DataAnalysis/LC/0.05/Results.xlsx
+++ b/DataAnalysis/LC/0.05/Results.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Utente\Desktop\CultureAwarenessTest\DataAnalysis\LC\0.05\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1A18028-EF88-453F-86F8-89609E80CD7F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97AD8F11-7591-46B5-A1F6-BD7FA552F6BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Foglio1" sheetId="1" r:id="rId1"/>
     <sheet name="MIT_DIFF_ONLYMIN_STDAUG" sheetId="19" r:id="rId2"/>
-    <sheet name="MIT_DIFF_ONLYMIN_NOAUG" sheetId="18" r:id="rId3"/>
+    <sheet name="PARBS_ONLYMIN_STDAUG" sheetId="18" r:id="rId3"/>
     <sheet name="MIT_PARBS_DIFF_ONLYMIN_STDAUG" sheetId="17" r:id="rId4"/>
     <sheet name="MIT_DIFF_STDAUG" sheetId="16" r:id="rId5"/>
     <sheet name="MIT_DIFF_NOAUG" sheetId="15" r:id="rId6"/>
@@ -52,7 +52,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="486" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="494" uniqueCount="76">
   <si>
     <t>Dati originali</t>
   </si>
@@ -597,7 +597,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:P29"/>
+  <dimension ref="A1:P34"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9.88671875" customWidth="1"/>
@@ -1043,202 +1043,345 @@
         <v>53</v>
       </c>
     </row>
-    <row r="20" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="D20" t="s">
-        <v>69</v>
-      </c>
-      <c r="G20">
-        <v>10.45</v>
-      </c>
-      <c r="H20">
-        <v>2.4432446550528732</v>
-      </c>
-      <c r="I20">
-        <v>16.05</v>
-      </c>
-      <c r="J20">
-        <v>2.4088955514462986</v>
-      </c>
-      <c r="K20">
-        <v>27.05</v>
-      </c>
-      <c r="L20">
-        <v>4.0514057916837869</v>
-      </c>
-      <c r="M20">
-        <v>17.850000000000001</v>
-      </c>
-      <c r="N20">
-        <v>1.8214259777966804</v>
-      </c>
-      <c r="O20">
-        <v>7.4</v>
-      </c>
-      <c r="P20">
-        <v>2.4434341346495017</v>
-      </c>
-    </row>
     <row r="21" spans="2:16" x14ac:dyDescent="0.3">
       <c r="D21" t="s">
-        <v>71</v>
+        <v>69</v>
+      </c>
+      <c r="G21">
+        <v>10.45</v>
+      </c>
+      <c r="H21">
+        <v>2.4432446550528732</v>
+      </c>
+      <c r="I21">
+        <v>16.05</v>
+      </c>
+      <c r="J21">
+        <v>2.4088955514462986</v>
+      </c>
+      <c r="K21">
+        <v>27.05</v>
+      </c>
+      <c r="L21">
+        <v>4.0514057916837869</v>
+      </c>
+      <c r="M21">
+        <v>17.850000000000001</v>
+      </c>
+      <c r="N21">
+        <v>1.8214259777966804</v>
+      </c>
+      <c r="O21">
+        <v>7.4</v>
+      </c>
+      <c r="P21">
+        <v>2.4434341346495017</v>
       </c>
     </row>
     <row r="22" spans="2:16" x14ac:dyDescent="0.3">
       <c r="E22" t="s">
+        <v>75</v>
+      </c>
+      <c r="G22">
+        <v>13</v>
+      </c>
+      <c r="H22">
+        <v>2.1213203435596424</v>
+      </c>
+      <c r="I22">
+        <v>20</v>
+      </c>
+      <c r="J22">
+        <v>0.70710678118654757</v>
+      </c>
+      <c r="K22">
+        <v>26.25</v>
+      </c>
+      <c r="L22">
+        <v>3.8890872965260113</v>
+      </c>
+      <c r="M22">
+        <v>19.75</v>
+      </c>
+      <c r="N22">
+        <v>0.35355339059327379</v>
+      </c>
+      <c r="O22">
+        <v>6.75</v>
+      </c>
+      <c r="P22">
+        <v>2.4748737341529163</v>
+      </c>
+    </row>
+    <row r="23" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="D23" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="24" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="E24" t="s">
         <v>69</v>
       </c>
-      <c r="G22">
+      <c r="G24">
         <v>8.625</v>
       </c>
-      <c r="H22">
+      <c r="H24">
         <v>1.7017148213885114</v>
       </c>
-      <c r="I22">
+      <c r="I24">
         <v>15.875</v>
       </c>
-      <c r="J22">
+      <c r="J24">
         <v>4.5711960506341587</v>
       </c>
-      <c r="K22">
+      <c r="K24">
         <v>26.75</v>
       </c>
-      <c r="L22">
+      <c r="L24">
         <v>1.5545631755148024</v>
       </c>
-      <c r="M22">
+      <c r="M24">
         <v>17.083333333333332</v>
       </c>
-      <c r="N22">
+      <c r="N24">
         <v>2.0389721448336333</v>
       </c>
-      <c r="O22">
+      <c r="O24">
         <v>8.4583333333333321</v>
       </c>
-      <c r="P22">
+      <c r="P24">
         <v>2.3028766229958482</v>
       </c>
     </row>
-    <row r="24" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B24" t="s">
+    <row r="25" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="E25" t="s">
+        <v>75</v>
+      </c>
+      <c r="G25">
+        <v>11.5</v>
+      </c>
+      <c r="H25">
+        <v>1.4142135623730951</v>
+      </c>
+      <c r="I25">
+        <v>16.25</v>
+      </c>
+      <c r="J25">
+        <v>3.1819805153394638</v>
+      </c>
+      <c r="K25">
+        <v>30.75</v>
+      </c>
+      <c r="L25">
+        <v>3.1819805153394638</v>
+      </c>
+      <c r="M25">
+        <v>19.5</v>
+      </c>
+      <c r="N25">
+        <v>0.47140452079103001</v>
+      </c>
+      <c r="O25">
+        <v>8</v>
+      </c>
+      <c r="P25">
+        <v>0.94280904158206502</v>
+      </c>
+    </row>
+    <row r="27" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B27" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="25" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="C25" t="s">
+    <row r="28" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="C28" t="s">
         <v>4</v>
       </c>
-      <c r="G25">
+      <c r="G28">
         <v>14.333333333333334</v>
       </c>
-      <c r="H25">
+      <c r="H28">
         <v>2.1602468994692834</v>
       </c>
-      <c r="I25">
+      <c r="I28">
         <v>16.166666666666668</v>
       </c>
-      <c r="J25">
+      <c r="J28">
         <v>2.6956755492207609</v>
       </c>
-      <c r="K25">
+      <c r="K28">
         <v>23.916666666666668</v>
       </c>
-      <c r="L25">
+      <c r="L28">
         <v>4.4879468208376423</v>
       </c>
-      <c r="M25">
+      <c r="M28">
         <v>18.138888888888889</v>
       </c>
-      <c r="N25">
+      <c r="N28">
         <v>1.8481722703094376</v>
       </c>
-      <c r="O25">
+      <c r="O28">
         <v>4.2222222222222223</v>
       </c>
-      <c r="P25">
+      <c r="P28">
         <v>1.6113026706042233</v>
       </c>
     </row>
-    <row r="26" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="C26" t="s">
+    <row r="29" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="C29" t="s">
         <v>69</v>
       </c>
-      <c r="F26" t="s">
+      <c r="F29" t="s">
         <v>22</v>
       </c>
-      <c r="G26">
+      <c r="G29">
         <v>10.5</v>
       </c>
-      <c r="H26">
+      <c r="H29">
         <v>2.2638462845343543</v>
       </c>
-      <c r="I26">
+      <c r="I29">
         <v>15.5</v>
       </c>
-      <c r="J26">
+      <c r="J29">
         <v>3.0207614933986431</v>
       </c>
-      <c r="K26">
+      <c r="K29">
         <v>17.899999999999999</v>
       </c>
-      <c r="L26">
+      <c r="L29">
         <v>2.8591956910991616</v>
       </c>
-      <c r="M26">
+      <c r="M29">
         <v>14.633333333333331</v>
       </c>
-      <c r="N26">
+      <c r="N29">
         <v>1.3091557924436987</v>
       </c>
-      <c r="O26">
+      <c r="O29">
         <v>4.1333333333333329</v>
       </c>
-      <c r="P26">
+      <c r="P29">
         <v>2.3816427570528349</v>
       </c>
     </row>
-    <row r="27" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="C27" t="s">
+    <row r="30" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="C30" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="28" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="D28" t="s">
+    <row r="31" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="D31" t="s">
+        <v>69</v>
+      </c>
+      <c r="F31" t="s">
+        <v>75</v>
+      </c>
+      <c r="G31">
+        <v>12.25</v>
+      </c>
+      <c r="H31">
+        <v>2.4748737341529163</v>
+      </c>
+      <c r="I31">
+        <v>16.75</v>
+      </c>
+      <c r="J31">
+        <v>1.7677669529663689</v>
+      </c>
+      <c r="K31">
+        <v>25.25</v>
+      </c>
+      <c r="L31">
+        <v>0.35355339059327379</v>
+      </c>
+      <c r="M31">
+        <v>18.083333333333336</v>
+      </c>
+      <c r="N31">
+        <v>1.5320646925708539</v>
+      </c>
+      <c r="O31">
+        <v>5.8333333333333339</v>
+      </c>
+      <c r="P31">
+        <v>0.94280904158206169</v>
+      </c>
+    </row>
+    <row r="32" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="D32" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="29" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="E29" t="s">
+    <row r="33" spans="5:16" x14ac:dyDescent="0.3">
+      <c r="E33" t="s">
         <v>69</v>
       </c>
-      <c r="G29">
+      <c r="G33">
         <v>11.5</v>
       </c>
-      <c r="H29">
+      <c r="H33">
         <v>3.2787192621510002</v>
       </c>
-      <c r="I29">
+      <c r="I33">
         <v>13.833333333333334</v>
       </c>
-      <c r="J29">
+      <c r="J33">
         <v>1.4433756729740645</v>
       </c>
-      <c r="K29">
+      <c r="K33">
         <v>24.666666666666668</v>
       </c>
-      <c r="L29">
+      <c r="L33">
         <v>2.9297326385411577</v>
       </c>
-      <c r="M29">
+      <c r="M33">
         <v>16.666666666666668</v>
       </c>
-      <c r="N29">
+      <c r="N33">
         <v>1.5898986690282426</v>
       </c>
-      <c r="O29">
+      <c r="O33">
         <v>5.166666666666667</v>
       </c>
-      <c r="P29">
+      <c r="P33">
         <v>1.9649710204252651</v>
+      </c>
+    </row>
+    <row r="34" spans="5:16" x14ac:dyDescent="0.3">
+      <c r="F34" t="s">
+        <v>75</v>
+      </c>
+      <c r="G34">
+        <v>9.1666666666666661</v>
+      </c>
+      <c r="H34">
+        <v>1.1547005383792495</v>
+      </c>
+      <c r="I34">
+        <v>16</v>
+      </c>
+      <c r="J34">
+        <v>1.8027756377319946</v>
+      </c>
+      <c r="K34">
+        <v>25.833333333333332</v>
+      </c>
+      <c r="L34">
+        <v>3.7527767497325724</v>
+      </c>
+      <c r="M34">
+        <v>17</v>
+      </c>
+      <c r="N34">
+        <v>0.60092521257733233</v>
+      </c>
+      <c r="O34">
+        <v>7.833333333333333</v>
+      </c>
+      <c r="P34">
+        <v>1.6414763002993502</v>
       </c>
     </row>
   </sheetData>
@@ -5633,27 +5776,27 @@
         <v>52</v>
       </c>
       <c r="Q8">
-        <f t="shared" ref="Q7:Q12" si="12">AVERAGE(C8:D8)</f>
+        <f t="shared" ref="Q8:Q12" si="12">AVERAGE(C8:D8)</f>
         <v>10</v>
       </c>
       <c r="R8">
-        <f t="shared" ref="R7:R12" si="13">AVERAGE(H8:I8)</f>
+        <f t="shared" ref="R8:R12" si="13">AVERAGE(H8:I8)</f>
         <v>22</v>
       </c>
       <c r="S8">
-        <f t="shared" ref="S7:S12" si="14">AVERAGE(M8:N8)</f>
+        <f t="shared" ref="S8:S12" si="14">AVERAGE(M8:N8)</f>
         <v>34</v>
       </c>
       <c r="T8">
-        <f t="shared" ref="T7:T12" si="15">AVERAGE(Q8:S8)</f>
+        <f t="shared" ref="T8:T12" si="15">AVERAGE(Q8:S8)</f>
         <v>22</v>
       </c>
       <c r="U8">
-        <f t="shared" ref="U7:U12" si="16">MIN(Q8:S8)</f>
+        <f t="shared" ref="U8:U12" si="16">MIN(Q8:S8)</f>
         <v>10</v>
       </c>
       <c r="V8">
-        <f t="shared" ref="V7:V12" si="17">T8-U8</f>
+        <f t="shared" ref="V8:V12" si="17">T8-U8</f>
         <v>12</v>
       </c>
       <c r="W8">
@@ -10668,7 +10811,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4D0CE18A-8B26-4E93-B497-B59E55EFEC0E}">
-  <dimension ref="A2:AF7"/>
+  <dimension ref="A2:AF19"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="2" spans="1:32" x14ac:dyDescent="0.3">
@@ -10789,36 +10932,36 @@
         <v>18</v>
       </c>
       <c r="U4">
-        <f>AVERAGE(Q4:Q13)</f>
-        <v>8.625</v>
+        <f>AVERAGE(Q4:Q20)</f>
+        <v>9.5833333333333339</v>
       </c>
       <c r="V4">
-        <f>_xlfn.STDEV.S(Q4:Q13)</f>
-        <v>1.7017148213885114</v>
+        <f>_xlfn.STDEV.S(Q4:Q20)</f>
+        <v>2.0836666400042674</v>
       </c>
       <c r="W4">
-        <f>AVERAGE(R4:R13)</f>
-        <v>15.875</v>
+        <f>AVERAGE(R4:R20)</f>
+        <v>16</v>
       </c>
       <c r="X4">
-        <f>_xlfn.STDEV.S(R4:R13)</f>
-        <v>4.5711960506341587</v>
+        <f>_xlfn.STDEV.S(R4:R20)</f>
+        <v>3.8209946349085602</v>
       </c>
       <c r="Y4">
-        <f>AVERAGE(S4:S13)</f>
-        <v>26.75</v>
+        <f>AVERAGE(S4:S20)</f>
+        <v>28.083333333333332</v>
       </c>
       <c r="Z4">
-        <f>_xlfn.STDEV.S(S4:S13)</f>
-        <v>1.5545631755148024</v>
+        <f>_xlfn.STDEV.S(S4:S20)</f>
+        <v>2.7823850680067035</v>
       </c>
       <c r="AA4">
-        <f>AVERAGE(T4:T13)</f>
-        <v>17.083333333333332</v>
+        <f>AVERAGE(T4:T20)</f>
+        <v>17.888888888888889</v>
       </c>
       <c r="AB4">
-        <f>_xlfn.STDEV.S(T4:T13)</f>
-        <v>2.0389721448336333</v>
+        <f>_xlfn.STDEV.S(T4:T20)</f>
+        <v>2.0239309020557754</v>
       </c>
       <c r="AC4">
         <f>MIN(Q4:S4)</f>
@@ -10829,12 +10972,12 @@
         <v>11.5</v>
       </c>
       <c r="AE4">
-        <f>AVERAGE(AD4:AD13)</f>
-        <v>8.4583333333333321</v>
+        <f>AVERAGE(AD4:AD20)</f>
+        <v>8.3055555555555554</v>
       </c>
       <c r="AF4">
-        <f>_xlfn.STDEV.S(AD4:AD13)</f>
-        <v>2.3028766229958482</v>
+        <f>_xlfn.STDEV.S(AD4:AD20)</f>
+        <v>1.8481722703094403</v>
       </c>
     </row>
     <row r="5" spans="1:32" x14ac:dyDescent="0.3">
@@ -11020,6 +11163,175 @@
       </c>
       <c r="AD7">
         <f t="shared" si="5"/>
+        <v>7.3333333333333321</v>
+      </c>
+    </row>
+    <row r="17" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="18" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B18">
+        <v>91</v>
+      </c>
+      <c r="C18">
+        <v>9</v>
+      </c>
+      <c r="D18">
+        <v>12</v>
+      </c>
+      <c r="E18">
+        <v>88</v>
+      </c>
+      <c r="G18">
+        <v>95</v>
+      </c>
+      <c r="H18">
+        <v>5</v>
+      </c>
+      <c r="I18">
+        <v>32</v>
+      </c>
+      <c r="J18">
+        <v>68</v>
+      </c>
+      <c r="L18">
+        <v>86</v>
+      </c>
+      <c r="M18">
+        <v>14</v>
+      </c>
+      <c r="N18">
+        <v>43</v>
+      </c>
+      <c r="O18">
+        <v>57</v>
+      </c>
+      <c r="Q18">
+        <f>AVERAGE(C18:D18)</f>
+        <v>10.5</v>
+      </c>
+      <c r="R18">
+        <f>AVERAGE(H18:I18)</f>
+        <v>18.5</v>
+      </c>
+      <c r="S18">
+        <f>AVERAGE(M18:N18)</f>
+        <v>28.5</v>
+      </c>
+      <c r="T18">
+        <f>AVERAGE(Q18:S18)</f>
+        <v>19.166666666666668</v>
+      </c>
+      <c r="U18">
+        <f>AVERAGE(Q18:Q34)</f>
+        <v>11.5</v>
+      </c>
+      <c r="V18">
+        <f>_xlfn.STDEV.S(Q18:Q34)</f>
+        <v>1.4142135623730951</v>
+      </c>
+      <c r="W18">
+        <f>AVERAGE(R18:R34)</f>
+        <v>16.25</v>
+      </c>
+      <c r="X18">
+        <f>_xlfn.STDEV.S(R18:R34)</f>
+        <v>3.1819805153394638</v>
+      </c>
+      <c r="Y18">
+        <f>AVERAGE(S18:S34)</f>
+        <v>30.75</v>
+      </c>
+      <c r="Z18">
+        <f>_xlfn.STDEV.S(S18:S34)</f>
+        <v>3.1819805153394638</v>
+      </c>
+      <c r="AA18">
+        <f>AVERAGE(T18:T34)</f>
+        <v>19.5</v>
+      </c>
+      <c r="AB18">
+        <f>_xlfn.STDEV.S(T18:T34)</f>
+        <v>0.47140452079103001</v>
+      </c>
+      <c r="AC18">
+        <f>MIN(Q18:S18)</f>
+        <v>10.5</v>
+      </c>
+      <c r="AD18">
+        <f>T18-AC18</f>
+        <v>8.6666666666666679</v>
+      </c>
+      <c r="AE18">
+        <f>AVERAGE(AD18:AD34)</f>
+        <v>8</v>
+      </c>
+      <c r="AF18">
+        <f>_xlfn.STDEV.S(AD18:AD34)</f>
+        <v>0.94280904158206502</v>
+      </c>
+    </row>
+    <row r="19" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B19">
+        <v>86</v>
+      </c>
+      <c r="C19">
+        <v>14</v>
+      </c>
+      <c r="D19">
+        <v>11</v>
+      </c>
+      <c r="E19">
+        <v>89</v>
+      </c>
+      <c r="G19">
+        <v>96</v>
+      </c>
+      <c r="H19">
+        <v>4</v>
+      </c>
+      <c r="I19">
+        <v>24</v>
+      </c>
+      <c r="J19">
+        <v>76</v>
+      </c>
+      <c r="L19">
+        <v>77</v>
+      </c>
+      <c r="M19">
+        <v>23</v>
+      </c>
+      <c r="N19">
+        <v>43</v>
+      </c>
+      <c r="O19">
+        <v>57</v>
+      </c>
+      <c r="Q19">
+        <f>AVERAGE(C19:D19)</f>
+        <v>12.5</v>
+      </c>
+      <c r="R19">
+        <f>AVERAGE(H19:I19)</f>
+        <v>14</v>
+      </c>
+      <c r="S19">
+        <f>AVERAGE(M19:N19)</f>
+        <v>33</v>
+      </c>
+      <c r="T19">
+        <f>AVERAGE(Q19:S19)</f>
+        <v>19.833333333333332</v>
+      </c>
+      <c r="AC19">
+        <f>MIN(Q19:S19)</f>
+        <v>12.5</v>
+      </c>
+      <c r="AD19">
+        <f>T19-AC19</f>
         <v>7.3333333333333321</v>
       </c>
     </row>
@@ -11030,7 +11342,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2E557A7D-364E-47EE-A0F3-0D888512E587}">
-  <dimension ref="A2:AF5"/>
+  <dimension ref="A2:AF6"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="2" spans="1:32" x14ac:dyDescent="0.3">
@@ -11098,95 +11410,229 @@
       </c>
     </row>
     <row r="4" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="Q4" t="e">
+      <c r="B4">
+        <v>93</v>
+      </c>
+      <c r="C4">
+        <v>7</v>
+      </c>
+      <c r="D4">
+        <v>10</v>
+      </c>
+      <c r="E4">
+        <v>90</v>
+      </c>
+      <c r="G4">
+        <v>97</v>
+      </c>
+      <c r="H4">
+        <v>3</v>
+      </c>
+      <c r="I4">
+        <v>25</v>
+      </c>
+      <c r="J4">
+        <v>75</v>
+      </c>
+      <c r="L4">
+        <v>79</v>
+      </c>
+      <c r="M4">
+        <v>21</v>
+      </c>
+      <c r="N4">
+        <v>35</v>
+      </c>
+      <c r="O4">
+        <v>65</v>
+      </c>
+      <c r="Q4">
         <f>AVERAGE(C4,D4)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="R4" t="e">
+        <v>8.5</v>
+      </c>
+      <c r="R4">
         <f>AVERAGE(H4,I4)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="S4" t="e">
+        <v>14</v>
+      </c>
+      <c r="S4">
         <f>AVERAGE(M4,N4)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="T4" t="e">
+        <v>28</v>
+      </c>
+      <c r="T4">
         <f>AVERAGE(Q4:S4)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="U4" t="e">
-        <f>AVERAGE(Q4,Q5)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="V4" t="e">
-        <f>_xlfn.STDEV.S(Q4,Q5)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="W4" t="e">
-        <f>AVERAGE(R4,R5)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="X4" t="e">
-        <f>_xlfn.STDEV.S(R4,R5)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Y4" t="e">
-        <f>AVERAGE(S4,S5)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Z4" t="e">
-        <f>_xlfn.STDEV.S(S4,S5)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AA4" t="e">
-        <f>AVERAGE(T4,T5)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AB4" t="e">
-        <f>_xlfn.STDEV.S(T4,T5)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AC4" t="e">
+        <v>16.833333333333332</v>
+      </c>
+      <c r="U4">
+        <f>AVERAGE(Q4,Q5:Q6)</f>
+        <v>9.1666666666666661</v>
+      </c>
+      <c r="V4">
+        <f>_xlfn.STDEV.S(Q4,Q5:Q6)</f>
+        <v>1.1547005383792495</v>
+      </c>
+      <c r="W4">
+        <f>AVERAGE(R4,R5:R7)</f>
+        <v>16</v>
+      </c>
+      <c r="X4">
+        <f>_xlfn.STDEV.S(R4,R5:R6)</f>
+        <v>1.8027756377319946</v>
+      </c>
+      <c r="Y4">
+        <f>AVERAGE(S4,S5:S6)</f>
+        <v>25.833333333333332</v>
+      </c>
+      <c r="Z4">
+        <f>_xlfn.STDEV.S(S4,S5:S6)</f>
+        <v>3.7527767497325724</v>
+      </c>
+      <c r="AA4">
+        <f>AVERAGE(T4,T5:T6)</f>
+        <v>17</v>
+      </c>
+      <c r="AB4">
+        <f>_xlfn.STDEV.S(T4,T5:T6)</f>
+        <v>0.60092521257733233</v>
+      </c>
+      <c r="AC4">
         <f>MIN(Q4:S4)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AD4" t="e">
-        <f>(1/3)*(T4-AC4)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AE4" t="e">
-        <f>AVERAGE(AD4,AD5)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AF4" t="e">
-        <f>_xlfn.STDEV.S(AD4,AD5)</f>
-        <v>#DIV/0!</v>
+        <v>8.5</v>
+      </c>
+      <c r="AD4">
+        <f t="shared" ref="AD4:AD5" si="0">(T4-AC4)</f>
+        <v>8.3333333333333321</v>
+      </c>
+      <c r="AE4">
+        <f>AVERAGE(AD4,AD5:AD6)</f>
+        <v>7.833333333333333</v>
+      </c>
+      <c r="AF4">
+        <f>_xlfn.STDEV.S(AD4,AD5:AD6)</f>
+        <v>1.6414763002993502</v>
       </c>
     </row>
     <row r="5" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="Q5" t="e">
+      <c r="B5">
+        <v>88</v>
+      </c>
+      <c r="C5">
+        <v>12</v>
+      </c>
+      <c r="D5">
+        <v>9</v>
+      </c>
+      <c r="E5">
+        <v>91</v>
+      </c>
+      <c r="G5">
+        <v>96</v>
+      </c>
+      <c r="H5">
+        <v>4</v>
+      </c>
+      <c r="I5">
+        <v>31</v>
+      </c>
+      <c r="J5">
+        <v>69</v>
+      </c>
+      <c r="L5">
+        <v>83</v>
+      </c>
+      <c r="M5">
+        <v>17</v>
+      </c>
+      <c r="N5">
+        <v>26</v>
+      </c>
+      <c r="O5">
+        <v>74</v>
+      </c>
+      <c r="Q5">
         <f>AVERAGE(C5,D5)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="R5" t="e">
+        <v>10.5</v>
+      </c>
+      <c r="R5">
         <f>AVERAGE(H5,I5)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="S5" t="e">
+        <v>17.5</v>
+      </c>
+      <c r="S5">
         <f>AVERAGE(M5,N5)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="T5" t="e">
+        <v>21.5</v>
+      </c>
+      <c r="T5">
         <f>AVERAGE(Q5:S5)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AC5" t="e">
+        <v>16.5</v>
+      </c>
+      <c r="AC5">
         <f>MIN(Q5:S5)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AD5" t="e">
-        <f>(1/3)*(T5-AC5)</f>
-        <v>#DIV/0!</v>
+        <v>10.5</v>
+      </c>
+      <c r="AD5">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B6">
+        <v>93</v>
+      </c>
+      <c r="C6">
+        <v>7</v>
+      </c>
+      <c r="D6">
+        <v>10</v>
+      </c>
+      <c r="E6">
+        <v>90</v>
+      </c>
+      <c r="G6">
+        <v>91</v>
+      </c>
+      <c r="H6">
+        <v>9</v>
+      </c>
+      <c r="I6">
+        <v>24</v>
+      </c>
+      <c r="J6">
+        <v>76</v>
+      </c>
+      <c r="L6">
+        <v>81</v>
+      </c>
+      <c r="M6">
+        <v>19</v>
+      </c>
+      <c r="N6">
+        <v>37</v>
+      </c>
+      <c r="O6">
+        <v>63</v>
+      </c>
+      <c r="Q6">
+        <f>AVERAGE(C6,D6)</f>
+        <v>8.5</v>
+      </c>
+      <c r="R6">
+        <f>AVERAGE(H6,I6)</f>
+        <v>16.5</v>
+      </c>
+      <c r="S6">
+        <f>AVERAGE(M6,N6)</f>
+        <v>28</v>
+      </c>
+      <c r="T6">
+        <f>AVERAGE(Q6:S6)</f>
+        <v>17.666666666666668</v>
+      </c>
+      <c r="AC6">
+        <f>MIN(Q6:S6)</f>
+        <v>8.5</v>
+      </c>
+      <c r="AD6">
+        <f>(T6-AC6)</f>
+        <v>9.1666666666666679</v>
       </c>
     </row>
   </sheetData>
@@ -11496,7 +11942,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8A4C68C5-0EAB-4233-98F5-D346BC512EB4}">
-  <dimension ref="A2:AF13"/>
+  <dimension ref="A2:AF21"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="2" spans="1:32" x14ac:dyDescent="0.3">
@@ -12223,8 +12669,178 @@
         <v>6</v>
       </c>
     </row>
+    <row r="19" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="20" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B20">
+        <v>94</v>
+      </c>
+      <c r="C20">
+        <v>6</v>
+      </c>
+      <c r="D20">
+        <v>17</v>
+      </c>
+      <c r="E20">
+        <v>83</v>
+      </c>
+      <c r="G20">
+        <v>97</v>
+      </c>
+      <c r="H20">
+        <v>3</v>
+      </c>
+      <c r="I20">
+        <v>36</v>
+      </c>
+      <c r="J20">
+        <v>64</v>
+      </c>
+      <c r="L20">
+        <v>93</v>
+      </c>
+      <c r="M20">
+        <v>7</v>
+      </c>
+      <c r="N20">
+        <v>51</v>
+      </c>
+      <c r="O20">
+        <v>49</v>
+      </c>
+      <c r="Q20">
+        <f t="shared" ref="Q14:Q21" si="6">AVERAGE(C20:D20)</f>
+        <v>11.5</v>
+      </c>
+      <c r="R20">
+        <f t="shared" ref="R14:R21" si="7">AVERAGE(H20:I20)</f>
+        <v>19.5</v>
+      </c>
+      <c r="S20">
+        <f t="shared" ref="S14:S21" si="8">AVERAGE(M20:N20)</f>
+        <v>29</v>
+      </c>
+      <c r="T20">
+        <f t="shared" ref="T14:T21" si="9">AVERAGE(Q20:S20)</f>
+        <v>20</v>
+      </c>
+      <c r="U20">
+        <f>AVERAGE(Q20:Q29)</f>
+        <v>13</v>
+      </c>
+      <c r="V20">
+        <f>_xlfn.STDEV.S(Q20:Q29)</f>
+        <v>2.1213203435596424</v>
+      </c>
+      <c r="W20">
+        <f>AVERAGE(R20:R29)</f>
+        <v>20</v>
+      </c>
+      <c r="X20">
+        <f>_xlfn.STDEV.S(R20:R29)</f>
+        <v>0.70710678118654757</v>
+      </c>
+      <c r="Y20">
+        <f>AVERAGE(S20:S29)</f>
+        <v>26.25</v>
+      </c>
+      <c r="Z20">
+        <f>_xlfn.STDEV.S(S20:S29)</f>
+        <v>3.8890872965260113</v>
+      </c>
+      <c r="AA20">
+        <f>AVERAGE(T20:T29)</f>
+        <v>19.75</v>
+      </c>
+      <c r="AB20">
+        <f>_xlfn.STDEV.S(T20:T29)</f>
+        <v>0.35355339059327379</v>
+      </c>
+      <c r="AC20">
+        <f t="shared" ref="AC14:AC21" si="10">MIN(Q20:S20)</f>
+        <v>11.5</v>
+      </c>
+      <c r="AD20">
+        <f t="shared" ref="AD14:AD21" si="11">T20-AC20</f>
+        <v>8.5</v>
+      </c>
+      <c r="AE20">
+        <f>AVERAGE(AD20:AD29)</f>
+        <v>6.75</v>
+      </c>
+      <c r="AF20">
+        <f>_xlfn.STDEV.S(AD20:AD29)</f>
+        <v>2.4748737341529163</v>
+      </c>
+    </row>
+    <row r="21" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B21">
+        <v>87</v>
+      </c>
+      <c r="C21">
+        <v>13</v>
+      </c>
+      <c r="D21">
+        <v>16</v>
+      </c>
+      <c r="E21">
+        <v>84</v>
+      </c>
+      <c r="G21">
+        <v>92</v>
+      </c>
+      <c r="H21">
+        <v>8</v>
+      </c>
+      <c r="I21">
+        <v>33</v>
+      </c>
+      <c r="J21">
+        <v>67</v>
+      </c>
+      <c r="L21">
+        <v>85</v>
+      </c>
+      <c r="M21">
+        <v>15</v>
+      </c>
+      <c r="N21">
+        <v>32</v>
+      </c>
+      <c r="O21">
+        <v>68</v>
+      </c>
+      <c r="Q21">
+        <f t="shared" si="6"/>
+        <v>14.5</v>
+      </c>
+      <c r="R21">
+        <f t="shared" si="7"/>
+        <v>20.5</v>
+      </c>
+      <c r="S21">
+        <f t="shared" si="8"/>
+        <v>23.5</v>
+      </c>
+      <c r="T21">
+        <f t="shared" si="9"/>
+        <v>19.5</v>
+      </c>
+      <c r="AC21">
+        <f t="shared" si="10"/>
+        <v>14.5</v>
+      </c>
+      <c r="AD21">
+        <f t="shared" si="11"/>
+        <v>5</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -12393,7 +13009,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A366D673-4552-407C-AD95-3B60150A1024}">
-  <dimension ref="A2:AF8"/>
+  <dimension ref="A2:AF13"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="2" spans="1:32" x14ac:dyDescent="0.3">
@@ -12807,6 +13423,175 @@
       </c>
       <c r="V8">
         <f t="shared" si="5"/>
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="12" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B12">
+        <v>92</v>
+      </c>
+      <c r="C12">
+        <v>8</v>
+      </c>
+      <c r="D12">
+        <v>20</v>
+      </c>
+      <c r="E12">
+        <v>80</v>
+      </c>
+      <c r="G12">
+        <v>98</v>
+      </c>
+      <c r="H12">
+        <v>2</v>
+      </c>
+      <c r="I12">
+        <v>34</v>
+      </c>
+      <c r="J12">
+        <v>66</v>
+      </c>
+      <c r="L12">
+        <v>87</v>
+      </c>
+      <c r="M12">
+        <v>13</v>
+      </c>
+      <c r="N12">
+        <v>38</v>
+      </c>
+      <c r="O12">
+        <v>62</v>
+      </c>
+      <c r="Q12">
+        <f t="shared" ref="Q9:Q13" si="6">AVERAGE(C12:D12)</f>
+        <v>14</v>
+      </c>
+      <c r="R12">
+        <f t="shared" ref="R9:R13" si="7">AVERAGE(H12:I12)</f>
+        <v>18</v>
+      </c>
+      <c r="S12">
+        <f t="shared" ref="S9:S13" si="8">AVERAGE(M12:N12)</f>
+        <v>25.5</v>
+      </c>
+      <c r="T12">
+        <f t="shared" ref="T9:T13" si="9">AVERAGE(Q12:S12)</f>
+        <v>19.166666666666668</v>
+      </c>
+      <c r="U12">
+        <f t="shared" ref="U9:U13" si="10">MIN(Q12:S12)</f>
+        <v>14</v>
+      </c>
+      <c r="V12">
+        <f t="shared" ref="V9:V13" si="11">T12-U12</f>
+        <v>5.1666666666666679</v>
+      </c>
+      <c r="W12">
+        <f>AVERAGE(Q12:Q18)</f>
+        <v>12.25</v>
+      </c>
+      <c r="X12">
+        <f>_xlfn.STDEV.S(Q12:Q18)</f>
+        <v>2.4748737341529163</v>
+      </c>
+      <c r="Y12">
+        <f>AVERAGE(R12:R18)</f>
+        <v>16.75</v>
+      </c>
+      <c r="Z12">
+        <f>_xlfn.STDEV.S(R12:R18)</f>
+        <v>1.7677669529663689</v>
+      </c>
+      <c r="AA12">
+        <f>AVERAGE(S12:S18)</f>
+        <v>25.25</v>
+      </c>
+      <c r="AB12">
+        <f>_xlfn.STDEV.S(S12:S18)</f>
+        <v>0.35355339059327379</v>
+      </c>
+      <c r="AC12">
+        <f>AVERAGE(T12:T18)</f>
+        <v>18.083333333333336</v>
+      </c>
+      <c r="AD12">
+        <f>_xlfn.STDEV.S(T12:T18)</f>
+        <v>1.5320646925708539</v>
+      </c>
+      <c r="AE12">
+        <f>AVERAGE(V12:V18)</f>
+        <v>5.8333333333333339</v>
+      </c>
+      <c r="AF12">
+        <f>_xlfn.STDEV.S(V12:V18)</f>
+        <v>0.94280904158206169</v>
+      </c>
+    </row>
+    <row r="13" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B13">
+        <v>93</v>
+      </c>
+      <c r="C13">
+        <v>7</v>
+      </c>
+      <c r="D13">
+        <v>14</v>
+      </c>
+      <c r="E13">
+        <v>86</v>
+      </c>
+      <c r="G13">
+        <v>94</v>
+      </c>
+      <c r="H13">
+        <v>6</v>
+      </c>
+      <c r="I13">
+        <v>25</v>
+      </c>
+      <c r="J13">
+        <v>75</v>
+      </c>
+      <c r="L13">
+        <v>70</v>
+      </c>
+      <c r="M13">
+        <v>30</v>
+      </c>
+      <c r="N13">
+        <v>20</v>
+      </c>
+      <c r="O13">
+        <v>80</v>
+      </c>
+      <c r="Q13">
+        <f t="shared" si="6"/>
+        <v>10.5</v>
+      </c>
+      <c r="R13">
+        <f t="shared" si="7"/>
+        <v>15.5</v>
+      </c>
+      <c r="S13">
+        <f t="shared" si="8"/>
+        <v>25</v>
+      </c>
+      <c r="T13">
+        <f t="shared" si="9"/>
+        <v>17</v>
+      </c>
+      <c r="U13">
+        <f t="shared" si="10"/>
+        <v>10.5</v>
+      </c>
+      <c r="V13">
+        <f t="shared" si="11"/>
         <v>6.5</v>
       </c>
     </row>

--- a/DataAnalysis/LC/0.05/Results.xlsx
+++ b/DataAnalysis/LC/0.05/Results.xlsx
@@ -8,28 +8,29 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Utente\Desktop\CultureAwarenessTest\DataAnalysis\LC\0.05\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97AD8F11-7591-46B5-A1F6-BD7FA552F6BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B26C9456-A234-4B51-BE0C-B29D2B82AF5D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Foglio1" sheetId="1" r:id="rId1"/>
-    <sheet name="MIT_DIFF_ONLYMIN_STDAUG" sheetId="19" r:id="rId2"/>
-    <sheet name="PARBS_ONLYMIN_STDAUG" sheetId="18" r:id="rId3"/>
-    <sheet name="MIT_PARBS_DIFF_ONLYMIN_STDAUG" sheetId="17" r:id="rId4"/>
-    <sheet name="MIT_DIFF_STDAUG" sheetId="16" r:id="rId5"/>
-    <sheet name="MIT_DIFF_NOAUG" sheetId="15" r:id="rId6"/>
-    <sheet name="MIT_PARBS_STDAUG" sheetId="14" r:id="rId7"/>
-    <sheet name="MIT_PARBS_NOAUG" sheetId="13" r:id="rId8"/>
-    <sheet name="MIT_STDAUG" sheetId="12" r:id="rId9"/>
-    <sheet name="MIT_NOAUG" sheetId="11" r:id="rId10"/>
-    <sheet name="STD_IMB_AUG" sheetId="10" r:id="rId11"/>
-    <sheet name="STD_IMB_NOAUG" sheetId="9" r:id="rId12"/>
-    <sheet name="DIFF" sheetId="8" r:id="rId13"/>
-    <sheet name="STD_BAL_ADV_NOCLSDIV" sheetId="7" r:id="rId14"/>
-    <sheet name="STD_BAL_ADV_CLSDIV" sheetId="6" r:id="rId15"/>
-    <sheet name="STD_BAL_STDAUG" sheetId="5" r:id="rId16"/>
-    <sheet name="STD_BAL_NOAUG" sheetId="2" r:id="rId17"/>
+    <sheet name="DIFF_ONLYMIN" sheetId="20" r:id="rId2"/>
+    <sheet name="MIT_DIFF_ONLYMIN_STDAUG" sheetId="19" r:id="rId3"/>
+    <sheet name="PARBS_ONLYMIN_STDAUG" sheetId="18" r:id="rId4"/>
+    <sheet name="MIT_PARBS_DIFF_ONLYMIN_STDAUG" sheetId="17" r:id="rId5"/>
+    <sheet name="MIT_DIFF_STDAUG" sheetId="16" r:id="rId6"/>
+    <sheet name="MIT_DIFF_NOAUG" sheetId="15" r:id="rId7"/>
+    <sheet name="MIT_PARBS_STDAUG" sheetId="14" r:id="rId8"/>
+    <sheet name="MIT_PARBS_NOAUG" sheetId="13" r:id="rId9"/>
+    <sheet name="MIT_STDAUG" sheetId="12" r:id="rId10"/>
+    <sheet name="MIT_NOAUG" sheetId="11" r:id="rId11"/>
+    <sheet name="STD_IMB_AUG" sheetId="10" r:id="rId12"/>
+    <sheet name="STD_IMB_NOAUG" sheetId="9" r:id="rId13"/>
+    <sheet name="DIFF" sheetId="8" r:id="rId14"/>
+    <sheet name="STD_BAL_ADV_NOCLSDIV" sheetId="7" r:id="rId15"/>
+    <sheet name="STD_BAL_ADV_CLSDIV" sheetId="6" r:id="rId16"/>
+    <sheet name="STD_BAL_STDAUG" sheetId="5" r:id="rId17"/>
+    <sheet name="STD_BAL_NOAUG" sheetId="2" r:id="rId18"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -52,7 +53,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="494" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="514" uniqueCount="76">
   <si>
     <t>Dati originali</t>
   </si>
@@ -597,13 +598,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:P34"/>
+  <dimension ref="A1:AA36"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -638,12 +639,12 @@
         <v>21</v>
       </c>
     </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:27" x14ac:dyDescent="0.3">
       <c r="B2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:27" x14ac:dyDescent="0.3">
       <c r="C3" t="s">
         <v>4</v>
       </c>
@@ -678,7 +679,7 @@
         <v>1.0715167512214481</v>
       </c>
     </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:27" x14ac:dyDescent="0.3">
       <c r="C4" t="s">
         <v>2</v>
       </c>
@@ -715,18 +716,51 @@
       <c r="P4">
         <v>1.4174834246859023</v>
       </c>
-    </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q4" t="s">
+        <v>75</v>
+      </c>
+      <c r="R4">
+        <v>12.5</v>
+      </c>
+      <c r="S4">
+        <v>1.4142135623730951</v>
+      </c>
+      <c r="T4">
+        <v>16.5</v>
+      </c>
+      <c r="U4">
+        <v>0</v>
+      </c>
+      <c r="V4">
+        <v>34</v>
+      </c>
+      <c r="W4">
+        <v>2.8284271247461903</v>
+      </c>
+      <c r="X4">
+        <v>21</v>
+      </c>
+      <c r="Y4">
+        <v>1.4142135623730951</v>
+      </c>
+      <c r="Z4">
+        <v>8.5</v>
+      </c>
+      <c r="AA4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:27" x14ac:dyDescent="0.3">
       <c r="C5" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:27" x14ac:dyDescent="0.3">
       <c r="D6" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:27" x14ac:dyDescent="0.3">
       <c r="E7" t="s">
         <v>44</v>
       </c>
@@ -764,12 +798,12 @@
         <v>0.93623886368626152</v>
       </c>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:27" x14ac:dyDescent="0.3">
       <c r="D8" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:27" x14ac:dyDescent="0.3">
       <c r="E9" t="s">
         <v>44</v>
       </c>
@@ -807,7 +841,7 @@
         <v>0.36111111111111049</v>
       </c>
     </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:27" x14ac:dyDescent="0.3">
       <c r="C10" t="s">
         <v>53</v>
       </c>
@@ -842,7 +876,7 @@
         <v>2.697735676039775</v>
       </c>
     </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:27" x14ac:dyDescent="0.3">
       <c r="C11" t="s">
         <v>75</v>
       </c>
@@ -877,510 +911,548 @@
         <v>2.5149552679918559</v>
       </c>
     </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="B12" t="s">
+    <row r="12" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="D12" t="s">
+        <v>71</v>
+      </c>
+      <c r="E12" t="s">
+        <v>75</v>
+      </c>
+      <c r="G12">
+        <v>12.666666666666666</v>
+      </c>
+      <c r="H12">
+        <v>1.2583057392117918</v>
+      </c>
+      <c r="I12">
+        <v>18</v>
+      </c>
+      <c r="J12">
+        <v>3.2787192621510002</v>
+      </c>
+      <c r="K12">
+        <v>30.833333333333332</v>
+      </c>
+      <c r="L12">
+        <v>5.251983752196236</v>
+      </c>
+      <c r="M12">
+        <v>20.5</v>
+      </c>
+      <c r="N12">
+        <v>1.3642254619787419</v>
+      </c>
+      <c r="O12">
+        <v>7.833333333333333</v>
+      </c>
+      <c r="P12">
+        <v>2.4551533104427046</v>
+      </c>
+    </row>
+    <row r="14" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="B14" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="C13" t="s">
+    <row r="15" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="C15" t="s">
         <v>4</v>
       </c>
-      <c r="G13">
+      <c r="G15">
         <v>14.45</v>
       </c>
-      <c r="H13">
+      <c r="H15">
         <v>2.4318488622628007</v>
       </c>
-      <c r="I13">
+      <c r="I15">
         <v>17.850000000000001</v>
       </c>
-      <c r="J13">
+      <c r="J15">
         <v>2.333928495524709</v>
       </c>
-      <c r="K13">
+      <c r="K15">
         <v>31.6</v>
       </c>
-      <c r="L13">
+      <c r="L15">
         <v>3.7475918193480466</v>
       </c>
-      <c r="M13">
+      <c r="M15">
         <v>21.3</v>
       </c>
-      <c r="N13">
+      <c r="N15">
         <v>1.4072124621322282</v>
       </c>
-      <c r="O13">
+      <c r="O15">
         <v>6.95</v>
       </c>
-      <c r="P13">
+      <c r="P15">
         <v>1.8840624612853705</v>
       </c>
     </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="C14" t="s">
+    <row r="16" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="C16" t="s">
         <v>2</v>
       </c>
-      <c r="F14" t="s">
+      <c r="F16" t="s">
         <v>22</v>
       </c>
-      <c r="G14">
+      <c r="G16">
         <v>11.5</v>
       </c>
-      <c r="H14">
+      <c r="H16">
         <v>2</v>
       </c>
-      <c r="I14">
+      <c r="I16">
         <v>16.375</v>
       </c>
-      <c r="J14">
+      <c r="J16">
         <v>1.685018016012207</v>
       </c>
-      <c r="K14">
+      <c r="K16">
         <v>29.0625</v>
       </c>
-      <c r="L14">
+      <c r="L16">
         <v>2.2903134532822609</v>
       </c>
-      <c r="M14">
+      <c r="M16">
         <v>18.979166666666668</v>
       </c>
-      <c r="N14">
+      <c r="N16">
         <v>0.56650908172997527</v>
       </c>
-      <c r="O14">
+      <c r="O16">
         <v>7.5416666666666661</v>
       </c>
-      <c r="P14">
+      <c r="P16">
         <v>1.8317092373405619</v>
       </c>
     </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A15" t="s">
+    <row r="17" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="B16" t="s">
+    <row r="18" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="B18" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="17" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="C17" t="s">
+    <row r="19" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="C19" t="s">
         <v>4</v>
       </c>
-      <c r="G17">
+      <c r="G19">
         <v>12.357142857142858</v>
       </c>
-      <c r="H17">
+      <c r="H19">
         <v>1.5197117521174255</v>
       </c>
-      <c r="I17">
+      <c r="I19">
         <v>16.428571428571427</v>
       </c>
-      <c r="J17">
+      <c r="J19">
         <v>1.3363062095621221</v>
       </c>
-      <c r="K17">
+      <c r="K19">
         <v>32.785714285714285</v>
       </c>
-      <c r="L17">
+      <c r="L19">
         <v>2.4976179127511156</v>
       </c>
-      <c r="M17">
+      <c r="M19">
         <v>20.523809523809526</v>
       </c>
-      <c r="N17">
+      <c r="N19">
         <v>1.5348681069786112</v>
       </c>
-      <c r="O17">
+      <c r="O19">
         <v>8.1666666666666679</v>
       </c>
-      <c r="P17">
+      <c r="P19">
         <v>0.98130676292531094</v>
       </c>
     </row>
-    <row r="18" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="C18" t="s">
+    <row r="20" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="C20" t="s">
         <v>69</v>
       </c>
-      <c r="F18" t="s">
+      <c r="F20" t="s">
         <v>22</v>
       </c>
-      <c r="G18">
+      <c r="G20">
         <v>9.9166666666666661</v>
       </c>
-      <c r="H18">
+      <c r="H20">
         <v>2.3540744819709238</v>
       </c>
-      <c r="I18">
+      <c r="I20">
         <v>14.083333333333334</v>
       </c>
-      <c r="J18">
+      <c r="J20">
         <v>2.1075261959621407</v>
       </c>
-      <c r="K18">
+      <c r="K20">
         <v>25.75</v>
       </c>
-      <c r="L18">
+      <c r="L20">
         <v>4.5798471590217948</v>
       </c>
-      <c r="M18">
+      <c r="M20">
         <v>16.583333333333332</v>
       </c>
-      <c r="N18">
+      <c r="N20">
         <v>1.4013882006385272</v>
       </c>
-      <c r="O18">
+      <c r="O20">
         <v>6.75</v>
       </c>
-      <c r="P18">
+      <c r="P20">
         <v>2.7381055900425419</v>
       </c>
     </row>
-    <row r="19" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="C19" t="s">
+    <row r="21" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="C21" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="21" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="D21" t="s">
+    <row r="23" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="D23" t="s">
         <v>69</v>
       </c>
-      <c r="G21">
+      <c r="G23">
         <v>10.45</v>
       </c>
-      <c r="H21">
+      <c r="H23">
         <v>2.4432446550528732</v>
       </c>
-      <c r="I21">
+      <c r="I23">
         <v>16.05</v>
       </c>
-      <c r="J21">
+      <c r="J23">
         <v>2.4088955514462986</v>
       </c>
-      <c r="K21">
+      <c r="K23">
         <v>27.05</v>
       </c>
-      <c r="L21">
+      <c r="L23">
         <v>4.0514057916837869</v>
       </c>
-      <c r="M21">
+      <c r="M23">
         <v>17.850000000000001</v>
       </c>
-      <c r="N21">
+      <c r="N23">
         <v>1.8214259777966804</v>
       </c>
-      <c r="O21">
+      <c r="O23">
         <v>7.4</v>
       </c>
-      <c r="P21">
+      <c r="P23">
         <v>2.4434341346495017</v>
       </c>
     </row>
-    <row r="22" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="E22" t="s">
+    <row r="24" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="E24" t="s">
         <v>75</v>
       </c>
-      <c r="G22">
+      <c r="G24">
         <v>13</v>
       </c>
-      <c r="H22">
+      <c r="H24">
         <v>2.1213203435596424</v>
       </c>
-      <c r="I22">
+      <c r="I24">
         <v>20</v>
       </c>
-      <c r="J22">
+      <c r="J24">
         <v>0.70710678118654757</v>
       </c>
-      <c r="K22">
+      <c r="K24">
         <v>26.25</v>
       </c>
-      <c r="L22">
+      <c r="L24">
         <v>3.8890872965260113</v>
       </c>
-      <c r="M22">
+      <c r="M24">
         <v>19.75</v>
       </c>
-      <c r="N22">
+      <c r="N24">
         <v>0.35355339059327379</v>
       </c>
-      <c r="O22">
+      <c r="O24">
         <v>6.75</v>
       </c>
-      <c r="P22">
+      <c r="P24">
         <v>2.4748737341529163</v>
       </c>
     </row>
-    <row r="23" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="D23" t="s">
+    <row r="25" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="D25" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="24" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="E24" t="s">
+    <row r="26" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="E26" t="s">
         <v>69</v>
       </c>
-      <c r="G24">
+      <c r="G26">
         <v>8.625</v>
       </c>
-      <c r="H24">
+      <c r="H26">
         <v>1.7017148213885114</v>
       </c>
-      <c r="I24">
+      <c r="I26">
         <v>15.875</v>
       </c>
-      <c r="J24">
+      <c r="J26">
         <v>4.5711960506341587</v>
       </c>
-      <c r="K24">
+      <c r="K26">
         <v>26.75</v>
       </c>
-      <c r="L24">
+      <c r="L26">
         <v>1.5545631755148024</v>
       </c>
-      <c r="M24">
+      <c r="M26">
         <v>17.083333333333332</v>
       </c>
-      <c r="N24">
+      <c r="N26">
         <v>2.0389721448336333</v>
       </c>
-      <c r="O24">
+      <c r="O26">
         <v>8.4583333333333321</v>
       </c>
-      <c r="P24">
+      <c r="P26">
         <v>2.3028766229958482</v>
       </c>
     </row>
-    <row r="25" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="E25" t="s">
+    <row r="27" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="E27" t="s">
         <v>75</v>
       </c>
-      <c r="G25">
+      <c r="G27">
         <v>11.5</v>
       </c>
-      <c r="H25">
+      <c r="H27">
         <v>1.4142135623730951</v>
       </c>
-      <c r="I25">
+      <c r="I27">
         <v>16.25</v>
       </c>
-      <c r="J25">
+      <c r="J27">
         <v>3.1819805153394638</v>
       </c>
-      <c r="K25">
+      <c r="K27">
         <v>30.75</v>
       </c>
-      <c r="L25">
+      <c r="L27">
         <v>3.1819805153394638</v>
       </c>
-      <c r="M25">
+      <c r="M27">
         <v>19.5</v>
       </c>
-      <c r="N25">
+      <c r="N27">
         <v>0.47140452079103001</v>
       </c>
-      <c r="O25">
+      <c r="O27">
         <v>8</v>
       </c>
-      <c r="P25">
+      <c r="P27">
         <v>0.94280904158206502</v>
       </c>
     </row>
-    <row r="27" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B27" t="s">
+    <row r="29" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="B29" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="28" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="C28" t="s">
+    <row r="30" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="C30" t="s">
         <v>4</v>
       </c>
-      <c r="G28">
+      <c r="G30">
         <v>14.333333333333334</v>
       </c>
-      <c r="H28">
+      <c r="H30">
         <v>2.1602468994692834</v>
       </c>
-      <c r="I28">
+      <c r="I30">
         <v>16.166666666666668</v>
       </c>
-      <c r="J28">
+      <c r="J30">
         <v>2.6956755492207609</v>
       </c>
-      <c r="K28">
+      <c r="K30">
         <v>23.916666666666668</v>
       </c>
-      <c r="L28">
+      <c r="L30">
         <v>4.4879468208376423</v>
       </c>
-      <c r="M28">
+      <c r="M30">
         <v>18.138888888888889</v>
       </c>
-      <c r="N28">
+      <c r="N30">
         <v>1.8481722703094376</v>
       </c>
-      <c r="O28">
+      <c r="O30">
         <v>4.2222222222222223</v>
       </c>
-      <c r="P28">
+      <c r="P30">
         <v>1.6113026706042233</v>
       </c>
     </row>
-    <row r="29" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="C29" t="s">
+    <row r="31" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="C31" t="s">
         <v>69</v>
       </c>
-      <c r="F29" t="s">
+      <c r="F31" t="s">
         <v>22</v>
       </c>
-      <c r="G29">
+      <c r="G31">
         <v>10.5</v>
       </c>
-      <c r="H29">
+      <c r="H31">
         <v>2.2638462845343543</v>
       </c>
-      <c r="I29">
+      <c r="I31">
         <v>15.5</v>
       </c>
-      <c r="J29">
+      <c r="J31">
         <v>3.0207614933986431</v>
       </c>
-      <c r="K29">
+      <c r="K31">
         <v>17.899999999999999</v>
       </c>
-      <c r="L29">
+      <c r="L31">
         <v>2.8591956910991616</v>
       </c>
-      <c r="M29">
+      <c r="M31">
         <v>14.633333333333331</v>
       </c>
-      <c r="N29">
+      <c r="N31">
         <v>1.3091557924436987</v>
       </c>
-      <c r="O29">
+      <c r="O31">
         <v>4.1333333333333329</v>
       </c>
-      <c r="P29">
+      <c r="P31">
         <v>2.3816427570528349</v>
       </c>
     </row>
-    <row r="30" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="C30" t="s">
+    <row r="32" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="C32" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="31" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="D31" t="s">
+    <row r="33" spans="4:16" x14ac:dyDescent="0.3">
+      <c r="D33" t="s">
         <v>69</v>
       </c>
-      <c r="F31" t="s">
+      <c r="F33" t="s">
         <v>75</v>
       </c>
-      <c r="G31">
+      <c r="G33">
         <v>12.25</v>
       </c>
-      <c r="H31">
+      <c r="H33">
         <v>2.4748737341529163</v>
       </c>
-      <c r="I31">
+      <c r="I33">
         <v>16.75</v>
       </c>
-      <c r="J31">
+      <c r="J33">
         <v>1.7677669529663689</v>
       </c>
-      <c r="K31">
+      <c r="K33">
         <v>25.25</v>
       </c>
-      <c r="L31">
+      <c r="L33">
         <v>0.35355339059327379</v>
       </c>
-      <c r="M31">
+      <c r="M33">
         <v>18.083333333333336</v>
       </c>
-      <c r="N31">
+      <c r="N33">
         <v>1.5320646925708539</v>
       </c>
-      <c r="O31">
+      <c r="O33">
         <v>5.8333333333333339</v>
       </c>
-      <c r="P31">
+      <c r="P33">
         <v>0.94280904158206169</v>
       </c>
     </row>
-    <row r="32" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="D32" t="s">
+    <row r="34" spans="4:16" x14ac:dyDescent="0.3">
+      <c r="D34" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="33" spans="5:16" x14ac:dyDescent="0.3">
-      <c r="E33" t="s">
+    <row r="35" spans="4:16" x14ac:dyDescent="0.3">
+      <c r="E35" t="s">
         <v>69</v>
       </c>
-      <c r="G33">
+      <c r="G35">
         <v>11.5</v>
       </c>
-      <c r="H33">
+      <c r="H35">
         <v>3.2787192621510002</v>
       </c>
-      <c r="I33">
+      <c r="I35">
         <v>13.833333333333334</v>
       </c>
-      <c r="J33">
+      <c r="J35">
         <v>1.4433756729740645</v>
       </c>
-      <c r="K33">
+      <c r="K35">
         <v>24.666666666666668</v>
       </c>
-      <c r="L33">
+      <c r="L35">
         <v>2.9297326385411577</v>
       </c>
-      <c r="M33">
+      <c r="M35">
         <v>16.666666666666668</v>
       </c>
-      <c r="N33">
+      <c r="N35">
         <v>1.5898986690282426</v>
       </c>
-      <c r="O33">
+      <c r="O35">
         <v>5.166666666666667</v>
       </c>
-      <c r="P33">
+      <c r="P35">
         <v>1.9649710204252651</v>
       </c>
     </row>
-    <row r="34" spans="5:16" x14ac:dyDescent="0.3">
-      <c r="F34" t="s">
+    <row r="36" spans="4:16" x14ac:dyDescent="0.3">
+      <c r="F36" t="s">
         <v>75</v>
       </c>
-      <c r="G34">
+      <c r="G36">
         <v>9.1666666666666661</v>
       </c>
-      <c r="H34">
+      <c r="H36">
         <v>1.1547005383792495</v>
       </c>
-      <c r="I34">
+      <c r="I36">
         <v>16</v>
       </c>
-      <c r="J34">
+      <c r="J36">
         <v>1.8027756377319946</v>
       </c>
-      <c r="K34">
+      <c r="K36">
         <v>25.833333333333332</v>
       </c>
-      <c r="L34">
+      <c r="L36">
         <v>3.7527767497325724</v>
       </c>
-      <c r="M34">
+      <c r="M36">
         <v>17</v>
       </c>
-      <c r="N34">
+      <c r="N36">
         <v>0.60092521257733233</v>
       </c>
-      <c r="O34">
+      <c r="O36">
         <v>7.833333333333333</v>
       </c>
-      <c r="P34">
+      <c r="P36">
         <v>1.6414763002993502</v>
       </c>
     </row>
@@ -1391,6 +1463,492 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{25FCA91D-5E11-4BE7-9F8B-616A902FA88F}">
+  <dimension ref="A2:AF9"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="2" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>56</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>36</v>
+      </c>
+      <c r="R2" t="s">
+        <v>37</v>
+      </c>
+      <c r="S2" t="s">
+        <v>38</v>
+      </c>
+      <c r="T2" t="s">
+        <v>17</v>
+      </c>
+      <c r="U2" t="s">
+        <v>19</v>
+      </c>
+      <c r="V2" t="s">
+        <v>16</v>
+      </c>
+      <c r="W2" t="s">
+        <v>6</v>
+      </c>
+      <c r="X2" t="s">
+        <v>50</v>
+      </c>
+      <c r="Y2" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z2" t="s">
+        <v>51</v>
+      </c>
+      <c r="AA2" t="s">
+        <v>10</v>
+      </c>
+      <c r="AB2" t="s">
+        <v>52</v>
+      </c>
+      <c r="AC2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD2" t="s">
+        <v>18</v>
+      </c>
+      <c r="AE2" t="s">
+        <v>20</v>
+      </c>
+      <c r="AF2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="3" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F3" t="s">
+        <v>68</v>
+      </c>
+      <c r="K3" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="4" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B4">
+        <v>86</v>
+      </c>
+      <c r="C4">
+        <v>14</v>
+      </c>
+      <c r="D4">
+        <v>14</v>
+      </c>
+      <c r="E4">
+        <v>86</v>
+      </c>
+      <c r="G4">
+        <v>95</v>
+      </c>
+      <c r="H4">
+        <v>5</v>
+      </c>
+      <c r="I4">
+        <v>22</v>
+      </c>
+      <c r="J4">
+        <v>78</v>
+      </c>
+      <c r="L4">
+        <v>86</v>
+      </c>
+      <c r="M4">
+        <v>14</v>
+      </c>
+      <c r="N4">
+        <v>22</v>
+      </c>
+      <c r="O4">
+        <v>78</v>
+      </c>
+      <c r="Q4">
+        <f>AVERAGE(C4:D4)</f>
+        <v>14</v>
+      </c>
+      <c r="R4">
+        <f>AVERAGE(H4:I4)</f>
+        <v>13.5</v>
+      </c>
+      <c r="S4">
+        <f>AVERAGE(M4:N4)</f>
+        <v>18</v>
+      </c>
+      <c r="T4">
+        <f>AVERAGE(Q4:S4)</f>
+        <v>15.166666666666666</v>
+      </c>
+      <c r="U4">
+        <f>MIN(Q4:S4)</f>
+        <v>13.5</v>
+      </c>
+      <c r="V4">
+        <f>T4-U4</f>
+        <v>1.6666666666666661</v>
+      </c>
+      <c r="W4">
+        <f>AVERAGE(Q4:Q10)</f>
+        <v>9.9166666666666661</v>
+      </c>
+      <c r="X4">
+        <f>_xlfn.STDEV.S(Q4:Q10)</f>
+        <v>2.3540744819709238</v>
+      </c>
+      <c r="Y4">
+        <f>AVERAGE(R4:R10)</f>
+        <v>14.083333333333334</v>
+      </c>
+      <c r="Z4">
+        <f>_xlfn.STDEV.S(R4:R10)</f>
+        <v>2.1075261959621407</v>
+      </c>
+      <c r="AA4">
+        <f>AVERAGE(S4:S10)</f>
+        <v>25.75</v>
+      </c>
+      <c r="AB4">
+        <f>_xlfn.STDEV.S(S4:S10)</f>
+        <v>4.5798471590217948</v>
+      </c>
+      <c r="AC4">
+        <f>AVERAGE(T4:T10)</f>
+        <v>16.583333333333332</v>
+      </c>
+      <c r="AD4">
+        <f>_xlfn.STDEV.S(T4:T10)</f>
+        <v>1.4013882006385272</v>
+      </c>
+      <c r="AE4">
+        <f>AVERAGE(V4:V10)</f>
+        <v>6.75</v>
+      </c>
+      <c r="AF4">
+        <f>_xlfn.STDEV.S(V4:V10)</f>
+        <v>2.7381055900425419</v>
+      </c>
+    </row>
+    <row r="5" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B5">
+        <v>94</v>
+      </c>
+      <c r="C5">
+        <v>6</v>
+      </c>
+      <c r="D5">
+        <v>8</v>
+      </c>
+      <c r="E5">
+        <v>92</v>
+      </c>
+      <c r="G5">
+        <v>97</v>
+      </c>
+      <c r="H5">
+        <v>3</v>
+      </c>
+      <c r="I5">
+        <v>20</v>
+      </c>
+      <c r="J5">
+        <v>80</v>
+      </c>
+      <c r="L5">
+        <v>84</v>
+      </c>
+      <c r="M5">
+        <v>16</v>
+      </c>
+      <c r="N5">
+        <v>46</v>
+      </c>
+      <c r="O5">
+        <v>54</v>
+      </c>
+      <c r="Q5">
+        <f t="shared" ref="Q5:Q9" si="0">AVERAGE(C5:D5)</f>
+        <v>7</v>
+      </c>
+      <c r="R5">
+        <f t="shared" ref="R5:R9" si="1">AVERAGE(H5:I5)</f>
+        <v>11.5</v>
+      </c>
+      <c r="S5">
+        <f t="shared" ref="S5:S9" si="2">AVERAGE(M5:N5)</f>
+        <v>31</v>
+      </c>
+      <c r="T5">
+        <f t="shared" ref="T5:T9" si="3">AVERAGE(Q5:S5)</f>
+        <v>16.5</v>
+      </c>
+      <c r="U5">
+        <f t="shared" ref="U5:U9" si="4">MIN(Q5:S5)</f>
+        <v>7</v>
+      </c>
+      <c r="V5">
+        <f t="shared" ref="V5:V9" si="5">T5-U5</f>
+        <v>9.5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B6">
+        <v>90</v>
+      </c>
+      <c r="C6">
+        <v>10</v>
+      </c>
+      <c r="D6">
+        <v>11</v>
+      </c>
+      <c r="E6">
+        <v>89</v>
+      </c>
+      <c r="G6">
+        <v>96</v>
+      </c>
+      <c r="H6">
+        <v>4</v>
+      </c>
+      <c r="I6">
+        <v>26</v>
+      </c>
+      <c r="J6">
+        <v>74</v>
+      </c>
+      <c r="L6">
+        <v>79</v>
+      </c>
+      <c r="M6">
+        <v>21</v>
+      </c>
+      <c r="N6">
+        <v>35</v>
+      </c>
+      <c r="O6">
+        <v>65</v>
+      </c>
+      <c r="Q6">
+        <f t="shared" si="0"/>
+        <v>10.5</v>
+      </c>
+      <c r="R6">
+        <f t="shared" si="1"/>
+        <v>15</v>
+      </c>
+      <c r="S6">
+        <f t="shared" si="2"/>
+        <v>28</v>
+      </c>
+      <c r="T6">
+        <f t="shared" si="3"/>
+        <v>17.833333333333332</v>
+      </c>
+      <c r="U6">
+        <f t="shared" si="4"/>
+        <v>10.5</v>
+      </c>
+      <c r="V6">
+        <f t="shared" si="5"/>
+        <v>7.3333333333333321</v>
+      </c>
+    </row>
+    <row r="7" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B7">
+        <v>87</v>
+      </c>
+      <c r="C7">
+        <v>13</v>
+      </c>
+      <c r="D7">
+        <v>4</v>
+      </c>
+      <c r="E7">
+        <v>96</v>
+      </c>
+      <c r="G7">
+        <v>92</v>
+      </c>
+      <c r="H7">
+        <v>8</v>
+      </c>
+      <c r="I7">
+        <v>17</v>
+      </c>
+      <c r="J7">
+        <v>83</v>
+      </c>
+      <c r="L7">
+        <v>87</v>
+      </c>
+      <c r="M7">
+        <v>13</v>
+      </c>
+      <c r="N7">
+        <v>33</v>
+      </c>
+      <c r="O7">
+        <v>67</v>
+      </c>
+      <c r="Q7">
+        <f t="shared" si="0"/>
+        <v>8.5</v>
+      </c>
+      <c r="R7">
+        <f t="shared" si="1"/>
+        <v>12.5</v>
+      </c>
+      <c r="S7">
+        <f t="shared" si="2"/>
+        <v>23</v>
+      </c>
+      <c r="T7">
+        <f t="shared" si="3"/>
+        <v>14.666666666666666</v>
+      </c>
+      <c r="U7">
+        <f t="shared" si="4"/>
+        <v>8.5</v>
+      </c>
+      <c r="V7">
+        <f t="shared" si="5"/>
+        <v>6.1666666666666661</v>
+      </c>
+    </row>
+    <row r="8" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B8">
+        <v>89</v>
+      </c>
+      <c r="C8">
+        <v>11</v>
+      </c>
+      <c r="D8">
+        <v>9</v>
+      </c>
+      <c r="E8">
+        <v>91</v>
+      </c>
+      <c r="G8">
+        <v>96</v>
+      </c>
+      <c r="H8">
+        <v>4</v>
+      </c>
+      <c r="I8">
+        <v>25</v>
+      </c>
+      <c r="J8">
+        <v>75</v>
+      </c>
+      <c r="L8">
+        <v>80</v>
+      </c>
+      <c r="M8">
+        <v>20</v>
+      </c>
+      <c r="N8">
+        <v>35</v>
+      </c>
+      <c r="O8">
+        <v>65</v>
+      </c>
+      <c r="Q8">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="R8">
+        <f t="shared" si="1"/>
+        <v>14.5</v>
+      </c>
+      <c r="S8">
+        <f t="shared" si="2"/>
+        <v>27.5</v>
+      </c>
+      <c r="T8">
+        <f t="shared" si="3"/>
+        <v>17.333333333333332</v>
+      </c>
+      <c r="U8">
+        <f t="shared" si="4"/>
+        <v>10</v>
+      </c>
+      <c r="V8">
+        <f t="shared" si="5"/>
+        <v>7.3333333333333321</v>
+      </c>
+    </row>
+    <row r="9" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B9">
+        <v>95</v>
+      </c>
+      <c r="C9">
+        <v>5</v>
+      </c>
+      <c r="D9">
+        <v>14</v>
+      </c>
+      <c r="E9">
+        <v>86</v>
+      </c>
+      <c r="G9">
+        <v>96</v>
+      </c>
+      <c r="H9">
+        <v>4</v>
+      </c>
+      <c r="I9">
+        <v>31</v>
+      </c>
+      <c r="J9">
+        <v>69</v>
+      </c>
+      <c r="L9">
+        <v>82</v>
+      </c>
+      <c r="M9">
+        <v>18</v>
+      </c>
+      <c r="N9">
+        <v>36</v>
+      </c>
+      <c r="O9">
+        <v>64</v>
+      </c>
+      <c r="Q9">
+        <f t="shared" si="0"/>
+        <v>9.5</v>
+      </c>
+      <c r="R9">
+        <f t="shared" si="1"/>
+        <v>17.5</v>
+      </c>
+      <c r="S9">
+        <f t="shared" si="2"/>
+        <v>27</v>
+      </c>
+      <c r="T9">
+        <f t="shared" si="3"/>
+        <v>18</v>
+      </c>
+      <c r="U9">
+        <f t="shared" si="4"/>
+        <v>9.5</v>
+      </c>
+      <c r="V9">
+        <f t="shared" si="5"/>
+        <v>8.5</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8328B926-3ADF-46D7-8F68-CEFFC1D24F6E}">
   <dimension ref="A2:AF10"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -1941,7 +2499,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{84CA6F53-9387-444E-890F-DCD3D83EC80C}">
   <dimension ref="A1:AN99"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -4644,7 +5202,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2C39A647-64D8-47BC-AD52-3FB80D45AD9F}">
   <dimension ref="A1:AG11"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -5376,7 +5934,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F319F6D0-ABAC-48C6-A867-062B0035D0C5}">
   <dimension ref="A1:AF12"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -6093,7 +6651,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{76F82D8A-1A23-4CF3-9872-DA5B576CDAF9}">
   <dimension ref="A1:AR14"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -7032,7 +7590,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8214124B-224B-4F9B-B528-181D112DB9C5}">
   <dimension ref="A1:AR14"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -7972,7 +8530,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{03D9506E-E2C3-4105-A101-2ED902EAE848}">
   <dimension ref="A1:AR109"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -8447,29 +9005,29 @@
       <c r="AH12" t="s">
         <v>22</v>
       </c>
-      <c r="AI12">
+      <c r="AI12" t="e">
         <f>AVERAGE(Q16:Q24)</f>
-        <v>12.333333333333334</v>
-      </c>
-      <c r="AJ12">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AJ12" t="e">
         <f>_xlfn.STDEV.S(Q16:Q24)</f>
-        <v>3.5118845842842474</v>
-      </c>
-      <c r="AK12">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AK12" t="e">
         <f>AVERAGE(R16:R24)</f>
-        <v>17.166666666666668</v>
-      </c>
-      <c r="AL12">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AL12" t="e">
         <f>_xlfn.STDEV.S(R16:R24)</f>
-        <v>4.8562674281111535</v>
-      </c>
-      <c r="AM12">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AM12" t="e">
         <f>AVERAGE(S16:S24)</f>
-        <v>24.666666666666668</v>
-      </c>
-      <c r="AN12">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AN12" t="e">
         <f>_xlfn.STDEV.S(S16:S24)</f>
-        <v>3.1754264805429475</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="AO12">
         <v>20.537037037037035</v>
@@ -8613,7 +9171,7 @@
         <v>4.8562674281111535</v>
       </c>
       <c r="AA16">
-        <f>AVERAGE(S16:S19)</f>
+        <f>AVERAGE(S16:S18)</f>
         <v>24.666666666666668</v>
       </c>
       <c r="AB16">
@@ -8621,19 +9179,19 @@
         <v>3.1754264805429475</v>
       </c>
       <c r="AC16">
-        <f>AVERAGE(T16:T24)</f>
+        <f>AVERAGE(T16:T18)</f>
         <v>18.055555555555557</v>
       </c>
       <c r="AD16">
-        <f>_xlfn.STDEV.S(T16:T24)</f>
+        <f>_xlfn.STDEV.S(T16:T18)</f>
         <v>3.1284240500668949</v>
       </c>
       <c r="AE16">
-        <f>AVERAGE(V16:V24)</f>
+        <f>AVERAGE(V16:V18)</f>
         <v>5.7222222222222223</v>
       </c>
       <c r="AF16">
-        <f>_xlfn.STDEV.S(V16:V24)</f>
+        <f>_xlfn.STDEV.S(V16:V18)</f>
         <v>1.4174834246859023</v>
       </c>
     </row>
@@ -8761,6 +9319,225 @@
         <v>4.3333333333333321</v>
       </c>
     </row>
+    <row r="19" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="Q19" t="e">
+        <f t="shared" ref="Q19:Q22" si="6">AVERAGE(C19,D19)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="R19" t="e">
+        <f t="shared" ref="R19:R22" si="7">AVERAGE(H19:I19)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="S19" t="e">
+        <f t="shared" ref="S19:S22" si="8">AVERAGE(M19,N19)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T19" t="e">
+        <f t="shared" ref="T19:T22" si="9">AVERAGE(Q19:S19)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U19" t="e">
+        <f t="shared" ref="U19:U22" si="10">MIN(Q19:S19)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="V19" t="e">
+        <f t="shared" ref="V19:V22" si="11">(T19-U19)</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="20" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>75</v>
+      </c>
+      <c r="Q20" t="e">
+        <f t="shared" si="6"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="R20" t="e">
+        <f t="shared" si="7"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="S20" t="e">
+        <f t="shared" si="8"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T20" t="e">
+        <f t="shared" si="9"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U20" t="e">
+        <f t="shared" si="10"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="V20" t="e">
+        <f t="shared" si="11"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="21" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B21">
+        <v>87</v>
+      </c>
+      <c r="C21">
+        <v>13</v>
+      </c>
+      <c r="D21">
+        <v>14</v>
+      </c>
+      <c r="E21">
+        <v>86</v>
+      </c>
+      <c r="G21">
+        <v>97</v>
+      </c>
+      <c r="H21">
+        <v>3</v>
+      </c>
+      <c r="I21">
+        <v>30</v>
+      </c>
+      <c r="J21">
+        <v>70</v>
+      </c>
+      <c r="L21">
+        <v>90</v>
+      </c>
+      <c r="M21">
+        <v>10</v>
+      </c>
+      <c r="N21">
+        <v>62</v>
+      </c>
+      <c r="O21">
+        <v>38</v>
+      </c>
+      <c r="Q21">
+        <f t="shared" si="6"/>
+        <v>13.5</v>
+      </c>
+      <c r="R21">
+        <f t="shared" si="7"/>
+        <v>16.5</v>
+      </c>
+      <c r="S21">
+        <f t="shared" si="8"/>
+        <v>36</v>
+      </c>
+      <c r="T21">
+        <f t="shared" si="9"/>
+        <v>22</v>
+      </c>
+      <c r="U21">
+        <f t="shared" si="10"/>
+        <v>13.5</v>
+      </c>
+      <c r="V21">
+        <f t="shared" si="11"/>
+        <v>8.5</v>
+      </c>
+      <c r="W21">
+        <f>AVERAGE(Q21:Q23)</f>
+        <v>12.5</v>
+      </c>
+      <c r="X21">
+        <f>_xlfn.STDEV.S(Q21:Q23)</f>
+        <v>1.4142135623730951</v>
+      </c>
+      <c r="Y21">
+        <f>AVERAGE(R21:R23)</f>
+        <v>16.5</v>
+      </c>
+      <c r="Z21">
+        <f>_xlfn.STDEV.S(R21:R23)</f>
+        <v>0</v>
+      </c>
+      <c r="AA21">
+        <f>AVERAGE(S21:S23)</f>
+        <v>34</v>
+      </c>
+      <c r="AB21">
+        <f>_xlfn.STDEV.S(S21:S23)</f>
+        <v>2.8284271247461903</v>
+      </c>
+      <c r="AC21">
+        <f>AVERAGE(T21:T23)</f>
+        <v>21</v>
+      </c>
+      <c r="AD21">
+        <f>_xlfn.STDEV.S(T21:T23)</f>
+        <v>1.4142135623730951</v>
+      </c>
+      <c r="AE21">
+        <f>AVERAGE(V21:V23)</f>
+        <v>8.5</v>
+      </c>
+      <c r="AF21">
+        <f>_xlfn.STDEV.S(V21:V23)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B22">
+        <v>88</v>
+      </c>
+      <c r="C22">
+        <v>12</v>
+      </c>
+      <c r="D22">
+        <v>11</v>
+      </c>
+      <c r="E22">
+        <v>89</v>
+      </c>
+      <c r="G22">
+        <v>93</v>
+      </c>
+      <c r="H22">
+        <v>7</v>
+      </c>
+      <c r="I22">
+        <v>26</v>
+      </c>
+      <c r="J22">
+        <v>74</v>
+      </c>
+      <c r="L22">
+        <v>77</v>
+      </c>
+      <c r="M22">
+        <v>23</v>
+      </c>
+      <c r="N22">
+        <v>41</v>
+      </c>
+      <c r="O22">
+        <v>59</v>
+      </c>
+      <c r="Q22">
+        <f t="shared" si="6"/>
+        <v>11.5</v>
+      </c>
+      <c r="R22">
+        <f t="shared" si="7"/>
+        <v>16.5</v>
+      </c>
+      <c r="S22">
+        <f t="shared" si="8"/>
+        <v>32</v>
+      </c>
+      <c r="T22">
+        <f t="shared" si="9"/>
+        <v>20</v>
+      </c>
+      <c r="U22">
+        <f t="shared" si="10"/>
+        <v>11.5</v>
+      </c>
+      <c r="V22">
+        <f t="shared" si="11"/>
+        <v>8.5</v>
+      </c>
+    </row>
     <row r="26" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>27</v>
@@ -9621,53 +10398,53 @@
     </row>
     <row r="68" spans="1:32" x14ac:dyDescent="0.3">
       <c r="Q68" t="e">
-        <f t="shared" ref="Q68:Q109" si="6">AVERAGE(C68,D68)</f>
+        <f t="shared" ref="Q68:Q109" si="12">AVERAGE(C68,D68)</f>
         <v>#DIV/0!</v>
       </c>
       <c r="R68" t="e">
-        <f t="shared" ref="R68:R109" si="7">AVERAGE(H68:I68)</f>
+        <f t="shared" ref="R68:R109" si="13">AVERAGE(H68:I68)</f>
         <v>#DIV/0!</v>
       </c>
       <c r="S68" t="e">
-        <f t="shared" ref="S68:S109" si="8">AVERAGE(M68,N68)</f>
+        <f t="shared" ref="S68:S109" si="14">AVERAGE(M68,N68)</f>
         <v>#DIV/0!</v>
       </c>
       <c r="T68" t="e">
-        <f t="shared" ref="T68:T109" si="9">AVERAGE(Q68:S68)</f>
+        <f t="shared" ref="T68:T109" si="15">AVERAGE(Q68:S68)</f>
         <v>#DIV/0!</v>
       </c>
       <c r="U68" t="e">
-        <f t="shared" ref="U68:U109" si="10">MIN(Q68:S68)</f>
+        <f t="shared" ref="U68:U109" si="16">MIN(Q68:S68)</f>
         <v>#DIV/0!</v>
       </c>
       <c r="V68" t="e">
-        <f t="shared" ref="V68:V109" si="11">(1/3)*(T68-U68)</f>
+        <f t="shared" ref="V68:V109" si="17">(1/3)*(T68-U68)</f>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="69" spans="1:32" x14ac:dyDescent="0.3">
       <c r="Q69" t="e">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v>#DIV/0!</v>
       </c>
       <c r="R69" t="e">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v>#DIV/0!</v>
       </c>
       <c r="S69" t="e">
-        <f t="shared" si="8"/>
+        <f t="shared" si="14"/>
         <v>#DIV/0!</v>
       </c>
       <c r="T69" t="e">
-        <f t="shared" si="9"/>
+        <f t="shared" si="15"/>
         <v>#DIV/0!</v>
       </c>
       <c r="U69" t="e">
-        <f t="shared" si="10"/>
+        <f t="shared" si="16"/>
         <v>#DIV/0!</v>
       </c>
       <c r="V69" t="e">
-        <f t="shared" si="11"/>
+        <f t="shared" si="17"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -9683,27 +10460,27 @@
     </row>
     <row r="73" spans="1:32" x14ac:dyDescent="0.3">
       <c r="Q73" t="e">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v>#DIV/0!</v>
       </c>
       <c r="R73" t="e">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v>#DIV/0!</v>
       </c>
       <c r="S73" t="e">
-        <f t="shared" si="8"/>
+        <f t="shared" si="14"/>
         <v>#DIV/0!</v>
       </c>
       <c r="T73" t="e">
-        <f t="shared" si="9"/>
+        <f t="shared" si="15"/>
         <v>#DIV/0!</v>
       </c>
       <c r="U73" t="e">
-        <f t="shared" si="10"/>
+        <f t="shared" si="16"/>
         <v>#DIV/0!</v>
       </c>
       <c r="V73" t="e">
-        <f t="shared" si="11"/>
+        <f t="shared" si="17"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AC73" t="e">
@@ -9725,53 +10502,53 @@
     </row>
     <row r="74" spans="1:32" x14ac:dyDescent="0.3">
       <c r="Q74" t="e">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v>#DIV/0!</v>
       </c>
       <c r="R74" t="e">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v>#DIV/0!</v>
       </c>
       <c r="S74" t="e">
-        <f t="shared" si="8"/>
+        <f t="shared" si="14"/>
         <v>#DIV/0!</v>
       </c>
       <c r="T74" t="e">
-        <f t="shared" si="9"/>
+        <f t="shared" si="15"/>
         <v>#DIV/0!</v>
       </c>
       <c r="U74" t="e">
-        <f t="shared" si="10"/>
+        <f t="shared" si="16"/>
         <v>#DIV/0!</v>
       </c>
       <c r="V74" t="e">
-        <f t="shared" si="11"/>
+        <f t="shared" si="17"/>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="75" spans="1:32" x14ac:dyDescent="0.3">
       <c r="Q75" t="e">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v>#DIV/0!</v>
       </c>
       <c r="R75" t="e">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v>#DIV/0!</v>
       </c>
       <c r="S75" t="e">
-        <f t="shared" si="8"/>
+        <f t="shared" si="14"/>
         <v>#DIV/0!</v>
       </c>
       <c r="T75" t="e">
-        <f t="shared" si="9"/>
+        <f t="shared" si="15"/>
         <v>#DIV/0!</v>
       </c>
       <c r="U75" t="e">
-        <f t="shared" si="10"/>
+        <f t="shared" si="16"/>
         <v>#DIV/0!</v>
       </c>
       <c r="V75" t="e">
-        <f t="shared" si="11"/>
+        <f t="shared" si="17"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -9787,27 +10564,27 @@
     </row>
     <row r="79" spans="1:32" x14ac:dyDescent="0.3">
       <c r="Q79" t="e">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v>#DIV/0!</v>
       </c>
       <c r="R79" t="e">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v>#DIV/0!</v>
       </c>
       <c r="S79" t="e">
-        <f t="shared" si="8"/>
+        <f t="shared" si="14"/>
         <v>#DIV/0!</v>
       </c>
       <c r="T79" t="e">
-        <f t="shared" si="9"/>
+        <f t="shared" si="15"/>
         <v>#DIV/0!</v>
       </c>
       <c r="U79" t="e">
-        <f t="shared" si="10"/>
+        <f t="shared" si="16"/>
         <v>#DIV/0!</v>
       </c>
       <c r="V79" t="e">
-        <f t="shared" si="11"/>
+        <f t="shared" si="17"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AC79" t="e">
@@ -9829,235 +10606,235 @@
     </row>
     <row r="80" spans="1:32" x14ac:dyDescent="0.3">
       <c r="Q80" t="e">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v>#DIV/0!</v>
       </c>
       <c r="R80" t="e">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v>#DIV/0!</v>
       </c>
       <c r="S80" t="e">
-        <f t="shared" si="8"/>
+        <f t="shared" si="14"/>
         <v>#DIV/0!</v>
       </c>
       <c r="T80" t="e">
-        <f t="shared" si="9"/>
+        <f t="shared" si="15"/>
         <v>#DIV/0!</v>
       </c>
       <c r="U80" t="e">
-        <f t="shared" si="10"/>
+        <f t="shared" si="16"/>
         <v>#DIV/0!</v>
       </c>
       <c r="V80" t="e">
-        <f t="shared" si="11"/>
+        <f t="shared" si="17"/>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="81" spans="1:32" x14ac:dyDescent="0.3">
       <c r="Q81" t="e">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v>#DIV/0!</v>
       </c>
       <c r="R81" t="e">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v>#DIV/0!</v>
       </c>
       <c r="S81" t="e">
-        <f t="shared" si="8"/>
+        <f t="shared" si="14"/>
         <v>#DIV/0!</v>
       </c>
       <c r="T81" t="e">
-        <f t="shared" si="9"/>
+        <f t="shared" si="15"/>
         <v>#DIV/0!</v>
       </c>
       <c r="U81" t="e">
-        <f t="shared" si="10"/>
+        <f t="shared" si="16"/>
         <v>#DIV/0!</v>
       </c>
       <c r="V81" t="e">
-        <f t="shared" si="11"/>
+        <f t="shared" si="17"/>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="82" spans="1:32" x14ac:dyDescent="0.3">
       <c r="Q82" t="e">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v>#DIV/0!</v>
       </c>
       <c r="R82" t="e">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v>#DIV/0!</v>
       </c>
       <c r="S82" t="e">
-        <f t="shared" si="8"/>
+        <f t="shared" si="14"/>
         <v>#DIV/0!</v>
       </c>
       <c r="T82" t="e">
-        <f t="shared" si="9"/>
+        <f t="shared" si="15"/>
         <v>#DIV/0!</v>
       </c>
       <c r="U82" t="e">
-        <f t="shared" si="10"/>
+        <f t="shared" si="16"/>
         <v>#DIV/0!</v>
       </c>
       <c r="V82" t="e">
-        <f t="shared" si="11"/>
+        <f t="shared" si="17"/>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="83" spans="1:32" x14ac:dyDescent="0.3">
       <c r="Q83" t="e">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v>#DIV/0!</v>
       </c>
       <c r="R83" t="e">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v>#DIV/0!</v>
       </c>
       <c r="S83" t="e">
-        <f t="shared" si="8"/>
+        <f t="shared" si="14"/>
         <v>#DIV/0!</v>
       </c>
       <c r="T83" t="e">
-        <f t="shared" si="9"/>
+        <f t="shared" si="15"/>
         <v>#DIV/0!</v>
       </c>
       <c r="U83" t="e">
-        <f t="shared" si="10"/>
+        <f t="shared" si="16"/>
         <v>#DIV/0!</v>
       </c>
       <c r="V83" t="e">
-        <f t="shared" si="11"/>
+        <f t="shared" si="17"/>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="84" spans="1:32" x14ac:dyDescent="0.3">
       <c r="Q84" t="e">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v>#DIV/0!</v>
       </c>
       <c r="R84" t="e">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v>#DIV/0!</v>
       </c>
       <c r="S84" t="e">
-        <f t="shared" si="8"/>
+        <f t="shared" si="14"/>
         <v>#DIV/0!</v>
       </c>
       <c r="T84" t="e">
-        <f t="shared" si="9"/>
+        <f t="shared" si="15"/>
         <v>#DIV/0!</v>
       </c>
       <c r="U84" t="e">
-        <f t="shared" si="10"/>
+        <f t="shared" si="16"/>
         <v>#DIV/0!</v>
       </c>
       <c r="V84" t="e">
-        <f t="shared" si="11"/>
+        <f t="shared" si="17"/>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="85" spans="1:32" x14ac:dyDescent="0.3">
       <c r="Q85" t="e">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v>#DIV/0!</v>
       </c>
       <c r="R85" t="e">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v>#DIV/0!</v>
       </c>
       <c r="S85" t="e">
-        <f t="shared" si="8"/>
+        <f t="shared" si="14"/>
         <v>#DIV/0!</v>
       </c>
       <c r="T85" t="e">
-        <f t="shared" si="9"/>
+        <f t="shared" si="15"/>
         <v>#DIV/0!</v>
       </c>
       <c r="U85" t="e">
-        <f t="shared" si="10"/>
+        <f t="shared" si="16"/>
         <v>#DIV/0!</v>
       </c>
       <c r="V85" t="e">
-        <f t="shared" si="11"/>
+        <f t="shared" si="17"/>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="86" spans="1:32" x14ac:dyDescent="0.3">
       <c r="Q86" t="e">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v>#DIV/0!</v>
       </c>
       <c r="R86" t="e">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v>#DIV/0!</v>
       </c>
       <c r="S86" t="e">
-        <f t="shared" si="8"/>
+        <f t="shared" si="14"/>
         <v>#DIV/0!</v>
       </c>
       <c r="T86" t="e">
-        <f t="shared" si="9"/>
+        <f t="shared" si="15"/>
         <v>#DIV/0!</v>
       </c>
       <c r="U86" t="e">
-        <f t="shared" si="10"/>
+        <f t="shared" si="16"/>
         <v>#DIV/0!</v>
       </c>
       <c r="V86" t="e">
-        <f t="shared" si="11"/>
+        <f t="shared" si="17"/>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="87" spans="1:32" x14ac:dyDescent="0.3">
       <c r="Q87" t="e">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v>#DIV/0!</v>
       </c>
       <c r="R87" t="e">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v>#DIV/0!</v>
       </c>
       <c r="S87" t="e">
-        <f t="shared" si="8"/>
+        <f t="shared" si="14"/>
         <v>#DIV/0!</v>
       </c>
       <c r="T87" t="e">
-        <f t="shared" si="9"/>
+        <f t="shared" si="15"/>
         <v>#DIV/0!</v>
       </c>
       <c r="U87" t="e">
-        <f t="shared" si="10"/>
+        <f t="shared" si="16"/>
         <v>#DIV/0!</v>
       </c>
       <c r="V87" t="e">
-        <f t="shared" si="11"/>
+        <f t="shared" si="17"/>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="88" spans="1:32" x14ac:dyDescent="0.3">
       <c r="Q88" t="e">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v>#DIV/0!</v>
       </c>
       <c r="R88" t="e">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v>#DIV/0!</v>
       </c>
       <c r="S88" t="e">
-        <f t="shared" si="8"/>
+        <f t="shared" si="14"/>
         <v>#DIV/0!</v>
       </c>
       <c r="T88" t="e">
-        <f t="shared" si="9"/>
+        <f t="shared" si="15"/>
         <v>#DIV/0!</v>
       </c>
       <c r="U88" t="e">
-        <f t="shared" si="10"/>
+        <f t="shared" si="16"/>
         <v>#DIV/0!</v>
       </c>
       <c r="V88" t="e">
-        <f t="shared" si="11"/>
+        <f t="shared" si="17"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -10073,27 +10850,27 @@
     </row>
     <row r="92" spans="1:32" x14ac:dyDescent="0.3">
       <c r="Q92" t="e">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v>#DIV/0!</v>
       </c>
       <c r="R92" t="e">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v>#DIV/0!</v>
       </c>
       <c r="S92" t="e">
-        <f t="shared" si="8"/>
+        <f t="shared" si="14"/>
         <v>#DIV/0!</v>
       </c>
       <c r="T92" t="e">
-        <f t="shared" si="9"/>
+        <f t="shared" si="15"/>
         <v>#DIV/0!</v>
       </c>
       <c r="U92" t="e">
-        <f t="shared" si="10"/>
+        <f t="shared" si="16"/>
         <v>#DIV/0!</v>
       </c>
       <c r="V92" t="e">
-        <f t="shared" si="11"/>
+        <f t="shared" si="17"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AC92" t="e">
@@ -10115,131 +10892,131 @@
     </row>
     <row r="93" spans="1:32" x14ac:dyDescent="0.3">
       <c r="Q93" t="e">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v>#DIV/0!</v>
       </c>
       <c r="R93" t="e">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v>#DIV/0!</v>
       </c>
       <c r="S93" t="e">
-        <f t="shared" si="8"/>
+        <f t="shared" si="14"/>
         <v>#DIV/0!</v>
       </c>
       <c r="T93" t="e">
-        <f t="shared" si="9"/>
+        <f t="shared" si="15"/>
         <v>#DIV/0!</v>
       </c>
       <c r="U93" t="e">
-        <f t="shared" si="10"/>
+        <f t="shared" si="16"/>
         <v>#DIV/0!</v>
       </c>
       <c r="V93" t="e">
-        <f t="shared" si="11"/>
+        <f t="shared" si="17"/>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="94" spans="1:32" x14ac:dyDescent="0.3">
       <c r="Q94" t="e">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v>#DIV/0!</v>
       </c>
       <c r="R94" t="e">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v>#DIV/0!</v>
       </c>
       <c r="S94" t="e">
-        <f t="shared" si="8"/>
+        <f t="shared" si="14"/>
         <v>#DIV/0!</v>
       </c>
       <c r="T94" t="e">
-        <f t="shared" si="9"/>
+        <f t="shared" si="15"/>
         <v>#DIV/0!</v>
       </c>
       <c r="U94" t="e">
-        <f t="shared" si="10"/>
+        <f t="shared" si="16"/>
         <v>#DIV/0!</v>
       </c>
       <c r="V94" t="e">
-        <f t="shared" si="11"/>
+        <f t="shared" si="17"/>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="95" spans="1:32" x14ac:dyDescent="0.3">
       <c r="Q95" t="e">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v>#DIV/0!</v>
       </c>
       <c r="R95" t="e">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v>#DIV/0!</v>
       </c>
       <c r="S95" t="e">
-        <f t="shared" si="8"/>
+        <f t="shared" si="14"/>
         <v>#DIV/0!</v>
       </c>
       <c r="T95" t="e">
-        <f t="shared" si="9"/>
+        <f t="shared" si="15"/>
         <v>#DIV/0!</v>
       </c>
       <c r="U95" t="e">
-        <f t="shared" si="10"/>
+        <f t="shared" si="16"/>
         <v>#DIV/0!</v>
       </c>
       <c r="V95" t="e">
-        <f t="shared" si="11"/>
+        <f t="shared" si="17"/>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="96" spans="1:32" x14ac:dyDescent="0.3">
       <c r="Q96" t="e">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v>#DIV/0!</v>
       </c>
       <c r="R96" t="e">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v>#DIV/0!</v>
       </c>
       <c r="S96" t="e">
-        <f t="shared" si="8"/>
+        <f t="shared" si="14"/>
         <v>#DIV/0!</v>
       </c>
       <c r="T96" t="e">
-        <f t="shared" si="9"/>
+        <f t="shared" si="15"/>
         <v>#DIV/0!</v>
       </c>
       <c r="U96" t="e">
-        <f t="shared" si="10"/>
+        <f t="shared" si="16"/>
         <v>#DIV/0!</v>
       </c>
       <c r="V96" t="e">
-        <f t="shared" si="11"/>
+        <f t="shared" si="17"/>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="97" spans="1:32" x14ac:dyDescent="0.3">
       <c r="Q97" t="e">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v>#DIV/0!</v>
       </c>
       <c r="R97" t="e">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v>#DIV/0!</v>
       </c>
       <c r="S97" t="e">
-        <f t="shared" si="8"/>
+        <f t="shared" si="14"/>
         <v>#DIV/0!</v>
       </c>
       <c r="T97" t="e">
-        <f t="shared" si="9"/>
+        <f t="shared" si="15"/>
         <v>#DIV/0!</v>
       </c>
       <c r="U97" t="e">
-        <f t="shared" si="10"/>
+        <f t="shared" si="16"/>
         <v>#DIV/0!</v>
       </c>
       <c r="V97" t="e">
-        <f t="shared" si="11"/>
+        <f t="shared" si="17"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -10255,27 +11032,27 @@
     </row>
     <row r="101" spans="1:32" x14ac:dyDescent="0.3">
       <c r="Q101" t="e">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v>#DIV/0!</v>
       </c>
       <c r="R101" t="e">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v>#DIV/0!</v>
       </c>
       <c r="S101" t="e">
-        <f t="shared" si="8"/>
+        <f t="shared" si="14"/>
         <v>#DIV/0!</v>
       </c>
       <c r="T101" t="e">
-        <f t="shared" si="9"/>
+        <f t="shared" si="15"/>
         <v>#DIV/0!</v>
       </c>
       <c r="U101" t="e">
-        <f t="shared" si="10"/>
+        <f t="shared" si="16"/>
         <v>#DIV/0!</v>
       </c>
       <c r="V101" t="e">
-        <f t="shared" si="11"/>
+        <f t="shared" si="17"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AC101" t="e">
@@ -10297,209 +11074,209 @@
     </row>
     <row r="102" spans="1:32" x14ac:dyDescent="0.3">
       <c r="Q102" t="e">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v>#DIV/0!</v>
       </c>
       <c r="R102" t="e">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v>#DIV/0!</v>
       </c>
       <c r="S102" t="e">
-        <f t="shared" si="8"/>
+        <f t="shared" si="14"/>
         <v>#DIV/0!</v>
       </c>
       <c r="T102" t="e">
-        <f t="shared" si="9"/>
+        <f t="shared" si="15"/>
         <v>#DIV/0!</v>
       </c>
       <c r="U102" t="e">
-        <f t="shared" si="10"/>
+        <f t="shared" si="16"/>
         <v>#DIV/0!</v>
       </c>
       <c r="V102" t="e">
-        <f t="shared" si="11"/>
+        <f t="shared" si="17"/>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="103" spans="1:32" x14ac:dyDescent="0.3">
       <c r="Q103" t="e">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v>#DIV/0!</v>
       </c>
       <c r="R103" t="e">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v>#DIV/0!</v>
       </c>
       <c r="S103" t="e">
-        <f t="shared" si="8"/>
+        <f t="shared" si="14"/>
         <v>#DIV/0!</v>
       </c>
       <c r="T103" t="e">
-        <f t="shared" si="9"/>
+        <f t="shared" si="15"/>
         <v>#DIV/0!</v>
       </c>
       <c r="U103" t="e">
-        <f t="shared" si="10"/>
+        <f t="shared" si="16"/>
         <v>#DIV/0!</v>
       </c>
       <c r="V103" t="e">
-        <f t="shared" si="11"/>
+        <f t="shared" si="17"/>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="104" spans="1:32" x14ac:dyDescent="0.3">
       <c r="Q104" t="e">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v>#DIV/0!</v>
       </c>
       <c r="R104" t="e">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v>#DIV/0!</v>
       </c>
       <c r="S104" t="e">
-        <f t="shared" si="8"/>
+        <f t="shared" si="14"/>
         <v>#DIV/0!</v>
       </c>
       <c r="T104" t="e">
-        <f t="shared" si="9"/>
+        <f t="shared" si="15"/>
         <v>#DIV/0!</v>
       </c>
       <c r="U104" t="e">
-        <f t="shared" si="10"/>
+        <f t="shared" si="16"/>
         <v>#DIV/0!</v>
       </c>
       <c r="V104" t="e">
-        <f t="shared" si="11"/>
+        <f t="shared" si="17"/>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="105" spans="1:32" x14ac:dyDescent="0.3">
       <c r="Q105" t="e">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v>#DIV/0!</v>
       </c>
       <c r="R105" t="e">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v>#DIV/0!</v>
       </c>
       <c r="S105" t="e">
-        <f t="shared" si="8"/>
+        <f t="shared" si="14"/>
         <v>#DIV/0!</v>
       </c>
       <c r="T105" t="e">
-        <f t="shared" si="9"/>
+        <f t="shared" si="15"/>
         <v>#DIV/0!</v>
       </c>
       <c r="U105" t="e">
-        <f t="shared" si="10"/>
+        <f t="shared" si="16"/>
         <v>#DIV/0!</v>
       </c>
       <c r="V105" t="e">
-        <f t="shared" si="11"/>
+        <f t="shared" si="17"/>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="106" spans="1:32" x14ac:dyDescent="0.3">
       <c r="Q106" t="e">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v>#DIV/0!</v>
       </c>
       <c r="R106" t="e">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v>#DIV/0!</v>
       </c>
       <c r="S106" t="e">
-        <f t="shared" si="8"/>
+        <f t="shared" si="14"/>
         <v>#DIV/0!</v>
       </c>
       <c r="T106" t="e">
-        <f t="shared" si="9"/>
+        <f t="shared" si="15"/>
         <v>#DIV/0!</v>
       </c>
       <c r="U106" t="e">
-        <f t="shared" si="10"/>
+        <f t="shared" si="16"/>
         <v>#DIV/0!</v>
       </c>
       <c r="V106" t="e">
-        <f t="shared" si="11"/>
+        <f t="shared" si="17"/>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="107" spans="1:32" x14ac:dyDescent="0.3">
       <c r="Q107" t="e">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v>#DIV/0!</v>
       </c>
       <c r="R107" t="e">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v>#DIV/0!</v>
       </c>
       <c r="S107" t="e">
-        <f t="shared" si="8"/>
+        <f t="shared" si="14"/>
         <v>#DIV/0!</v>
       </c>
       <c r="T107" t="e">
-        <f t="shared" si="9"/>
+        <f t="shared" si="15"/>
         <v>#DIV/0!</v>
       </c>
       <c r="U107" t="e">
-        <f t="shared" si="10"/>
+        <f t="shared" si="16"/>
         <v>#DIV/0!</v>
       </c>
       <c r="V107" t="e">
-        <f t="shared" si="11"/>
+        <f t="shared" si="17"/>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="108" spans="1:32" x14ac:dyDescent="0.3">
       <c r="Q108" t="e">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v>#DIV/0!</v>
       </c>
       <c r="R108" t="e">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v>#DIV/0!</v>
       </c>
       <c r="S108" t="e">
-        <f t="shared" si="8"/>
+        <f t="shared" si="14"/>
         <v>#DIV/0!</v>
       </c>
       <c r="T108" t="e">
-        <f t="shared" si="9"/>
+        <f t="shared" si="15"/>
         <v>#DIV/0!</v>
       </c>
       <c r="U108" t="e">
-        <f t="shared" si="10"/>
+        <f t="shared" si="16"/>
         <v>#DIV/0!</v>
       </c>
       <c r="V108" t="e">
-        <f t="shared" si="11"/>
+        <f t="shared" si="17"/>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="109" spans="1:32" x14ac:dyDescent="0.3">
       <c r="Q109" t="e">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v>#DIV/0!</v>
       </c>
       <c r="R109" t="e">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v>#DIV/0!</v>
       </c>
       <c r="S109" t="e">
-        <f t="shared" si="8"/>
+        <f t="shared" si="14"/>
         <v>#DIV/0!</v>
       </c>
       <c r="T109" t="e">
-        <f t="shared" si="9"/>
+        <f t="shared" si="15"/>
         <v>#DIV/0!</v>
       </c>
       <c r="U109" t="e">
-        <f t="shared" si="10"/>
+        <f t="shared" si="16"/>
         <v>#DIV/0!</v>
       </c>
       <c r="V109" t="e">
-        <f t="shared" si="11"/>
+        <f t="shared" si="17"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -10508,7 +11285,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D80BAE23-A740-4698-B840-F018E78CD098}">
   <dimension ref="A1:AF5"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -10810,6 +11587,292 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E9419A36-EEBE-474C-8BAC-DB0715B87887}">
+  <dimension ref="B2:AF5"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="2" spans="2:32" x14ac:dyDescent="0.3">
+      <c r="Q2" t="s">
+        <v>13</v>
+      </c>
+      <c r="R2" t="s">
+        <v>14</v>
+      </c>
+      <c r="S2" t="s">
+        <v>15</v>
+      </c>
+      <c r="T2" t="s">
+        <v>17</v>
+      </c>
+      <c r="U2" t="s">
+        <v>57</v>
+      </c>
+      <c r="V2" t="s">
+        <v>50</v>
+      </c>
+      <c r="W2" t="s">
+        <v>58</v>
+      </c>
+      <c r="X2" t="s">
+        <v>51</v>
+      </c>
+      <c r="Y2" t="s">
+        <v>59</v>
+      </c>
+      <c r="Z2" t="s">
+        <v>52</v>
+      </c>
+      <c r="AA2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB2" t="s">
+        <v>18</v>
+      </c>
+      <c r="AC2" t="s">
+        <v>19</v>
+      </c>
+      <c r="AD2" t="s">
+        <v>16</v>
+      </c>
+      <c r="AE2" t="s">
+        <v>20</v>
+      </c>
+      <c r="AF2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="3" spans="2:32" x14ac:dyDescent="0.3">
+      <c r="B3">
+        <v>93</v>
+      </c>
+      <c r="C3">
+        <v>7</v>
+      </c>
+      <c r="D3">
+        <v>21</v>
+      </c>
+      <c r="E3">
+        <v>79</v>
+      </c>
+      <c r="G3">
+        <v>98</v>
+      </c>
+      <c r="H3">
+        <v>2</v>
+      </c>
+      <c r="I3">
+        <v>33</v>
+      </c>
+      <c r="J3">
+        <v>67</v>
+      </c>
+      <c r="L3">
+        <v>88</v>
+      </c>
+      <c r="M3">
+        <v>12</v>
+      </c>
+      <c r="N3">
+        <v>39</v>
+      </c>
+      <c r="O3">
+        <v>61</v>
+      </c>
+      <c r="Q3">
+        <f>AVERAGE(C3:D3)</f>
+        <v>14</v>
+      </c>
+      <c r="R3">
+        <f>AVERAGE(H3:I3)</f>
+        <v>17.5</v>
+      </c>
+      <c r="S3">
+        <f>AVERAGE(M3:N3)</f>
+        <v>25.5</v>
+      </c>
+      <c r="T3">
+        <f>AVERAGE(Q3:S3)</f>
+        <v>19</v>
+      </c>
+      <c r="U3">
+        <f>AVERAGE(Q3:Q19)</f>
+        <v>12.666666666666666</v>
+      </c>
+      <c r="V3">
+        <f>_xlfn.STDEV.S(Q3:Q19)</f>
+        <v>1.2583057392117918</v>
+      </c>
+      <c r="W3">
+        <f>AVERAGE(R3:R19)</f>
+        <v>18</v>
+      </c>
+      <c r="X3">
+        <f>_xlfn.STDEV.S(R3:R19)</f>
+        <v>3.2787192621510002</v>
+      </c>
+      <c r="Y3">
+        <f>AVERAGE(S3:S19)</f>
+        <v>30.833333333333332</v>
+      </c>
+      <c r="Z3">
+        <f>_xlfn.STDEV.S(S3:S19)</f>
+        <v>5.251983752196236</v>
+      </c>
+      <c r="AA3">
+        <f>AVERAGE(T3:T19)</f>
+        <v>20.5</v>
+      </c>
+      <c r="AB3">
+        <f>_xlfn.STDEV.S(T3:T19)</f>
+        <v>1.3642254619787419</v>
+      </c>
+      <c r="AC3">
+        <f>MIN(Q3:S3)</f>
+        <v>14</v>
+      </c>
+      <c r="AD3">
+        <f>T3-AC3</f>
+        <v>5</v>
+      </c>
+      <c r="AE3">
+        <f>AVERAGE(AD3:AD19)</f>
+        <v>7.833333333333333</v>
+      </c>
+      <c r="AF3">
+        <f>_xlfn.STDEV.S(AD3:AD19)</f>
+        <v>2.4551533104427046</v>
+      </c>
+    </row>
+    <row r="4" spans="2:32" x14ac:dyDescent="0.3">
+      <c r="B4">
+        <v>89</v>
+      </c>
+      <c r="C4">
+        <v>11</v>
+      </c>
+      <c r="D4">
+        <v>12</v>
+      </c>
+      <c r="E4">
+        <v>88</v>
+      </c>
+      <c r="G4">
+        <v>97</v>
+      </c>
+      <c r="H4">
+        <v>3</v>
+      </c>
+      <c r="I4">
+        <v>27</v>
+      </c>
+      <c r="J4">
+        <v>73</v>
+      </c>
+      <c r="L4">
+        <v>81</v>
+      </c>
+      <c r="M4">
+        <v>19</v>
+      </c>
+      <c r="N4">
+        <v>53</v>
+      </c>
+      <c r="O4">
+        <v>47</v>
+      </c>
+      <c r="Q4">
+        <f t="shared" ref="Q4:Q5" si="0">AVERAGE(C4:D4)</f>
+        <v>11.5</v>
+      </c>
+      <c r="R4">
+        <f t="shared" ref="R4:R5" si="1">AVERAGE(H4:I4)</f>
+        <v>15</v>
+      </c>
+      <c r="S4">
+        <f t="shared" ref="S4:S5" si="2">AVERAGE(M4:N4)</f>
+        <v>36</v>
+      </c>
+      <c r="T4">
+        <f t="shared" ref="T4:T5" si="3">AVERAGE(Q4:S4)</f>
+        <v>20.833333333333332</v>
+      </c>
+      <c r="AC4">
+        <f t="shared" ref="AC4:AC5" si="4">MIN(Q4:S4)</f>
+        <v>11.5</v>
+      </c>
+      <c r="AD4">
+        <f t="shared" ref="AD4:AD5" si="5">T4-AC4</f>
+        <v>9.3333333333333321</v>
+      </c>
+    </row>
+    <row r="5" spans="2:32" x14ac:dyDescent="0.3">
+      <c r="B5">
+        <v>90</v>
+      </c>
+      <c r="C5">
+        <v>10</v>
+      </c>
+      <c r="D5">
+        <v>15</v>
+      </c>
+      <c r="E5">
+        <v>85</v>
+      </c>
+      <c r="G5">
+        <v>97</v>
+      </c>
+      <c r="H5">
+        <v>3</v>
+      </c>
+      <c r="I5">
+        <v>40</v>
+      </c>
+      <c r="J5">
+        <v>60</v>
+      </c>
+      <c r="L5">
+        <v>83</v>
+      </c>
+      <c r="M5">
+        <v>17</v>
+      </c>
+      <c r="N5">
+        <v>45</v>
+      </c>
+      <c r="O5">
+        <v>55</v>
+      </c>
+      <c r="Q5">
+        <f t="shared" si="0"/>
+        <v>12.5</v>
+      </c>
+      <c r="R5">
+        <f t="shared" si="1"/>
+        <v>21.5</v>
+      </c>
+      <c r="S5">
+        <f t="shared" si="2"/>
+        <v>31</v>
+      </c>
+      <c r="T5">
+        <f t="shared" si="3"/>
+        <v>21.666666666666668</v>
+      </c>
+      <c r="AC5">
+        <f t="shared" si="4"/>
+        <v>12.5</v>
+      </c>
+      <c r="AD5">
+        <f t="shared" si="5"/>
+        <v>9.1666666666666679</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4D0CE18A-8B26-4E93-B497-B59E55EFEC0E}">
   <dimension ref="A2:AF19"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -11340,7 +12403,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2E557A7D-364E-47EE-A0F3-0D888512E587}">
   <dimension ref="A2:AF6"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -11640,7 +12703,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C1B67D71-588A-4985-8ACA-35F7A9B1AF58}">
   <dimension ref="A2:AF6"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -11940,7 +13003,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8A4C68C5-0EAB-4233-98F5-D346BC512EB4}">
   <dimension ref="A2:AF21"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -12712,19 +13775,19 @@
         <v>49</v>
       </c>
       <c r="Q20">
-        <f t="shared" ref="Q14:Q21" si="6">AVERAGE(C20:D20)</f>
+        <f t="shared" ref="Q20:Q21" si="6">AVERAGE(C20:D20)</f>
         <v>11.5</v>
       </c>
       <c r="R20">
-        <f t="shared" ref="R14:R21" si="7">AVERAGE(H20:I20)</f>
+        <f t="shared" ref="R20:R21" si="7">AVERAGE(H20:I20)</f>
         <v>19.5</v>
       </c>
       <c r="S20">
-        <f t="shared" ref="S14:S21" si="8">AVERAGE(M20:N20)</f>
+        <f t="shared" ref="S20:S21" si="8">AVERAGE(M20:N20)</f>
         <v>29</v>
       </c>
       <c r="T20">
-        <f t="shared" ref="T14:T21" si="9">AVERAGE(Q20:S20)</f>
+        <f t="shared" ref="T20:T21" si="9">AVERAGE(Q20:S20)</f>
         <v>20</v>
       </c>
       <c r="U20">
@@ -12760,11 +13823,11 @@
         <v>0.35355339059327379</v>
       </c>
       <c r="AC20">
-        <f t="shared" ref="AC14:AC21" si="10">MIN(Q20:S20)</f>
+        <f t="shared" ref="AC20:AC21" si="10">MIN(Q20:S20)</f>
         <v>11.5</v>
       </c>
       <c r="AD20">
-        <f t="shared" ref="AD14:AD21" si="11">T20-AC20</f>
+        <f t="shared" ref="AD20:AD21" si="11">T20-AC20</f>
         <v>8.5</v>
       </c>
       <c r="AE20">
@@ -12844,7 +13907,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0843B137-6F6F-47C7-80DB-2FF2B4BCD957}">
   <dimension ref="A2:AF5"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -13007,7 +14070,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A366D673-4552-407C-AD95-3B60150A1024}">
   <dimension ref="A2:AF13"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -13469,27 +14532,27 @@
         <v>62</v>
       </c>
       <c r="Q12">
-        <f t="shared" ref="Q9:Q13" si="6">AVERAGE(C12:D12)</f>
+        <f t="shared" ref="Q12:Q13" si="6">AVERAGE(C12:D12)</f>
         <v>14</v>
       </c>
       <c r="R12">
-        <f t="shared" ref="R9:R13" si="7">AVERAGE(H12:I12)</f>
+        <f t="shared" ref="R12:R13" si="7">AVERAGE(H12:I12)</f>
         <v>18</v>
       </c>
       <c r="S12">
-        <f t="shared" ref="S9:S13" si="8">AVERAGE(M12:N12)</f>
+        <f t="shared" ref="S12:S13" si="8">AVERAGE(M12:N12)</f>
         <v>25.5</v>
       </c>
       <c r="T12">
-        <f t="shared" ref="T9:T13" si="9">AVERAGE(Q12:S12)</f>
+        <f t="shared" ref="T12:T13" si="9">AVERAGE(Q12:S12)</f>
         <v>19.166666666666668</v>
       </c>
       <c r="U12">
-        <f t="shared" ref="U9:U13" si="10">MIN(Q12:S12)</f>
+        <f t="shared" ref="U12:U13" si="10">MIN(Q12:S12)</f>
         <v>14</v>
       </c>
       <c r="V12">
-        <f t="shared" ref="V9:V13" si="11">T12-U12</f>
+        <f t="shared" ref="V12:V13" si="11">T12-U12</f>
         <v>5.1666666666666679</v>
       </c>
       <c r="W12">
@@ -13600,7 +14663,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EEC9CF4A-6F3D-4BA0-B506-17E3C93FB04B}">
   <dimension ref="A2:AF9"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -14084,490 +15147,4 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{25FCA91D-5E11-4BE7-9F8B-616A902FA88F}">
-  <dimension ref="A2:AF9"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <sheetData>
-    <row r="2" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>56</v>
-      </c>
-      <c r="Q2" t="s">
-        <v>36</v>
-      </c>
-      <c r="R2" t="s">
-        <v>37</v>
-      </c>
-      <c r="S2" t="s">
-        <v>38</v>
-      </c>
-      <c r="T2" t="s">
-        <v>17</v>
-      </c>
-      <c r="U2" t="s">
-        <v>19</v>
-      </c>
-      <c r="V2" t="s">
-        <v>16</v>
-      </c>
-      <c r="W2" t="s">
-        <v>6</v>
-      </c>
-      <c r="X2" t="s">
-        <v>50</v>
-      </c>
-      <c r="Y2" t="s">
-        <v>8</v>
-      </c>
-      <c r="Z2" t="s">
-        <v>51</v>
-      </c>
-      <c r="AA2" t="s">
-        <v>10</v>
-      </c>
-      <c r="AB2" t="s">
-        <v>52</v>
-      </c>
-      <c r="AC2" t="s">
-        <v>1</v>
-      </c>
-      <c r="AD2" t="s">
-        <v>18</v>
-      </c>
-      <c r="AE2" t="s">
-        <v>20</v>
-      </c>
-      <c r="AF2" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="3" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>24</v>
-      </c>
-      <c r="F3" t="s">
-        <v>68</v>
-      </c>
-      <c r="K3" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="4" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="B4">
-        <v>86</v>
-      </c>
-      <c r="C4">
-        <v>14</v>
-      </c>
-      <c r="D4">
-        <v>14</v>
-      </c>
-      <c r="E4">
-        <v>86</v>
-      </c>
-      <c r="G4">
-        <v>95</v>
-      </c>
-      <c r="H4">
-        <v>5</v>
-      </c>
-      <c r="I4">
-        <v>22</v>
-      </c>
-      <c r="J4">
-        <v>78</v>
-      </c>
-      <c r="L4">
-        <v>86</v>
-      </c>
-      <c r="M4">
-        <v>14</v>
-      </c>
-      <c r="N4">
-        <v>22</v>
-      </c>
-      <c r="O4">
-        <v>78</v>
-      </c>
-      <c r="Q4">
-        <f>AVERAGE(C4:D4)</f>
-        <v>14</v>
-      </c>
-      <c r="R4">
-        <f>AVERAGE(H4:I4)</f>
-        <v>13.5</v>
-      </c>
-      <c r="S4">
-        <f>AVERAGE(M4:N4)</f>
-        <v>18</v>
-      </c>
-      <c r="T4">
-        <f>AVERAGE(Q4:S4)</f>
-        <v>15.166666666666666</v>
-      </c>
-      <c r="U4">
-        <f>MIN(Q4:S4)</f>
-        <v>13.5</v>
-      </c>
-      <c r="V4">
-        <f>T4-U4</f>
-        <v>1.6666666666666661</v>
-      </c>
-      <c r="W4">
-        <f>AVERAGE(Q4:Q10)</f>
-        <v>9.9166666666666661</v>
-      </c>
-      <c r="X4">
-        <f>_xlfn.STDEV.S(Q4:Q10)</f>
-        <v>2.3540744819709238</v>
-      </c>
-      <c r="Y4">
-        <f>AVERAGE(R4:R10)</f>
-        <v>14.083333333333334</v>
-      </c>
-      <c r="Z4">
-        <f>_xlfn.STDEV.S(R4:R10)</f>
-        <v>2.1075261959621407</v>
-      </c>
-      <c r="AA4">
-        <f>AVERAGE(S4:S10)</f>
-        <v>25.75</v>
-      </c>
-      <c r="AB4">
-        <f>_xlfn.STDEV.S(S4:S10)</f>
-        <v>4.5798471590217948</v>
-      </c>
-      <c r="AC4">
-        <f>AVERAGE(T4:T10)</f>
-        <v>16.583333333333332</v>
-      </c>
-      <c r="AD4">
-        <f>_xlfn.STDEV.S(T4:T10)</f>
-        <v>1.4013882006385272</v>
-      </c>
-      <c r="AE4">
-        <f>AVERAGE(V4:V10)</f>
-        <v>6.75</v>
-      </c>
-      <c r="AF4">
-        <f>_xlfn.STDEV.S(V4:V10)</f>
-        <v>2.7381055900425419</v>
-      </c>
-    </row>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="B5">
-        <v>94</v>
-      </c>
-      <c r="C5">
-        <v>6</v>
-      </c>
-      <c r="D5">
-        <v>8</v>
-      </c>
-      <c r="E5">
-        <v>92</v>
-      </c>
-      <c r="G5">
-        <v>97</v>
-      </c>
-      <c r="H5">
-        <v>3</v>
-      </c>
-      <c r="I5">
-        <v>20</v>
-      </c>
-      <c r="J5">
-        <v>80</v>
-      </c>
-      <c r="L5">
-        <v>84</v>
-      </c>
-      <c r="M5">
-        <v>16</v>
-      </c>
-      <c r="N5">
-        <v>46</v>
-      </c>
-      <c r="O5">
-        <v>54</v>
-      </c>
-      <c r="Q5">
-        <f t="shared" ref="Q5:Q9" si="0">AVERAGE(C5:D5)</f>
-        <v>7</v>
-      </c>
-      <c r="R5">
-        <f t="shared" ref="R5:R9" si="1">AVERAGE(H5:I5)</f>
-        <v>11.5</v>
-      </c>
-      <c r="S5">
-        <f t="shared" ref="S5:S9" si="2">AVERAGE(M5:N5)</f>
-        <v>31</v>
-      </c>
-      <c r="T5">
-        <f t="shared" ref="T5:T9" si="3">AVERAGE(Q5:S5)</f>
-        <v>16.5</v>
-      </c>
-      <c r="U5">
-        <f t="shared" ref="U5:U9" si="4">MIN(Q5:S5)</f>
-        <v>7</v>
-      </c>
-      <c r="V5">
-        <f t="shared" ref="V5:V9" si="5">T5-U5</f>
-        <v>9.5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="B6">
-        <v>90</v>
-      </c>
-      <c r="C6">
-        <v>10</v>
-      </c>
-      <c r="D6">
-        <v>11</v>
-      </c>
-      <c r="E6">
-        <v>89</v>
-      </c>
-      <c r="G6">
-        <v>96</v>
-      </c>
-      <c r="H6">
-        <v>4</v>
-      </c>
-      <c r="I6">
-        <v>26</v>
-      </c>
-      <c r="J6">
-        <v>74</v>
-      </c>
-      <c r="L6">
-        <v>79</v>
-      </c>
-      <c r="M6">
-        <v>21</v>
-      </c>
-      <c r="N6">
-        <v>35</v>
-      </c>
-      <c r="O6">
-        <v>65</v>
-      </c>
-      <c r="Q6">
-        <f t="shared" si="0"/>
-        <v>10.5</v>
-      </c>
-      <c r="R6">
-        <f t="shared" si="1"/>
-        <v>15</v>
-      </c>
-      <c r="S6">
-        <f t="shared" si="2"/>
-        <v>28</v>
-      </c>
-      <c r="T6">
-        <f t="shared" si="3"/>
-        <v>17.833333333333332</v>
-      </c>
-      <c r="U6">
-        <f t="shared" si="4"/>
-        <v>10.5</v>
-      </c>
-      <c r="V6">
-        <f t="shared" si="5"/>
-        <v>7.3333333333333321</v>
-      </c>
-    </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="B7">
-        <v>87</v>
-      </c>
-      <c r="C7">
-        <v>13</v>
-      </c>
-      <c r="D7">
-        <v>4</v>
-      </c>
-      <c r="E7">
-        <v>96</v>
-      </c>
-      <c r="G7">
-        <v>92</v>
-      </c>
-      <c r="H7">
-        <v>8</v>
-      </c>
-      <c r="I7">
-        <v>17</v>
-      </c>
-      <c r="J7">
-        <v>83</v>
-      </c>
-      <c r="L7">
-        <v>87</v>
-      </c>
-      <c r="M7">
-        <v>13</v>
-      </c>
-      <c r="N7">
-        <v>33</v>
-      </c>
-      <c r="O7">
-        <v>67</v>
-      </c>
-      <c r="Q7">
-        <f t="shared" si="0"/>
-        <v>8.5</v>
-      </c>
-      <c r="R7">
-        <f t="shared" si="1"/>
-        <v>12.5</v>
-      </c>
-      <c r="S7">
-        <f t="shared" si="2"/>
-        <v>23</v>
-      </c>
-      <c r="T7">
-        <f t="shared" si="3"/>
-        <v>14.666666666666666</v>
-      </c>
-      <c r="U7">
-        <f t="shared" si="4"/>
-        <v>8.5</v>
-      </c>
-      <c r="V7">
-        <f t="shared" si="5"/>
-        <v>6.1666666666666661</v>
-      </c>
-    </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="B8">
-        <v>89</v>
-      </c>
-      <c r="C8">
-        <v>11</v>
-      </c>
-      <c r="D8">
-        <v>9</v>
-      </c>
-      <c r="E8">
-        <v>91</v>
-      </c>
-      <c r="G8">
-        <v>96</v>
-      </c>
-      <c r="H8">
-        <v>4</v>
-      </c>
-      <c r="I8">
-        <v>25</v>
-      </c>
-      <c r="J8">
-        <v>75</v>
-      </c>
-      <c r="L8">
-        <v>80</v>
-      </c>
-      <c r="M8">
-        <v>20</v>
-      </c>
-      <c r="N8">
-        <v>35</v>
-      </c>
-      <c r="O8">
-        <v>65</v>
-      </c>
-      <c r="Q8">
-        <f t="shared" si="0"/>
-        <v>10</v>
-      </c>
-      <c r="R8">
-        <f t="shared" si="1"/>
-        <v>14.5</v>
-      </c>
-      <c r="S8">
-        <f t="shared" si="2"/>
-        <v>27.5</v>
-      </c>
-      <c r="T8">
-        <f t="shared" si="3"/>
-        <v>17.333333333333332</v>
-      </c>
-      <c r="U8">
-        <f t="shared" si="4"/>
-        <v>10</v>
-      </c>
-      <c r="V8">
-        <f t="shared" si="5"/>
-        <v>7.3333333333333321</v>
-      </c>
-    </row>
-    <row r="9" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="B9">
-        <v>95</v>
-      </c>
-      <c r="C9">
-        <v>5</v>
-      </c>
-      <c r="D9">
-        <v>14</v>
-      </c>
-      <c r="E9">
-        <v>86</v>
-      </c>
-      <c r="G9">
-        <v>96</v>
-      </c>
-      <c r="H9">
-        <v>4</v>
-      </c>
-      <c r="I9">
-        <v>31</v>
-      </c>
-      <c r="J9">
-        <v>69</v>
-      </c>
-      <c r="L9">
-        <v>82</v>
-      </c>
-      <c r="M9">
-        <v>18</v>
-      </c>
-      <c r="N9">
-        <v>36</v>
-      </c>
-      <c r="O9">
-        <v>64</v>
-      </c>
-      <c r="Q9">
-        <f t="shared" si="0"/>
-        <v>9.5</v>
-      </c>
-      <c r="R9">
-        <f t="shared" si="1"/>
-        <v>17.5</v>
-      </c>
-      <c r="S9">
-        <f t="shared" si="2"/>
-        <v>27</v>
-      </c>
-      <c r="T9">
-        <f t="shared" si="3"/>
-        <v>18</v>
-      </c>
-      <c r="U9">
-        <f t="shared" si="4"/>
-        <v>9.5</v>
-      </c>
-      <c r="V9">
-        <f t="shared" si="5"/>
-        <v>8.5</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>
--- a/DataAnalysis/LC/0.05/Results.xlsx
+++ b/DataAnalysis/LC/0.05/Results.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Utente\Desktop\CultureAwarenessTest\DataAnalysis\LC\0.05\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B26C9456-A234-4B51-BE0C-B29D2B82AF5D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AFAE925B-A7D7-47D6-8A9F-E66DAB51D19C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -53,7 +53,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="514" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="518" uniqueCount="76">
   <si>
     <t>Dati originali</t>
   </si>
@@ -678,6 +678,36 @@
       <c r="P3">
         <v>1.0715167512214481</v>
       </c>
+      <c r="R3">
+        <v>13.666666666666666</v>
+      </c>
+      <c r="S3">
+        <v>2.0816659994661282</v>
+      </c>
+      <c r="T3">
+        <v>17.166666666666668</v>
+      </c>
+      <c r="U3">
+        <v>1.5275252316519465</v>
+      </c>
+      <c r="V3">
+        <v>33</v>
+      </c>
+      <c r="W3">
+        <v>3.1224989991991992</v>
+      </c>
+      <c r="X3">
+        <v>21.277777777777775</v>
+      </c>
+      <c r="Y3">
+        <v>1.9743728493240953</v>
+      </c>
+      <c r="Z3">
+        <v>7.6111111111111107</v>
+      </c>
+      <c r="AA3">
+        <v>1.5122952876462401</v>
+      </c>
     </row>
     <row r="4" spans="1:27" x14ac:dyDescent="0.3">
       <c r="C4" t="s">
@@ -720,34 +750,34 @@
         <v>75</v>
       </c>
       <c r="R4">
-        <v>12.5</v>
+        <v>12.9</v>
       </c>
       <c r="S4">
-        <v>1.4142135623730951</v>
+        <v>1.6733200530681545</v>
       </c>
       <c r="T4">
-        <v>16.5</v>
+        <v>18.399999999999999</v>
       </c>
       <c r="U4">
-        <v>0</v>
+        <v>2.2748626332154678</v>
       </c>
       <c r="V4">
-        <v>34</v>
+        <v>31.3</v>
       </c>
       <c r="W4">
-        <v>2.8284271247461903</v>
+        <v>7.0498226928058303</v>
       </c>
       <c r="X4">
-        <v>21</v>
+        <v>20.866666666666667</v>
       </c>
       <c r="Y4">
-        <v>1.4142135623730951</v>
+        <v>2.7923506624745986</v>
       </c>
       <c r="Z4">
-        <v>8.5</v>
+        <v>7.9666666666666659</v>
       </c>
       <c r="AA4">
-        <v>0</v>
+        <v>1.7215948678155679</v>
       </c>
     </row>
     <row r="5" spans="1:27" x14ac:dyDescent="0.3">
@@ -1027,17 +1057,17 @@
         <v>1.8317092373405619</v>
       </c>
     </row>
-    <row r="17" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="18" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:27" x14ac:dyDescent="0.3">
       <c r="B18" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="19" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:27" x14ac:dyDescent="0.3">
       <c r="C19" t="s">
         <v>4</v>
       </c>
@@ -1071,8 +1101,38 @@
       <c r="P19">
         <v>0.98130676292531094</v>
       </c>
-    </row>
-    <row r="20" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="R19">
+        <v>10.333333333333334</v>
+      </c>
+      <c r="S19">
+        <v>2.7537852736430528</v>
+      </c>
+      <c r="T19">
+        <v>16.833333333333332</v>
+      </c>
+      <c r="U19">
+        <v>2.0207259421636903</v>
+      </c>
+      <c r="V19">
+        <v>32.5</v>
+      </c>
+      <c r="W19">
+        <v>5.634713834792322</v>
+      </c>
+      <c r="X19">
+        <v>19.888888888888889</v>
+      </c>
+      <c r="Y19">
+        <v>2.3353166174426336</v>
+      </c>
+      <c r="Z19">
+        <v>9.5555555555555554</v>
+      </c>
+      <c r="AA19">
+        <v>0.58531409738070839</v>
+      </c>
+    </row>
+    <row r="20" spans="1:27" x14ac:dyDescent="0.3">
       <c r="C20" t="s">
         <v>69</v>
       </c>
@@ -1109,13 +1169,43 @@
       <c r="P20">
         <v>2.7381055900425419</v>
       </c>
-    </row>
-    <row r="21" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="R20">
+        <v>12.285714285714286</v>
+      </c>
+      <c r="S20">
+        <v>2.4470584868562546</v>
+      </c>
+      <c r="T20">
+        <v>15.642857142857142</v>
+      </c>
+      <c r="U20">
+        <v>1.9086270308410567</v>
+      </c>
+      <c r="V20">
+        <v>26.571428571428573</v>
+      </c>
+      <c r="W20">
+        <v>3.3094381626464764</v>
+      </c>
+      <c r="X20">
+        <v>18.166666666666664</v>
+      </c>
+      <c r="Y20">
+        <v>1.1785113019775788</v>
+      </c>
+      <c r="Z20">
+        <v>5.9523809523809508</v>
+      </c>
+      <c r="AA20">
+        <v>2.00396432500008</v>
+      </c>
+    </row>
+    <row r="21" spans="1:27" x14ac:dyDescent="0.3">
       <c r="C21" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="23" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:27" x14ac:dyDescent="0.3">
       <c r="D23" t="s">
         <v>69</v>
       </c>
@@ -1150,7 +1240,7 @@
         <v>2.4434341346495017</v>
       </c>
     </row>
-    <row r="24" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:27" x14ac:dyDescent="0.3">
       <c r="E24" t="s">
         <v>75</v>
       </c>
@@ -1185,12 +1275,12 @@
         <v>2.4748737341529163</v>
       </c>
     </row>
-    <row r="25" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:27" x14ac:dyDescent="0.3">
       <c r="D25" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="26" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:27" x14ac:dyDescent="0.3">
       <c r="E26" t="s">
         <v>69</v>
       </c>
@@ -1225,7 +1315,7 @@
         <v>2.3028766229958482</v>
       </c>
     </row>
-    <row r="27" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:27" x14ac:dyDescent="0.3">
       <c r="E27" t="s">
         <v>75</v>
       </c>
@@ -1260,12 +1350,12 @@
         <v>0.94280904158206502</v>
       </c>
     </row>
-    <row r="29" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:27" x14ac:dyDescent="0.3">
       <c r="B29" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="30" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:27" x14ac:dyDescent="0.3">
       <c r="C30" t="s">
         <v>4</v>
       </c>
@@ -1299,8 +1389,38 @@
       <c r="P30">
         <v>1.6113026706042233</v>
       </c>
-    </row>
-    <row r="31" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="R30">
+        <v>14.5</v>
+      </c>
+      <c r="S30">
+        <v>4.7696960070847281</v>
+      </c>
+      <c r="T30">
+        <v>16.5</v>
+      </c>
+      <c r="U30">
+        <v>5.196152422706632</v>
+      </c>
+      <c r="V30">
+        <v>25.333333333333332</v>
+      </c>
+      <c r="W30">
+        <v>1.5275252316519465</v>
+      </c>
+      <c r="X30">
+        <v>18.777777777777775</v>
+      </c>
+      <c r="Y30">
+        <v>3.4251250315107677</v>
+      </c>
+      <c r="Z30">
+        <v>5.4444444444444438</v>
+      </c>
+      <c r="AA30">
+        <v>0.91792842454768508</v>
+      </c>
+    </row>
+    <row r="31" spans="1:27" x14ac:dyDescent="0.3">
       <c r="C31" t="s">
         <v>69</v>
       </c>
@@ -1337,8 +1457,38 @@
       <c r="P31">
         <v>2.3816427570528349</v>
       </c>
-    </row>
-    <row r="32" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="R31">
+        <v>10.5</v>
+      </c>
+      <c r="S31">
+        <v>2.7838821814150108</v>
+      </c>
+      <c r="T31">
+        <v>15.166666666666666</v>
+      </c>
+      <c r="U31">
+        <v>4.2524502740576891</v>
+      </c>
+      <c r="V31">
+        <v>21.666666666666668</v>
+      </c>
+      <c r="W31">
+        <v>1.2583057392117916</v>
+      </c>
+      <c r="X31">
+        <v>15.777777777777777</v>
+      </c>
+      <c r="Y31">
+        <v>2.2381374531648746</v>
+      </c>
+      <c r="Z31">
+        <v>5.2777777777777777</v>
+      </c>
+      <c r="AA31">
+        <v>1.3877773329774237</v>
+      </c>
+    </row>
+    <row r="32" spans="1:27" x14ac:dyDescent="0.3">
       <c r="C32" t="s">
         <v>53</v>
       </c>
@@ -1464,7 +1614,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{25FCA91D-5E11-4BE7-9F8B-616A902FA88F}">
-  <dimension ref="A2:AF9"/>
+  <dimension ref="A2:AF18"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="2" spans="1:32" x14ac:dyDescent="0.3">
@@ -1941,6 +2091,485 @@
       <c r="V9">
         <f t="shared" si="5"/>
         <v>8.5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="12" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B12">
+        <v>95</v>
+      </c>
+      <c r="C12">
+        <v>5</v>
+      </c>
+      <c r="D12">
+        <v>14</v>
+      </c>
+      <c r="E12">
+        <v>86</v>
+      </c>
+      <c r="G12">
+        <v>95</v>
+      </c>
+      <c r="H12">
+        <v>5</v>
+      </c>
+      <c r="I12">
+        <v>24</v>
+      </c>
+      <c r="J12">
+        <v>76</v>
+      </c>
+      <c r="L12">
+        <v>85</v>
+      </c>
+      <c r="M12">
+        <v>15</v>
+      </c>
+      <c r="N12">
+        <v>42</v>
+      </c>
+      <c r="O12">
+        <v>58</v>
+      </c>
+      <c r="Q12">
+        <f t="shared" ref="Q10:Q18" si="6">AVERAGE(C12:D12)</f>
+        <v>9.5</v>
+      </c>
+      <c r="R12">
+        <f t="shared" ref="R10:R18" si="7">AVERAGE(H12:I12)</f>
+        <v>14.5</v>
+      </c>
+      <c r="S12">
+        <f t="shared" ref="S10:S18" si="8">AVERAGE(M12:N12)</f>
+        <v>28.5</v>
+      </c>
+      <c r="T12">
+        <f t="shared" ref="T10:T18" si="9">AVERAGE(Q12:S12)</f>
+        <v>17.5</v>
+      </c>
+      <c r="U12">
+        <f t="shared" ref="U10:U18" si="10">MIN(Q12:S12)</f>
+        <v>9.5</v>
+      </c>
+      <c r="V12">
+        <f t="shared" ref="V10:V18" si="11">T12-U12</f>
+        <v>8</v>
+      </c>
+      <c r="W12">
+        <f>AVERAGE(Q12:Q18)</f>
+        <v>12.285714285714286</v>
+      </c>
+      <c r="X12">
+        <f>_xlfn.STDEV.S(Q12:Q18)</f>
+        <v>2.4470584868562546</v>
+      </c>
+      <c r="Y12">
+        <f>AVERAGE(R12:R18)</f>
+        <v>15.642857142857142</v>
+      </c>
+      <c r="Z12">
+        <f>_xlfn.STDEV.S(R12:R18)</f>
+        <v>1.9086270308410567</v>
+      </c>
+      <c r="AA12">
+        <f>AVERAGE(S12:S18)</f>
+        <v>26.571428571428573</v>
+      </c>
+      <c r="AB12">
+        <f>_xlfn.STDEV.S(S12:S18)</f>
+        <v>3.3094381626464764</v>
+      </c>
+      <c r="AC12">
+        <f>AVERAGE(T12:T18)</f>
+        <v>18.166666666666664</v>
+      </c>
+      <c r="AD12">
+        <f>_xlfn.STDEV.S(T12:T18)</f>
+        <v>1.1785113019775788</v>
+      </c>
+      <c r="AE12">
+        <f>AVERAGE(V12:V18)</f>
+        <v>5.9523809523809508</v>
+      </c>
+      <c r="AF12">
+        <f>_xlfn.STDEV.S(V12:V18)</f>
+        <v>2.00396432500008</v>
+      </c>
+    </row>
+    <row r="13" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B13">
+        <v>88</v>
+      </c>
+      <c r="C13">
+        <v>12</v>
+      </c>
+      <c r="D13">
+        <v>15</v>
+      </c>
+      <c r="E13">
+        <v>85</v>
+      </c>
+      <c r="G13">
+        <v>98</v>
+      </c>
+      <c r="H13">
+        <v>2</v>
+      </c>
+      <c r="I13">
+        <v>34</v>
+      </c>
+      <c r="J13">
+        <v>66</v>
+      </c>
+      <c r="L13">
+        <v>90</v>
+      </c>
+      <c r="M13">
+        <v>10</v>
+      </c>
+      <c r="N13">
+        <v>33</v>
+      </c>
+      <c r="O13">
+        <v>67</v>
+      </c>
+      <c r="Q13">
+        <f t="shared" si="6"/>
+        <v>13.5</v>
+      </c>
+      <c r="R13">
+        <f t="shared" si="7"/>
+        <v>18</v>
+      </c>
+      <c r="S13">
+        <f t="shared" si="8"/>
+        <v>21.5</v>
+      </c>
+      <c r="T13">
+        <f t="shared" si="9"/>
+        <v>17.666666666666668</v>
+      </c>
+      <c r="U13">
+        <f t="shared" si="10"/>
+        <v>13.5</v>
+      </c>
+      <c r="V13">
+        <f t="shared" si="11"/>
+        <v>4.1666666666666679</v>
+      </c>
+    </row>
+    <row r="14" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B14">
+        <v>94</v>
+      </c>
+      <c r="C14">
+        <v>6</v>
+      </c>
+      <c r="D14">
+        <v>19</v>
+      </c>
+      <c r="E14">
+        <v>81</v>
+      </c>
+      <c r="G14">
+        <v>99</v>
+      </c>
+      <c r="H14">
+        <v>1</v>
+      </c>
+      <c r="I14">
+        <v>33</v>
+      </c>
+      <c r="J14">
+        <v>67</v>
+      </c>
+      <c r="L14">
+        <v>75</v>
+      </c>
+      <c r="M14">
+        <v>25</v>
+      </c>
+      <c r="N14">
+        <v>26</v>
+      </c>
+      <c r="O14">
+        <v>74</v>
+      </c>
+      <c r="Q14">
+        <f t="shared" si="6"/>
+        <v>12.5</v>
+      </c>
+      <c r="R14">
+        <f t="shared" si="7"/>
+        <v>17</v>
+      </c>
+      <c r="S14">
+        <f t="shared" si="8"/>
+        <v>25.5</v>
+      </c>
+      <c r="T14">
+        <f t="shared" si="9"/>
+        <v>18.333333333333332</v>
+      </c>
+      <c r="U14">
+        <f t="shared" si="10"/>
+        <v>12.5</v>
+      </c>
+      <c r="V14">
+        <f t="shared" si="11"/>
+        <v>5.8333333333333321</v>
+      </c>
+    </row>
+    <row r="15" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B15">
+        <v>88</v>
+      </c>
+      <c r="C15">
+        <v>12</v>
+      </c>
+      <c r="D15">
+        <v>18</v>
+      </c>
+      <c r="E15">
+        <v>82</v>
+      </c>
+      <c r="G15">
+        <v>99</v>
+      </c>
+      <c r="H15">
+        <v>1</v>
+      </c>
+      <c r="I15">
+        <v>30</v>
+      </c>
+      <c r="J15">
+        <v>70</v>
+      </c>
+      <c r="L15">
+        <v>86</v>
+      </c>
+      <c r="M15">
+        <v>14</v>
+      </c>
+      <c r="N15">
+        <v>32</v>
+      </c>
+      <c r="O15">
+        <v>68</v>
+      </c>
+      <c r="Q15">
+        <f t="shared" si="6"/>
+        <v>15</v>
+      </c>
+      <c r="R15">
+        <f t="shared" si="7"/>
+        <v>15.5</v>
+      </c>
+      <c r="S15">
+        <f t="shared" si="8"/>
+        <v>23</v>
+      </c>
+      <c r="T15">
+        <f t="shared" si="9"/>
+        <v>17.833333333333332</v>
+      </c>
+      <c r="U15">
+        <f t="shared" si="10"/>
+        <v>15</v>
+      </c>
+      <c r="V15">
+        <f t="shared" si="11"/>
+        <v>2.8333333333333321</v>
+      </c>
+    </row>
+    <row r="16" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B16">
+        <v>91</v>
+      </c>
+      <c r="C16">
+        <v>9</v>
+      </c>
+      <c r="D16">
+        <v>8</v>
+      </c>
+      <c r="E16">
+        <v>92</v>
+      </c>
+      <c r="G16">
+        <v>95</v>
+      </c>
+      <c r="H16">
+        <v>5</v>
+      </c>
+      <c r="I16">
+        <v>21</v>
+      </c>
+      <c r="J16">
+        <v>79</v>
+      </c>
+      <c r="L16">
+        <v>86</v>
+      </c>
+      <c r="M16">
+        <v>14</v>
+      </c>
+      <c r="N16">
+        <v>42</v>
+      </c>
+      <c r="O16">
+        <v>58</v>
+      </c>
+      <c r="Q16">
+        <f t="shared" si="6"/>
+        <v>8.5</v>
+      </c>
+      <c r="R16">
+        <f t="shared" si="7"/>
+        <v>13</v>
+      </c>
+      <c r="S16">
+        <f t="shared" si="8"/>
+        <v>28</v>
+      </c>
+      <c r="T16">
+        <f t="shared" si="9"/>
+        <v>16.5</v>
+      </c>
+      <c r="U16">
+        <f t="shared" si="10"/>
+        <v>8.5</v>
+      </c>
+      <c r="V16">
+        <f t="shared" si="11"/>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="17" spans="2:22" x14ac:dyDescent="0.3">
+      <c r="B17">
+        <v>92</v>
+      </c>
+      <c r="C17">
+        <v>8</v>
+      </c>
+      <c r="D17">
+        <v>17</v>
+      </c>
+      <c r="E17">
+        <v>83</v>
+      </c>
+      <c r="G17">
+        <v>95</v>
+      </c>
+      <c r="H17">
+        <v>5</v>
+      </c>
+      <c r="I17">
+        <v>30</v>
+      </c>
+      <c r="J17">
+        <v>70</v>
+      </c>
+      <c r="L17">
+        <v>89</v>
+      </c>
+      <c r="M17">
+        <v>11</v>
+      </c>
+      <c r="N17">
+        <v>49</v>
+      </c>
+      <c r="O17">
+        <v>51</v>
+      </c>
+      <c r="Q17">
+        <f t="shared" si="6"/>
+        <v>12.5</v>
+      </c>
+      <c r="R17">
+        <f t="shared" si="7"/>
+        <v>17.5</v>
+      </c>
+      <c r="S17">
+        <f t="shared" si="8"/>
+        <v>30</v>
+      </c>
+      <c r="T17">
+        <f t="shared" si="9"/>
+        <v>20</v>
+      </c>
+      <c r="U17">
+        <f t="shared" si="10"/>
+        <v>12.5</v>
+      </c>
+      <c r="V17">
+        <f t="shared" si="11"/>
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="18" spans="2:22" x14ac:dyDescent="0.3">
+      <c r="B18">
+        <v>94</v>
+      </c>
+      <c r="C18">
+        <v>6</v>
+      </c>
+      <c r="D18">
+        <v>23</v>
+      </c>
+      <c r="E18">
+        <v>77</v>
+      </c>
+      <c r="G18">
+        <v>97</v>
+      </c>
+      <c r="H18">
+        <v>3</v>
+      </c>
+      <c r="I18">
+        <v>25</v>
+      </c>
+      <c r="J18">
+        <v>75</v>
+      </c>
+      <c r="L18">
+        <v>76</v>
+      </c>
+      <c r="M18">
+        <v>24</v>
+      </c>
+      <c r="N18">
+        <v>35</v>
+      </c>
+      <c r="O18">
+        <v>65</v>
+      </c>
+      <c r="Q18">
+        <f t="shared" si="6"/>
+        <v>14.5</v>
+      </c>
+      <c r="R18">
+        <f t="shared" si="7"/>
+        <v>14</v>
+      </c>
+      <c r="S18">
+        <f t="shared" si="8"/>
+        <v>29.5</v>
+      </c>
+      <c r="T18">
+        <f t="shared" si="9"/>
+        <v>19.333333333333332</v>
+      </c>
+      <c r="U18">
+        <f t="shared" si="10"/>
+        <v>14</v>
+      </c>
+      <c r="V18">
+        <f t="shared" si="11"/>
+        <v>5.3333333333333321</v>
       </c>
     </row>
   </sheetData>
@@ -1950,7 +2579,7 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8328B926-3ADF-46D7-8F68-CEFFC1D24F6E}">
-  <dimension ref="A2:AF10"/>
+  <dimension ref="A2:AF15"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="2" spans="1:32" x14ac:dyDescent="0.3">
@@ -2492,6 +3121,237 @@
       <c r="V10">
         <f t="shared" si="5"/>
         <v>8.3333333333333321</v>
+      </c>
+    </row>
+    <row r="12" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="13" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B13">
+        <v>87</v>
+      </c>
+      <c r="C13">
+        <v>13</v>
+      </c>
+      <c r="D13">
+        <v>4</v>
+      </c>
+      <c r="E13">
+        <v>96</v>
+      </c>
+      <c r="G13">
+        <v>93</v>
+      </c>
+      <c r="H13">
+        <v>7</v>
+      </c>
+      <c r="I13">
+        <v>26</v>
+      </c>
+      <c r="J13">
+        <v>74</v>
+      </c>
+      <c r="L13">
+        <v>82</v>
+      </c>
+      <c r="M13">
+        <v>18</v>
+      </c>
+      <c r="N13">
+        <v>40</v>
+      </c>
+      <c r="O13">
+        <v>60</v>
+      </c>
+      <c r="Q13">
+        <f t="shared" ref="Q11:Q15" si="6">AVERAGE(C13:D13)</f>
+        <v>8.5</v>
+      </c>
+      <c r="R13">
+        <f t="shared" ref="R11:R15" si="7">AVERAGE(H13:I13)</f>
+        <v>16.5</v>
+      </c>
+      <c r="S13">
+        <f t="shared" ref="S11:S15" si="8">AVERAGE(M13:N13)</f>
+        <v>29</v>
+      </c>
+      <c r="T13">
+        <f t="shared" ref="T11:T15" si="9">AVERAGE(Q13:S13)</f>
+        <v>18</v>
+      </c>
+      <c r="U13">
+        <f t="shared" ref="U11:U15" si="10">MIN(Q13:S13)</f>
+        <v>8.5</v>
+      </c>
+      <c r="V13">
+        <f t="shared" ref="V11:V15" si="11">T13-U13</f>
+        <v>9.5</v>
+      </c>
+      <c r="W13">
+        <f>AVERAGE(Q13:Q19)</f>
+        <v>10.333333333333334</v>
+      </c>
+      <c r="X13">
+        <f>_xlfn.STDEV.S(Q13:Q19)</f>
+        <v>2.7537852736430528</v>
+      </c>
+      <c r="Y13">
+        <f>AVERAGE(R13:R19)</f>
+        <v>16.833333333333332</v>
+      </c>
+      <c r="Z13">
+        <f>_xlfn.STDEV.S(R13:R19)</f>
+        <v>2.0207259421636903</v>
+      </c>
+      <c r="AA13">
+        <f>AVERAGE(S13:S19)</f>
+        <v>32.5</v>
+      </c>
+      <c r="AB13">
+        <f>_xlfn.STDEV.S(S13:S19)</f>
+        <v>5.634713834792322</v>
+      </c>
+      <c r="AC13">
+        <f>AVERAGE(T13:T19)</f>
+        <v>19.888888888888889</v>
+      </c>
+      <c r="AD13">
+        <f>_xlfn.STDEV.S(T13:T19)</f>
+        <v>2.3353166174426336</v>
+      </c>
+      <c r="AE13">
+        <f>AVERAGE(V13:V19)</f>
+        <v>9.5555555555555554</v>
+      </c>
+      <c r="AF13">
+        <f>_xlfn.STDEV.S(V13:V19)</f>
+        <v>0.58531409738070839</v>
+      </c>
+    </row>
+    <row r="14" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B14">
+        <v>83</v>
+      </c>
+      <c r="C14">
+        <v>17</v>
+      </c>
+      <c r="D14">
+        <v>10</v>
+      </c>
+      <c r="E14">
+        <v>90</v>
+      </c>
+      <c r="G14">
+        <v>97</v>
+      </c>
+      <c r="H14">
+        <v>3</v>
+      </c>
+      <c r="I14">
+        <v>27</v>
+      </c>
+      <c r="J14">
+        <v>73</v>
+      </c>
+      <c r="L14">
+        <v>69</v>
+      </c>
+      <c r="M14">
+        <v>31</v>
+      </c>
+      <c r="N14">
+        <v>47</v>
+      </c>
+      <c r="O14">
+        <v>53</v>
+      </c>
+      <c r="Q14">
+        <f t="shared" si="6"/>
+        <v>13.5</v>
+      </c>
+      <c r="R14">
+        <f t="shared" si="7"/>
+        <v>15</v>
+      </c>
+      <c r="S14">
+        <f t="shared" si="8"/>
+        <v>39</v>
+      </c>
+      <c r="T14">
+        <f t="shared" si="9"/>
+        <v>22.5</v>
+      </c>
+      <c r="U14">
+        <f t="shared" si="10"/>
+        <v>13.5</v>
+      </c>
+      <c r="V14">
+        <f t="shared" si="11"/>
+        <v>9</v>
+      </c>
+    </row>
+    <row r="15" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B15">
+        <v>86</v>
+      </c>
+      <c r="C15">
+        <v>14</v>
+      </c>
+      <c r="D15">
+        <v>4</v>
+      </c>
+      <c r="E15">
+        <v>96</v>
+      </c>
+      <c r="G15">
+        <v>93</v>
+      </c>
+      <c r="H15">
+        <v>7</v>
+      </c>
+      <c r="I15">
+        <v>31</v>
+      </c>
+      <c r="J15">
+        <v>69</v>
+      </c>
+      <c r="L15">
+        <v>86</v>
+      </c>
+      <c r="M15">
+        <v>14</v>
+      </c>
+      <c r="N15">
+        <v>45</v>
+      </c>
+      <c r="O15">
+        <v>55</v>
+      </c>
+      <c r="Q15">
+        <f t="shared" si="6"/>
+        <v>9</v>
+      </c>
+      <c r="R15">
+        <f t="shared" si="7"/>
+        <v>19</v>
+      </c>
+      <c r="S15">
+        <f t="shared" si="8"/>
+        <v>29.5</v>
+      </c>
+      <c r="T15">
+        <f t="shared" si="9"/>
+        <v>19.166666666666668</v>
+      </c>
+      <c r="U15">
+        <f t="shared" si="10"/>
+        <v>9</v>
+      </c>
+      <c r="V15">
+        <f t="shared" si="11"/>
+        <v>10.166666666666668</v>
       </c>
     </row>
   </sheetData>
@@ -9436,44 +10296,44 @@
         <v>8.5</v>
       </c>
       <c r="W21">
-        <f>AVERAGE(Q21:Q23)</f>
-        <v>12.5</v>
+        <f>AVERAGE(Q21:Q25)</f>
+        <v>12.9</v>
       </c>
       <c r="X21">
-        <f>_xlfn.STDEV.S(Q21:Q23)</f>
-        <v>1.4142135623730951</v>
+        <f>_xlfn.STDEV.S(Q21:Q25)</f>
+        <v>1.6733200530681545</v>
       </c>
       <c r="Y21">
-        <f>AVERAGE(R21:R23)</f>
-        <v>16.5</v>
+        <f>AVERAGE(R21:R25)</f>
+        <v>18.399999999999999</v>
       </c>
       <c r="Z21">
-        <f>_xlfn.STDEV.S(R21:R23)</f>
-        <v>0</v>
+        <f>_xlfn.STDEV.S(R21:R25)</f>
+        <v>2.2748626332154678</v>
       </c>
       <c r="AA21">
-        <f>AVERAGE(S21:S23)</f>
-        <v>34</v>
+        <f>AVERAGE(S21:S25)</f>
+        <v>31.3</v>
       </c>
       <c r="AB21">
-        <f>_xlfn.STDEV.S(S21:S23)</f>
-        <v>2.8284271247461903</v>
+        <f>_xlfn.STDEV.S(S21:S25)</f>
+        <v>7.0498226928058303</v>
       </c>
       <c r="AC21">
-        <f>AVERAGE(T21:T23)</f>
-        <v>21</v>
+        <f>AVERAGE(T21:T25)</f>
+        <v>20.866666666666667</v>
       </c>
       <c r="AD21">
-        <f>_xlfn.STDEV.S(T21:T23)</f>
-        <v>1.4142135623730951</v>
+        <f>_xlfn.STDEV.S(T21:T25)</f>
+        <v>2.7923506624745986</v>
       </c>
       <c r="AE21">
-        <f>AVERAGE(V21:V23)</f>
-        <v>8.5</v>
+        <f>AVERAGE(V21:V25)</f>
+        <v>7.9666666666666659</v>
       </c>
       <c r="AF21">
-        <f>_xlfn.STDEV.S(V21:V23)</f>
-        <v>0</v>
+        <f>_xlfn.STDEV.S(V21:V25)</f>
+        <v>1.7215948678155679</v>
       </c>
     </row>
     <row r="22" spans="1:32" x14ac:dyDescent="0.3">
@@ -9538,6 +10398,192 @@
         <v>8.5</v>
       </c>
     </row>
+    <row r="23" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B23">
+        <v>90</v>
+      </c>
+      <c r="C23">
+        <v>10</v>
+      </c>
+      <c r="D23">
+        <v>21</v>
+      </c>
+      <c r="E23">
+        <v>79</v>
+      </c>
+      <c r="G23">
+        <v>92</v>
+      </c>
+      <c r="H23">
+        <v>8</v>
+      </c>
+      <c r="I23">
+        <v>36</v>
+      </c>
+      <c r="J23">
+        <v>64</v>
+      </c>
+      <c r="L23">
+        <v>78</v>
+      </c>
+      <c r="M23">
+        <v>22</v>
+      </c>
+      <c r="N23">
+        <v>46</v>
+      </c>
+      <c r="O23">
+        <v>54</v>
+      </c>
+      <c r="Q23">
+        <f t="shared" ref="Q23:Q25" si="12">AVERAGE(C23,D23)</f>
+        <v>15.5</v>
+      </c>
+      <c r="R23">
+        <f t="shared" ref="R23:R25" si="13">AVERAGE(H23:I23)</f>
+        <v>22</v>
+      </c>
+      <c r="S23">
+        <f t="shared" ref="S23:S25" si="14">AVERAGE(M23,N23)</f>
+        <v>34</v>
+      </c>
+      <c r="T23">
+        <f t="shared" ref="T23:T25" si="15">AVERAGE(Q23:S23)</f>
+        <v>23.833333333333332</v>
+      </c>
+      <c r="U23">
+        <f t="shared" ref="U23:U25" si="16">MIN(Q23:S23)</f>
+        <v>15.5</v>
+      </c>
+      <c r="V23">
+        <f t="shared" ref="V23:V25" si="17">(T23-U23)</f>
+        <v>8.3333333333333321</v>
+      </c>
+    </row>
+    <row r="24" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B24">
+        <v>84</v>
+      </c>
+      <c r="C24">
+        <v>16</v>
+      </c>
+      <c r="D24">
+        <v>9</v>
+      </c>
+      <c r="E24">
+        <v>91</v>
+      </c>
+      <c r="G24">
+        <v>93</v>
+      </c>
+      <c r="H24">
+        <v>7</v>
+      </c>
+      <c r="I24">
+        <v>29</v>
+      </c>
+      <c r="J24">
+        <v>71</v>
+      </c>
+      <c r="L24">
+        <v>78</v>
+      </c>
+      <c r="M24">
+        <v>22</v>
+      </c>
+      <c r="N24">
+        <v>49</v>
+      </c>
+      <c r="O24">
+        <v>51</v>
+      </c>
+      <c r="Q24">
+        <f t="shared" si="12"/>
+        <v>12.5</v>
+      </c>
+      <c r="R24">
+        <f t="shared" si="13"/>
+        <v>18</v>
+      </c>
+      <c r="S24">
+        <f t="shared" si="14"/>
+        <v>35.5</v>
+      </c>
+      <c r="T24">
+        <f t="shared" si="15"/>
+        <v>22</v>
+      </c>
+      <c r="U24">
+        <f t="shared" si="16"/>
+        <v>12.5</v>
+      </c>
+      <c r="V24">
+        <f t="shared" si="17"/>
+        <v>9.5</v>
+      </c>
+    </row>
+    <row r="25" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B25">
+        <v>88</v>
+      </c>
+      <c r="C25">
+        <v>12</v>
+      </c>
+      <c r="D25">
+        <v>11</v>
+      </c>
+      <c r="E25">
+        <v>89</v>
+      </c>
+      <c r="G25">
+        <v>97</v>
+      </c>
+      <c r="H25">
+        <v>3</v>
+      </c>
+      <c r="I25">
+        <v>35</v>
+      </c>
+      <c r="J25">
+        <v>65</v>
+      </c>
+      <c r="L25">
+        <v>84</v>
+      </c>
+      <c r="M25">
+        <v>16</v>
+      </c>
+      <c r="N25">
+        <v>22</v>
+      </c>
+      <c r="O25">
+        <v>78</v>
+      </c>
+      <c r="Q25">
+        <f t="shared" si="12"/>
+        <v>11.5</v>
+      </c>
+      <c r="R25">
+        <f t="shared" si="13"/>
+        <v>19</v>
+      </c>
+      <c r="S25">
+        <f t="shared" si="14"/>
+        <v>19</v>
+      </c>
+      <c r="T25">
+        <f t="shared" si="15"/>
+        <v>16.5</v>
+      </c>
+      <c r="U25">
+        <f t="shared" si="16"/>
+        <v>11.5</v>
+      </c>
+      <c r="V25">
+        <f t="shared" si="17"/>
+        <v>5</v>
+      </c>
+    </row>
     <row r="26" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>27</v>
@@ -10398,53 +11444,53 @@
     </row>
     <row r="68" spans="1:32" x14ac:dyDescent="0.3">
       <c r="Q68" t="e">
-        <f t="shared" ref="Q68:Q109" si="12">AVERAGE(C68,D68)</f>
+        <f t="shared" ref="Q68:Q109" si="18">AVERAGE(C68,D68)</f>
         <v>#DIV/0!</v>
       </c>
       <c r="R68" t="e">
-        <f t="shared" ref="R68:R109" si="13">AVERAGE(H68:I68)</f>
+        <f t="shared" ref="R68:R109" si="19">AVERAGE(H68:I68)</f>
         <v>#DIV/0!</v>
       </c>
       <c r="S68" t="e">
-        <f t="shared" ref="S68:S109" si="14">AVERAGE(M68,N68)</f>
+        <f t="shared" ref="S68:S109" si="20">AVERAGE(M68,N68)</f>
         <v>#DIV/0!</v>
       </c>
       <c r="T68" t="e">
-        <f t="shared" ref="T68:T109" si="15">AVERAGE(Q68:S68)</f>
+        <f t="shared" ref="T68:T109" si="21">AVERAGE(Q68:S68)</f>
         <v>#DIV/0!</v>
       </c>
       <c r="U68" t="e">
-        <f t="shared" ref="U68:U109" si="16">MIN(Q68:S68)</f>
+        <f t="shared" ref="U68:U109" si="22">MIN(Q68:S68)</f>
         <v>#DIV/0!</v>
       </c>
       <c r="V68" t="e">
-        <f t="shared" ref="V68:V109" si="17">(1/3)*(T68-U68)</f>
+        <f t="shared" ref="V68:V109" si="23">(1/3)*(T68-U68)</f>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="69" spans="1:32" x14ac:dyDescent="0.3">
       <c r="Q69" t="e">
-        <f t="shared" si="12"/>
+        <f t="shared" si="18"/>
         <v>#DIV/0!</v>
       </c>
       <c r="R69" t="e">
-        <f t="shared" si="13"/>
+        <f t="shared" si="19"/>
         <v>#DIV/0!</v>
       </c>
       <c r="S69" t="e">
-        <f t="shared" si="14"/>
+        <f t="shared" si="20"/>
         <v>#DIV/0!</v>
       </c>
       <c r="T69" t="e">
-        <f t="shared" si="15"/>
+        <f t="shared" si="21"/>
         <v>#DIV/0!</v>
       </c>
       <c r="U69" t="e">
-        <f t="shared" si="16"/>
+        <f t="shared" si="22"/>
         <v>#DIV/0!</v>
       </c>
       <c r="V69" t="e">
-        <f t="shared" si="17"/>
+        <f t="shared" si="23"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -10460,27 +11506,27 @@
     </row>
     <row r="73" spans="1:32" x14ac:dyDescent="0.3">
       <c r="Q73" t="e">
-        <f t="shared" si="12"/>
+        <f t="shared" si="18"/>
         <v>#DIV/0!</v>
       </c>
       <c r="R73" t="e">
-        <f t="shared" si="13"/>
+        <f t="shared" si="19"/>
         <v>#DIV/0!</v>
       </c>
       <c r="S73" t="e">
-        <f t="shared" si="14"/>
+        <f t="shared" si="20"/>
         <v>#DIV/0!</v>
       </c>
       <c r="T73" t="e">
-        <f t="shared" si="15"/>
+        <f t="shared" si="21"/>
         <v>#DIV/0!</v>
       </c>
       <c r="U73" t="e">
-        <f t="shared" si="16"/>
+        <f t="shared" si="22"/>
         <v>#DIV/0!</v>
       </c>
       <c r="V73" t="e">
-        <f t="shared" si="17"/>
+        <f t="shared" si="23"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AC73" t="e">
@@ -10502,53 +11548,53 @@
     </row>
     <row r="74" spans="1:32" x14ac:dyDescent="0.3">
       <c r="Q74" t="e">
-        <f t="shared" si="12"/>
+        <f t="shared" si="18"/>
         <v>#DIV/0!</v>
       </c>
       <c r="R74" t="e">
-        <f t="shared" si="13"/>
+        <f t="shared" si="19"/>
         <v>#DIV/0!</v>
       </c>
       <c r="S74" t="e">
-        <f t="shared" si="14"/>
+        <f t="shared" si="20"/>
         <v>#DIV/0!</v>
       </c>
       <c r="T74" t="e">
-        <f t="shared" si="15"/>
+        <f t="shared" si="21"/>
         <v>#DIV/0!</v>
       </c>
       <c r="U74" t="e">
-        <f t="shared" si="16"/>
+        <f t="shared" si="22"/>
         <v>#DIV/0!</v>
       </c>
       <c r="V74" t="e">
-        <f t="shared" si="17"/>
+        <f t="shared" si="23"/>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="75" spans="1:32" x14ac:dyDescent="0.3">
       <c r="Q75" t="e">
-        <f t="shared" si="12"/>
+        <f t="shared" si="18"/>
         <v>#DIV/0!</v>
       </c>
       <c r="R75" t="e">
-        <f t="shared" si="13"/>
+        <f t="shared" si="19"/>
         <v>#DIV/0!</v>
       </c>
       <c r="S75" t="e">
-        <f t="shared" si="14"/>
+        <f t="shared" si="20"/>
         <v>#DIV/0!</v>
       </c>
       <c r="T75" t="e">
-        <f t="shared" si="15"/>
+        <f t="shared" si="21"/>
         <v>#DIV/0!</v>
       </c>
       <c r="U75" t="e">
-        <f t="shared" si="16"/>
+        <f t="shared" si="22"/>
         <v>#DIV/0!</v>
       </c>
       <c r="V75" t="e">
-        <f t="shared" si="17"/>
+        <f t="shared" si="23"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -10564,27 +11610,27 @@
     </row>
     <row r="79" spans="1:32" x14ac:dyDescent="0.3">
       <c r="Q79" t="e">
-        <f t="shared" si="12"/>
+        <f t="shared" si="18"/>
         <v>#DIV/0!</v>
       </c>
       <c r="R79" t="e">
-        <f t="shared" si="13"/>
+        <f t="shared" si="19"/>
         <v>#DIV/0!</v>
       </c>
       <c r="S79" t="e">
-        <f t="shared" si="14"/>
+        <f t="shared" si="20"/>
         <v>#DIV/0!</v>
       </c>
       <c r="T79" t="e">
-        <f t="shared" si="15"/>
+        <f t="shared" si="21"/>
         <v>#DIV/0!</v>
       </c>
       <c r="U79" t="e">
-        <f t="shared" si="16"/>
+        <f t="shared" si="22"/>
         <v>#DIV/0!</v>
       </c>
       <c r="V79" t="e">
-        <f t="shared" si="17"/>
+        <f t="shared" si="23"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AC79" t="e">
@@ -10606,235 +11652,235 @@
     </row>
     <row r="80" spans="1:32" x14ac:dyDescent="0.3">
       <c r="Q80" t="e">
-        <f t="shared" si="12"/>
+        <f t="shared" si="18"/>
         <v>#DIV/0!</v>
       </c>
       <c r="R80" t="e">
-        <f t="shared" si="13"/>
+        <f t="shared" si="19"/>
         <v>#DIV/0!</v>
       </c>
       <c r="S80" t="e">
-        <f t="shared" si="14"/>
+        <f t="shared" si="20"/>
         <v>#DIV/0!</v>
       </c>
       <c r="T80" t="e">
-        <f t="shared" si="15"/>
+        <f t="shared" si="21"/>
         <v>#DIV/0!</v>
       </c>
       <c r="U80" t="e">
-        <f t="shared" si="16"/>
+        <f t="shared" si="22"/>
         <v>#DIV/0!</v>
       </c>
       <c r="V80" t="e">
-        <f t="shared" si="17"/>
+        <f t="shared" si="23"/>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="81" spans="1:32" x14ac:dyDescent="0.3">
       <c r="Q81" t="e">
-        <f t="shared" si="12"/>
+        <f t="shared" si="18"/>
         <v>#DIV/0!</v>
       </c>
       <c r="R81" t="e">
-        <f t="shared" si="13"/>
+        <f t="shared" si="19"/>
         <v>#DIV/0!</v>
       </c>
       <c r="S81" t="e">
-        <f t="shared" si="14"/>
+        <f t="shared" si="20"/>
         <v>#DIV/0!</v>
       </c>
       <c r="T81" t="e">
-        <f t="shared" si="15"/>
+        <f t="shared" si="21"/>
         <v>#DIV/0!</v>
       </c>
       <c r="U81" t="e">
-        <f t="shared" si="16"/>
+        <f t="shared" si="22"/>
         <v>#DIV/0!</v>
       </c>
       <c r="V81" t="e">
-        <f t="shared" si="17"/>
+        <f t="shared" si="23"/>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="82" spans="1:32" x14ac:dyDescent="0.3">
       <c r="Q82" t="e">
-        <f t="shared" si="12"/>
+        <f t="shared" si="18"/>
         <v>#DIV/0!</v>
       </c>
       <c r="R82" t="e">
-        <f t="shared" si="13"/>
+        <f t="shared" si="19"/>
         <v>#DIV/0!</v>
       </c>
       <c r="S82" t="e">
-        <f t="shared" si="14"/>
+        <f t="shared" si="20"/>
         <v>#DIV/0!</v>
       </c>
       <c r="T82" t="e">
-        <f t="shared" si="15"/>
+        <f t="shared" si="21"/>
         <v>#DIV/0!</v>
       </c>
       <c r="U82" t="e">
-        <f t="shared" si="16"/>
+        <f t="shared" si="22"/>
         <v>#DIV/0!</v>
       </c>
       <c r="V82" t="e">
-        <f t="shared" si="17"/>
+        <f t="shared" si="23"/>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="83" spans="1:32" x14ac:dyDescent="0.3">
       <c r="Q83" t="e">
-        <f t="shared" si="12"/>
+        <f t="shared" si="18"/>
         <v>#DIV/0!</v>
       </c>
       <c r="R83" t="e">
-        <f t="shared" si="13"/>
+        <f t="shared" si="19"/>
         <v>#DIV/0!</v>
       </c>
       <c r="S83" t="e">
-        <f t="shared" si="14"/>
+        <f t="shared" si="20"/>
         <v>#DIV/0!</v>
       </c>
       <c r="T83" t="e">
-        <f t="shared" si="15"/>
+        <f t="shared" si="21"/>
         <v>#DIV/0!</v>
       </c>
       <c r="U83" t="e">
-        <f t="shared" si="16"/>
+        <f t="shared" si="22"/>
         <v>#DIV/0!</v>
       </c>
       <c r="V83" t="e">
-        <f t="shared" si="17"/>
+        <f t="shared" si="23"/>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="84" spans="1:32" x14ac:dyDescent="0.3">
       <c r="Q84" t="e">
-        <f t="shared" si="12"/>
+        <f t="shared" si="18"/>
         <v>#DIV/0!</v>
       </c>
       <c r="R84" t="e">
-        <f t="shared" si="13"/>
+        <f t="shared" si="19"/>
         <v>#DIV/0!</v>
       </c>
       <c r="S84" t="e">
-        <f t="shared" si="14"/>
+        <f t="shared" si="20"/>
         <v>#DIV/0!</v>
       </c>
       <c r="T84" t="e">
-        <f t="shared" si="15"/>
+        <f t="shared" si="21"/>
         <v>#DIV/0!</v>
       </c>
       <c r="U84" t="e">
-        <f t="shared" si="16"/>
+        <f t="shared" si="22"/>
         <v>#DIV/0!</v>
       </c>
       <c r="V84" t="e">
-        <f t="shared" si="17"/>
+        <f t="shared" si="23"/>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="85" spans="1:32" x14ac:dyDescent="0.3">
       <c r="Q85" t="e">
-        <f t="shared" si="12"/>
+        <f t="shared" si="18"/>
         <v>#DIV/0!</v>
       </c>
       <c r="R85" t="e">
-        <f t="shared" si="13"/>
+        <f t="shared" si="19"/>
         <v>#DIV/0!</v>
       </c>
       <c r="S85" t="e">
-        <f t="shared" si="14"/>
+        <f t="shared" si="20"/>
         <v>#DIV/0!</v>
       </c>
       <c r="T85" t="e">
-        <f t="shared" si="15"/>
+        <f t="shared" si="21"/>
         <v>#DIV/0!</v>
       </c>
       <c r="U85" t="e">
-        <f t="shared" si="16"/>
+        <f t="shared" si="22"/>
         <v>#DIV/0!</v>
       </c>
       <c r="V85" t="e">
-        <f t="shared" si="17"/>
+        <f t="shared" si="23"/>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="86" spans="1:32" x14ac:dyDescent="0.3">
       <c r="Q86" t="e">
-        <f t="shared" si="12"/>
+        <f t="shared" si="18"/>
         <v>#DIV/0!</v>
       </c>
       <c r="R86" t="e">
-        <f t="shared" si="13"/>
+        <f t="shared" si="19"/>
         <v>#DIV/0!</v>
       </c>
       <c r="S86" t="e">
-        <f t="shared" si="14"/>
+        <f t="shared" si="20"/>
         <v>#DIV/0!</v>
       </c>
       <c r="T86" t="e">
-        <f t="shared" si="15"/>
+        <f t="shared" si="21"/>
         <v>#DIV/0!</v>
       </c>
       <c r="U86" t="e">
-        <f t="shared" si="16"/>
+        <f t="shared" si="22"/>
         <v>#DIV/0!</v>
       </c>
       <c r="V86" t="e">
-        <f t="shared" si="17"/>
+        <f t="shared" si="23"/>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="87" spans="1:32" x14ac:dyDescent="0.3">
       <c r="Q87" t="e">
-        <f t="shared" si="12"/>
+        <f t="shared" si="18"/>
         <v>#DIV/0!</v>
       </c>
       <c r="R87" t="e">
-        <f t="shared" si="13"/>
+        <f t="shared" si="19"/>
         <v>#DIV/0!</v>
       </c>
       <c r="S87" t="e">
-        <f t="shared" si="14"/>
+        <f t="shared" si="20"/>
         <v>#DIV/0!</v>
       </c>
       <c r="T87" t="e">
-        <f t="shared" si="15"/>
+        <f t="shared" si="21"/>
         <v>#DIV/0!</v>
       </c>
       <c r="U87" t="e">
-        <f t="shared" si="16"/>
+        <f t="shared" si="22"/>
         <v>#DIV/0!</v>
       </c>
       <c r="V87" t="e">
-        <f t="shared" si="17"/>
+        <f t="shared" si="23"/>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="88" spans="1:32" x14ac:dyDescent="0.3">
       <c r="Q88" t="e">
-        <f t="shared" si="12"/>
+        <f t="shared" si="18"/>
         <v>#DIV/0!</v>
       </c>
       <c r="R88" t="e">
-        <f t="shared" si="13"/>
+        <f t="shared" si="19"/>
         <v>#DIV/0!</v>
       </c>
       <c r="S88" t="e">
-        <f t="shared" si="14"/>
+        <f t="shared" si="20"/>
         <v>#DIV/0!</v>
       </c>
       <c r="T88" t="e">
-        <f t="shared" si="15"/>
+        <f t="shared" si="21"/>
         <v>#DIV/0!</v>
       </c>
       <c r="U88" t="e">
-        <f t="shared" si="16"/>
+        <f t="shared" si="22"/>
         <v>#DIV/0!</v>
       </c>
       <c r="V88" t="e">
-        <f t="shared" si="17"/>
+        <f t="shared" si="23"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -10850,27 +11896,27 @@
     </row>
     <row r="92" spans="1:32" x14ac:dyDescent="0.3">
       <c r="Q92" t="e">
-        <f t="shared" si="12"/>
+        <f t="shared" si="18"/>
         <v>#DIV/0!</v>
       </c>
       <c r="R92" t="e">
-        <f t="shared" si="13"/>
+        <f t="shared" si="19"/>
         <v>#DIV/0!</v>
       </c>
       <c r="S92" t="e">
-        <f t="shared" si="14"/>
+        <f t="shared" si="20"/>
         <v>#DIV/0!</v>
       </c>
       <c r="T92" t="e">
-        <f t="shared" si="15"/>
+        <f t="shared" si="21"/>
         <v>#DIV/0!</v>
       </c>
       <c r="U92" t="e">
-        <f t="shared" si="16"/>
+        <f t="shared" si="22"/>
         <v>#DIV/0!</v>
       </c>
       <c r="V92" t="e">
-        <f t="shared" si="17"/>
+        <f t="shared" si="23"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AC92" t="e">
@@ -10892,131 +11938,131 @@
     </row>
     <row r="93" spans="1:32" x14ac:dyDescent="0.3">
       <c r="Q93" t="e">
-        <f t="shared" si="12"/>
+        <f t="shared" si="18"/>
         <v>#DIV/0!</v>
       </c>
       <c r="R93" t="e">
-        <f t="shared" si="13"/>
+        <f t="shared" si="19"/>
         <v>#DIV/0!</v>
       </c>
       <c r="S93" t="e">
-        <f t="shared" si="14"/>
+        <f t="shared" si="20"/>
         <v>#DIV/0!</v>
       </c>
       <c r="T93" t="e">
-        <f t="shared" si="15"/>
+        <f t="shared" si="21"/>
         <v>#DIV/0!</v>
       </c>
       <c r="U93" t="e">
-        <f t="shared" si="16"/>
+        <f t="shared" si="22"/>
         <v>#DIV/0!</v>
       </c>
       <c r="V93" t="e">
-        <f t="shared" si="17"/>
+        <f t="shared" si="23"/>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="94" spans="1:32" x14ac:dyDescent="0.3">
       <c r="Q94" t="e">
-        <f t="shared" si="12"/>
+        <f t="shared" si="18"/>
         <v>#DIV/0!</v>
       </c>
       <c r="R94" t="e">
-        <f t="shared" si="13"/>
+        <f t="shared" si="19"/>
         <v>#DIV/0!</v>
       </c>
       <c r="S94" t="e">
-        <f t="shared" si="14"/>
+        <f t="shared" si="20"/>
         <v>#DIV/0!</v>
       </c>
       <c r="T94" t="e">
-        <f t="shared" si="15"/>
+        <f t="shared" si="21"/>
         <v>#DIV/0!</v>
       </c>
       <c r="U94" t="e">
-        <f t="shared" si="16"/>
+        <f t="shared" si="22"/>
         <v>#DIV/0!</v>
       </c>
       <c r="V94" t="e">
-        <f t="shared" si="17"/>
+        <f t="shared" si="23"/>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="95" spans="1:32" x14ac:dyDescent="0.3">
       <c r="Q95" t="e">
-        <f t="shared" si="12"/>
+        <f t="shared" si="18"/>
         <v>#DIV/0!</v>
       </c>
       <c r="R95" t="e">
-        <f t="shared" si="13"/>
+        <f t="shared" si="19"/>
         <v>#DIV/0!</v>
       </c>
       <c r="S95" t="e">
-        <f t="shared" si="14"/>
+        <f t="shared" si="20"/>
         <v>#DIV/0!</v>
       </c>
       <c r="T95" t="e">
-        <f t="shared" si="15"/>
+        <f t="shared" si="21"/>
         <v>#DIV/0!</v>
       </c>
       <c r="U95" t="e">
-        <f t="shared" si="16"/>
+        <f t="shared" si="22"/>
         <v>#DIV/0!</v>
       </c>
       <c r="V95" t="e">
-        <f t="shared" si="17"/>
+        <f t="shared" si="23"/>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="96" spans="1:32" x14ac:dyDescent="0.3">
       <c r="Q96" t="e">
-        <f t="shared" si="12"/>
+        <f t="shared" si="18"/>
         <v>#DIV/0!</v>
       </c>
       <c r="R96" t="e">
-        <f t="shared" si="13"/>
+        <f t="shared" si="19"/>
         <v>#DIV/0!</v>
       </c>
       <c r="S96" t="e">
-        <f t="shared" si="14"/>
+        <f t="shared" si="20"/>
         <v>#DIV/0!</v>
       </c>
       <c r="T96" t="e">
-        <f t="shared" si="15"/>
+        <f t="shared" si="21"/>
         <v>#DIV/0!</v>
       </c>
       <c r="U96" t="e">
-        <f t="shared" si="16"/>
+        <f t="shared" si="22"/>
         <v>#DIV/0!</v>
       </c>
       <c r="V96" t="e">
-        <f t="shared" si="17"/>
+        <f t="shared" si="23"/>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="97" spans="1:32" x14ac:dyDescent="0.3">
       <c r="Q97" t="e">
-        <f t="shared" si="12"/>
+        <f t="shared" si="18"/>
         <v>#DIV/0!</v>
       </c>
       <c r="R97" t="e">
-        <f t="shared" si="13"/>
+        <f t="shared" si="19"/>
         <v>#DIV/0!</v>
       </c>
       <c r="S97" t="e">
-        <f t="shared" si="14"/>
+        <f t="shared" si="20"/>
         <v>#DIV/0!</v>
       </c>
       <c r="T97" t="e">
-        <f t="shared" si="15"/>
+        <f t="shared" si="21"/>
         <v>#DIV/0!</v>
       </c>
       <c r="U97" t="e">
-        <f t="shared" si="16"/>
+        <f t="shared" si="22"/>
         <v>#DIV/0!</v>
       </c>
       <c r="V97" t="e">
-        <f t="shared" si="17"/>
+        <f t="shared" si="23"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -11032,27 +12078,27 @@
     </row>
     <row r="101" spans="1:32" x14ac:dyDescent="0.3">
       <c r="Q101" t="e">
-        <f t="shared" si="12"/>
+        <f t="shared" si="18"/>
         <v>#DIV/0!</v>
       </c>
       <c r="R101" t="e">
-        <f t="shared" si="13"/>
+        <f t="shared" si="19"/>
         <v>#DIV/0!</v>
       </c>
       <c r="S101" t="e">
-        <f t="shared" si="14"/>
+        <f t="shared" si="20"/>
         <v>#DIV/0!</v>
       </c>
       <c r="T101" t="e">
-        <f t="shared" si="15"/>
+        <f t="shared" si="21"/>
         <v>#DIV/0!</v>
       </c>
       <c r="U101" t="e">
-        <f t="shared" si="16"/>
+        <f t="shared" si="22"/>
         <v>#DIV/0!</v>
       </c>
       <c r="V101" t="e">
-        <f t="shared" si="17"/>
+        <f t="shared" si="23"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AC101" t="e">
@@ -11074,220 +12120,221 @@
     </row>
     <row r="102" spans="1:32" x14ac:dyDescent="0.3">
       <c r="Q102" t="e">
-        <f t="shared" si="12"/>
+        <f t="shared" si="18"/>
         <v>#DIV/0!</v>
       </c>
       <c r="R102" t="e">
-        <f t="shared" si="13"/>
+        <f t="shared" si="19"/>
         <v>#DIV/0!</v>
       </c>
       <c r="S102" t="e">
-        <f t="shared" si="14"/>
+        <f t="shared" si="20"/>
         <v>#DIV/0!</v>
       </c>
       <c r="T102" t="e">
-        <f t="shared" si="15"/>
+        <f t="shared" si="21"/>
         <v>#DIV/0!</v>
       </c>
       <c r="U102" t="e">
-        <f t="shared" si="16"/>
+        <f t="shared" si="22"/>
         <v>#DIV/0!</v>
       </c>
       <c r="V102" t="e">
-        <f t="shared" si="17"/>
+        <f t="shared" si="23"/>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="103" spans="1:32" x14ac:dyDescent="0.3">
       <c r="Q103" t="e">
-        <f t="shared" si="12"/>
+        <f t="shared" si="18"/>
         <v>#DIV/0!</v>
       </c>
       <c r="R103" t="e">
-        <f t="shared" si="13"/>
+        <f t="shared" si="19"/>
         <v>#DIV/0!</v>
       </c>
       <c r="S103" t="e">
-        <f t="shared" si="14"/>
+        <f t="shared" si="20"/>
         <v>#DIV/0!</v>
       </c>
       <c r="T103" t="e">
-        <f t="shared" si="15"/>
+        <f t="shared" si="21"/>
         <v>#DIV/0!</v>
       </c>
       <c r="U103" t="e">
-        <f t="shared" si="16"/>
+        <f t="shared" si="22"/>
         <v>#DIV/0!</v>
       </c>
       <c r="V103" t="e">
-        <f t="shared" si="17"/>
+        <f t="shared" si="23"/>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="104" spans="1:32" x14ac:dyDescent="0.3">
       <c r="Q104" t="e">
-        <f t="shared" si="12"/>
+        <f t="shared" si="18"/>
         <v>#DIV/0!</v>
       </c>
       <c r="R104" t="e">
-        <f t="shared" si="13"/>
+        <f t="shared" si="19"/>
         <v>#DIV/0!</v>
       </c>
       <c r="S104" t="e">
-        <f t="shared" si="14"/>
+        <f t="shared" si="20"/>
         <v>#DIV/0!</v>
       </c>
       <c r="T104" t="e">
-        <f t="shared" si="15"/>
+        <f t="shared" si="21"/>
         <v>#DIV/0!</v>
       </c>
       <c r="U104" t="e">
-        <f t="shared" si="16"/>
+        <f t="shared" si="22"/>
         <v>#DIV/0!</v>
       </c>
       <c r="V104" t="e">
-        <f t="shared" si="17"/>
+        <f t="shared" si="23"/>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="105" spans="1:32" x14ac:dyDescent="0.3">
       <c r="Q105" t="e">
-        <f t="shared" si="12"/>
+        <f t="shared" si="18"/>
         <v>#DIV/0!</v>
       </c>
       <c r="R105" t="e">
-        <f t="shared" si="13"/>
+        <f t="shared" si="19"/>
         <v>#DIV/0!</v>
       </c>
       <c r="S105" t="e">
-        <f t="shared" si="14"/>
+        <f t="shared" si="20"/>
         <v>#DIV/0!</v>
       </c>
       <c r="T105" t="e">
-        <f t="shared" si="15"/>
+        <f t="shared" si="21"/>
         <v>#DIV/0!</v>
       </c>
       <c r="U105" t="e">
-        <f t="shared" si="16"/>
+        <f t="shared" si="22"/>
         <v>#DIV/0!</v>
       </c>
       <c r="V105" t="e">
-        <f t="shared" si="17"/>
+        <f t="shared" si="23"/>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="106" spans="1:32" x14ac:dyDescent="0.3">
       <c r="Q106" t="e">
-        <f t="shared" si="12"/>
+        <f t="shared" si="18"/>
         <v>#DIV/0!</v>
       </c>
       <c r="R106" t="e">
-        <f t="shared" si="13"/>
+        <f t="shared" si="19"/>
         <v>#DIV/0!</v>
       </c>
       <c r="S106" t="e">
-        <f t="shared" si="14"/>
+        <f t="shared" si="20"/>
         <v>#DIV/0!</v>
       </c>
       <c r="T106" t="e">
-        <f t="shared" si="15"/>
+        <f t="shared" si="21"/>
         <v>#DIV/0!</v>
       </c>
       <c r="U106" t="e">
-        <f t="shared" si="16"/>
+        <f t="shared" si="22"/>
         <v>#DIV/0!</v>
       </c>
       <c r="V106" t="e">
-        <f t="shared" si="17"/>
+        <f t="shared" si="23"/>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="107" spans="1:32" x14ac:dyDescent="0.3">
       <c r="Q107" t="e">
-        <f t="shared" si="12"/>
+        <f t="shared" si="18"/>
         <v>#DIV/0!</v>
       </c>
       <c r="R107" t="e">
-        <f t="shared" si="13"/>
+        <f t="shared" si="19"/>
         <v>#DIV/0!</v>
       </c>
       <c r="S107" t="e">
-        <f t="shared" si="14"/>
+        <f t="shared" si="20"/>
         <v>#DIV/0!</v>
       </c>
       <c r="T107" t="e">
-        <f t="shared" si="15"/>
+        <f t="shared" si="21"/>
         <v>#DIV/0!</v>
       </c>
       <c r="U107" t="e">
-        <f t="shared" si="16"/>
+        <f t="shared" si="22"/>
         <v>#DIV/0!</v>
       </c>
       <c r="V107" t="e">
-        <f t="shared" si="17"/>
+        <f t="shared" si="23"/>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="108" spans="1:32" x14ac:dyDescent="0.3">
       <c r="Q108" t="e">
-        <f t="shared" si="12"/>
+        <f t="shared" si="18"/>
         <v>#DIV/0!</v>
       </c>
       <c r="R108" t="e">
-        <f t="shared" si="13"/>
+        <f t="shared" si="19"/>
         <v>#DIV/0!</v>
       </c>
       <c r="S108" t="e">
-        <f t="shared" si="14"/>
+        <f t="shared" si="20"/>
         <v>#DIV/0!</v>
       </c>
       <c r="T108" t="e">
-        <f t="shared" si="15"/>
+        <f t="shared" si="21"/>
         <v>#DIV/0!</v>
       </c>
       <c r="U108" t="e">
-        <f t="shared" si="16"/>
+        <f t="shared" si="22"/>
         <v>#DIV/0!</v>
       </c>
       <c r="V108" t="e">
-        <f t="shared" si="17"/>
+        <f t="shared" si="23"/>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="109" spans="1:32" x14ac:dyDescent="0.3">
       <c r="Q109" t="e">
-        <f t="shared" si="12"/>
+        <f t="shared" si="18"/>
         <v>#DIV/0!</v>
       </c>
       <c r="R109" t="e">
-        <f t="shared" si="13"/>
+        <f t="shared" si="19"/>
         <v>#DIV/0!</v>
       </c>
       <c r="S109" t="e">
-        <f t="shared" si="14"/>
+        <f t="shared" si="20"/>
         <v>#DIV/0!</v>
       </c>
       <c r="T109" t="e">
-        <f t="shared" si="15"/>
+        <f t="shared" si="21"/>
         <v>#DIV/0!</v>
       </c>
       <c r="U109" t="e">
-        <f t="shared" si="16"/>
+        <f t="shared" si="22"/>
         <v>#DIV/0!</v>
       </c>
       <c r="V109" t="e">
-        <f t="shared" si="17"/>
+        <f t="shared" si="23"/>
         <v>#DIV/0!</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D80BAE23-A740-4698-B840-F018E78CD098}">
-  <dimension ref="A1:AF5"/>
+  <dimension ref="A1:AF10"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="23" max="23" width="8.21875" customWidth="1"/>
@@ -11578,6 +12625,237 @@
       <c r="V5">
         <f t="shared" si="5"/>
         <v>7</v>
+      </c>
+    </row>
+    <row r="7" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="8" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B8">
+        <v>88</v>
+      </c>
+      <c r="C8">
+        <v>12</v>
+      </c>
+      <c r="D8">
+        <v>20</v>
+      </c>
+      <c r="E8">
+        <v>80</v>
+      </c>
+      <c r="G8">
+        <v>95</v>
+      </c>
+      <c r="H8">
+        <v>5</v>
+      </c>
+      <c r="I8">
+        <v>30</v>
+      </c>
+      <c r="J8">
+        <v>70</v>
+      </c>
+      <c r="L8">
+        <v>80</v>
+      </c>
+      <c r="M8">
+        <v>20</v>
+      </c>
+      <c r="N8">
+        <v>48</v>
+      </c>
+      <c r="O8">
+        <v>52</v>
+      </c>
+      <c r="Q8">
+        <f t="shared" ref="Q6:Q10" si="6">AVERAGE(C8:D8)</f>
+        <v>16</v>
+      </c>
+      <c r="R8">
+        <f t="shared" ref="R6:R10" si="7">AVERAGE(H8:I8)</f>
+        <v>17.5</v>
+      </c>
+      <c r="S8">
+        <f t="shared" ref="S6:S10" si="8">AVERAGE(M8:N8)</f>
+        <v>34</v>
+      </c>
+      <c r="T8">
+        <f t="shared" ref="T6:T10" si="9">AVERAGE(Q8:S8)</f>
+        <v>22.5</v>
+      </c>
+      <c r="U8">
+        <f t="shared" ref="U6:U10" si="10">MIN(Q8:S8)</f>
+        <v>16</v>
+      </c>
+      <c r="V8">
+        <f t="shared" ref="V6:V10" si="11">T8-U8</f>
+        <v>6.5</v>
+      </c>
+      <c r="W8">
+        <f>AVERAGE(Q8:Q10)</f>
+        <v>13.666666666666666</v>
+      </c>
+      <c r="X8">
+        <f>_xlfn.STDEV.S(Q8:Q10)</f>
+        <v>2.0816659994661282</v>
+      </c>
+      <c r="Y8">
+        <f>AVERAGE(R8:R10)</f>
+        <v>17.166666666666668</v>
+      </c>
+      <c r="Z8">
+        <f>_xlfn.STDEV.S(R8:R10)</f>
+        <v>1.5275252316519465</v>
+      </c>
+      <c r="AA8">
+        <f>AVERAGE(S8:S10)</f>
+        <v>33</v>
+      </c>
+      <c r="AB8">
+        <f>_xlfn.STDEV.S(S8:S10)</f>
+        <v>3.1224989991991992</v>
+      </c>
+      <c r="AC8">
+        <f>AVERAGE(T8:T10)</f>
+        <v>21.277777777777775</v>
+      </c>
+      <c r="AD8">
+        <f>_xlfn.STDEV.S(T8:T10)</f>
+        <v>1.9743728493240953</v>
+      </c>
+      <c r="AE8">
+        <f>AVERAGE(V8:V10)</f>
+        <v>7.6111111111111107</v>
+      </c>
+      <c r="AF8">
+        <f>_xlfn.STDEV.S(V8:V10)</f>
+        <v>1.5122952876462401</v>
+      </c>
+    </row>
+    <row r="9" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B9">
+        <v>88</v>
+      </c>
+      <c r="C9">
+        <v>12</v>
+      </c>
+      <c r="D9">
+        <v>12</v>
+      </c>
+      <c r="E9">
+        <v>88</v>
+      </c>
+      <c r="G9">
+        <v>92</v>
+      </c>
+      <c r="H9">
+        <v>8</v>
+      </c>
+      <c r="I9">
+        <v>23</v>
+      </c>
+      <c r="J9">
+        <v>77</v>
+      </c>
+      <c r="L9">
+        <v>75</v>
+      </c>
+      <c r="M9">
+        <v>25</v>
+      </c>
+      <c r="N9">
+        <v>34</v>
+      </c>
+      <c r="O9">
+        <v>66</v>
+      </c>
+      <c r="Q9">
+        <f t="shared" si="6"/>
+        <v>12</v>
+      </c>
+      <c r="R9">
+        <f t="shared" si="7"/>
+        <v>15.5</v>
+      </c>
+      <c r="S9">
+        <f t="shared" si="8"/>
+        <v>29.5</v>
+      </c>
+      <c r="T9">
+        <f t="shared" si="9"/>
+        <v>19</v>
+      </c>
+      <c r="U9">
+        <f t="shared" si="10"/>
+        <v>12</v>
+      </c>
+      <c r="V9">
+        <f t="shared" si="11"/>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="10" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B10">
+        <v>87</v>
+      </c>
+      <c r="C10">
+        <v>13</v>
+      </c>
+      <c r="D10">
+        <v>13</v>
+      </c>
+      <c r="E10">
+        <v>87</v>
+      </c>
+      <c r="G10">
+        <v>95</v>
+      </c>
+      <c r="H10">
+        <v>5</v>
+      </c>
+      <c r="I10">
+        <v>32</v>
+      </c>
+      <c r="J10">
+        <v>68</v>
+      </c>
+      <c r="L10">
+        <v>80</v>
+      </c>
+      <c r="M10">
+        <v>20</v>
+      </c>
+      <c r="N10">
+        <v>51</v>
+      </c>
+      <c r="O10">
+        <v>49</v>
+      </c>
+      <c r="Q10">
+        <f t="shared" si="6"/>
+        <v>13</v>
+      </c>
+      <c r="R10">
+        <f t="shared" si="7"/>
+        <v>18.5</v>
+      </c>
+      <c r="S10">
+        <f t="shared" si="8"/>
+        <v>35.5</v>
+      </c>
+      <c r="T10">
+        <f t="shared" si="9"/>
+        <v>22.333333333333332</v>
+      </c>
+      <c r="U10">
+        <f t="shared" si="10"/>
+        <v>13</v>
+      </c>
+      <c r="V10">
+        <f t="shared" si="11"/>
+        <v>9.3333333333333321</v>
       </c>
     </row>
   </sheetData>
@@ -14072,7 +15350,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A366D673-4552-407C-AD95-3B60150A1024}">
-  <dimension ref="A2:AF13"/>
+  <dimension ref="A2:AF14"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="2" spans="1:32" x14ac:dyDescent="0.3">
@@ -14496,16 +15774,16 @@
     </row>
     <row r="12" spans="1:32" x14ac:dyDescent="0.3">
       <c r="B12">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C12">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D12">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="E12">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="G12">
         <v>98</v>
@@ -14514,148 +15792,210 @@
         <v>2</v>
       </c>
       <c r="I12">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="J12">
-        <v>66</v>
+        <v>75</v>
       </c>
       <c r="L12">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="M12">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="N12">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="O12">
-        <v>62</v>
+        <v>74</v>
       </c>
       <c r="Q12">
         <f t="shared" ref="Q12:Q13" si="6">AVERAGE(C12:D12)</f>
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="R12">
         <f t="shared" ref="R12:R13" si="7">AVERAGE(H12:I12)</f>
-        <v>18</v>
+        <v>13.5</v>
       </c>
       <c r="S12">
         <f t="shared" ref="S12:S13" si="8">AVERAGE(M12:N12)</f>
-        <v>25.5</v>
+        <v>23</v>
       </c>
       <c r="T12">
         <f t="shared" ref="T12:T13" si="9">AVERAGE(Q12:S12)</f>
-        <v>19.166666666666668</v>
+        <v>14.833333333333334</v>
       </c>
       <c r="U12">
         <f t="shared" ref="U12:U13" si="10">MIN(Q12:S12)</f>
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="V12">
         <f t="shared" ref="V12:V13" si="11">T12-U12</f>
-        <v>5.1666666666666679</v>
+        <v>6.8333333333333339</v>
       </c>
       <c r="W12">
         <f>AVERAGE(Q12:Q18)</f>
-        <v>12.25</v>
+        <v>10.5</v>
       </c>
       <c r="X12">
         <f>_xlfn.STDEV.S(Q12:Q18)</f>
-        <v>2.4748737341529163</v>
+        <v>2.7838821814150108</v>
       </c>
       <c r="Y12">
         <f>AVERAGE(R12:R18)</f>
-        <v>16.75</v>
+        <v>15.166666666666666</v>
       </c>
       <c r="Z12">
         <f>_xlfn.STDEV.S(R12:R18)</f>
-        <v>1.7677669529663689</v>
+        <v>4.2524502740576891</v>
       </c>
       <c r="AA12">
         <f>AVERAGE(S12:S18)</f>
-        <v>25.25</v>
+        <v>21.666666666666668</v>
       </c>
       <c r="AB12">
         <f>_xlfn.STDEV.S(S12:S18)</f>
-        <v>0.35355339059327379</v>
+        <v>1.2583057392117916</v>
       </c>
       <c r="AC12">
         <f>AVERAGE(T12:T18)</f>
-        <v>18.083333333333336</v>
+        <v>15.777777777777777</v>
       </c>
       <c r="AD12">
         <f>_xlfn.STDEV.S(T12:T18)</f>
-        <v>1.5320646925708539</v>
+        <v>2.2381374531648746</v>
       </c>
       <c r="AE12">
         <f>AVERAGE(V12:V18)</f>
-        <v>5.8333333333333339</v>
+        <v>5.2777777777777777</v>
       </c>
       <c r="AF12">
         <f>_xlfn.STDEV.S(V12:V18)</f>
-        <v>0.94280904158206169</v>
+        <v>1.3877773329774237</v>
       </c>
     </row>
     <row r="13" spans="1:32" x14ac:dyDescent="0.3">
       <c r="B13">
+        <v>89</v>
+      </c>
+      <c r="C13">
+        <v>11</v>
+      </c>
+      <c r="D13">
+        <v>16</v>
+      </c>
+      <c r="E13">
+        <v>84</v>
+      </c>
+      <c r="G13">
+        <v>98</v>
+      </c>
+      <c r="H13">
+        <v>2</v>
+      </c>
+      <c r="I13">
+        <v>38</v>
+      </c>
+      <c r="J13">
+        <v>62</v>
+      </c>
+      <c r="L13">
+        <v>81</v>
+      </c>
+      <c r="M13">
+        <v>19</v>
+      </c>
+      <c r="N13">
+        <v>24</v>
+      </c>
+      <c r="O13">
+        <v>76</v>
+      </c>
+      <c r="Q13">
+        <f>AVERAGE(C13:D13)</f>
+        <v>13.5</v>
+      </c>
+      <c r="R13">
+        <f>AVERAGE(H13:I13)</f>
+        <v>20</v>
+      </c>
+      <c r="S13">
+        <f>AVERAGE(M13:N13)</f>
+        <v>21.5</v>
+      </c>
+      <c r="T13">
+        <f>AVERAGE(Q13:S13)</f>
+        <v>18.333333333333332</v>
+      </c>
+      <c r="U13">
+        <f>MIN(Q13:S13)</f>
+        <v>13.5</v>
+      </c>
+      <c r="V13">
+        <f>T13-U13</f>
+        <v>4.8333333333333321</v>
+      </c>
+    </row>
+    <row r="14" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B14">
         <v>93</v>
       </c>
-      <c r="C13">
+      <c r="C14">
         <v>7</v>
       </c>
-      <c r="D13">
-        <v>14</v>
-      </c>
-      <c r="E13">
-        <v>86</v>
-      </c>
-      <c r="G13">
-        <v>94</v>
-      </c>
-      <c r="H13">
-        <v>6</v>
-      </c>
-      <c r="I13">
+      <c r="D14">
+        <v>13</v>
+      </c>
+      <c r="E14">
+        <v>87</v>
+      </c>
+      <c r="G14">
+        <v>97</v>
+      </c>
+      <c r="H14">
+        <v>3</v>
+      </c>
+      <c r="I14">
+        <v>21</v>
+      </c>
+      <c r="J14">
+        <v>79</v>
+      </c>
+      <c r="L14">
+        <v>75</v>
+      </c>
+      <c r="M14">
         <v>25</v>
       </c>
-      <c r="J13">
-        <v>75</v>
-      </c>
-      <c r="L13">
-        <v>70</v>
-      </c>
-      <c r="M13">
-        <v>30</v>
-      </c>
-      <c r="N13">
-        <v>20</v>
-      </c>
-      <c r="O13">
-        <v>80</v>
-      </c>
-      <c r="Q13">
-        <f t="shared" si="6"/>
-        <v>10.5</v>
-      </c>
-      <c r="R13">
-        <f t="shared" si="7"/>
-        <v>15.5</v>
-      </c>
-      <c r="S13">
-        <f t="shared" si="8"/>
-        <v>25</v>
-      </c>
-      <c r="T13">
-        <f t="shared" si="9"/>
-        <v>17</v>
-      </c>
-      <c r="U13">
-        <f t="shared" si="10"/>
-        <v>10.5</v>
-      </c>
-      <c r="V13">
-        <f t="shared" si="11"/>
-        <v>6.5</v>
+      <c r="N14">
+        <v>16</v>
+      </c>
+      <c r="O14">
+        <v>84</v>
+      </c>
+      <c r="Q14">
+        <f>AVERAGE(C14:D14)</f>
+        <v>10</v>
+      </c>
+      <c r="R14">
+        <f>AVERAGE(H14:I14)</f>
+        <v>12</v>
+      </c>
+      <c r="S14">
+        <f>AVERAGE(M14:N14)</f>
+        <v>20.5</v>
+      </c>
+      <c r="T14">
+        <f>AVERAGE(Q14:S14)</f>
+        <v>14.166666666666666</v>
+      </c>
+      <c r="U14">
+        <f>MIN(Q14:S14)</f>
+        <v>10</v>
+      </c>
+      <c r="V14">
+        <f>T14-U14</f>
+        <v>4.1666666666666661</v>
       </c>
     </row>
   </sheetData>
@@ -14665,7 +16005,7 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EEC9CF4A-6F3D-4BA0-B506-17E3C93FB04B}">
-  <dimension ref="A2:AF9"/>
+  <dimension ref="A2:AF14"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="2" spans="1:32" x14ac:dyDescent="0.3">
@@ -15144,6 +16484,237 @@
         <v>5</v>
       </c>
     </row>
+    <row r="11" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="12" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B12">
+        <v>90</v>
+      </c>
+      <c r="C12">
+        <v>10</v>
+      </c>
+      <c r="D12">
+        <v>8</v>
+      </c>
+      <c r="E12">
+        <v>92</v>
+      </c>
+      <c r="G12">
+        <v>95</v>
+      </c>
+      <c r="H12">
+        <v>5</v>
+      </c>
+      <c r="I12">
+        <v>22</v>
+      </c>
+      <c r="J12">
+        <v>78</v>
+      </c>
+      <c r="L12">
+        <v>79</v>
+      </c>
+      <c r="M12">
+        <v>21</v>
+      </c>
+      <c r="N12">
+        <v>27</v>
+      </c>
+      <c r="O12">
+        <v>73</v>
+      </c>
+      <c r="Q12">
+        <f t="shared" ref="Q10:Q14" si="6">AVERAGE(C12:D12)</f>
+        <v>9</v>
+      </c>
+      <c r="R12">
+        <f t="shared" ref="R10:R14" si="7">AVERAGE(H12:I12)</f>
+        <v>13.5</v>
+      </c>
+      <c r="S12">
+        <f t="shared" ref="S10:S14" si="8">AVERAGE(M12:N12)</f>
+        <v>24</v>
+      </c>
+      <c r="T12">
+        <f t="shared" ref="T10:T14" si="9">AVERAGE(Q12:S12)</f>
+        <v>15.5</v>
+      </c>
+      <c r="U12">
+        <f t="shared" ref="U10:U14" si="10">MIN(Q12:S12)</f>
+        <v>9</v>
+      </c>
+      <c r="V12">
+        <f t="shared" ref="V10:V14" si="11">T12-U12</f>
+        <v>6.5</v>
+      </c>
+      <c r="W12">
+        <f>AVERAGE(Q12:Q18)</f>
+        <v>14.5</v>
+      </c>
+      <c r="X12">
+        <f>_xlfn.STDEV.S(Q12:Q18)</f>
+        <v>4.7696960070847281</v>
+      </c>
+      <c r="Y12">
+        <f>AVERAGE(R12:R18)</f>
+        <v>16.5</v>
+      </c>
+      <c r="Z12">
+        <f>_xlfn.STDEV.S(R12:R18)</f>
+        <v>5.196152422706632</v>
+      </c>
+      <c r="AA12">
+        <f>AVERAGE(S12:S18)</f>
+        <v>25.333333333333332</v>
+      </c>
+      <c r="AB12">
+        <f>_xlfn.STDEV.S(S12:S18)</f>
+        <v>1.5275252316519465</v>
+      </c>
+      <c r="AC12">
+        <f>AVERAGE(T12:T18)</f>
+        <v>18.777777777777775</v>
+      </c>
+      <c r="AD12">
+        <f>_xlfn.STDEV.S(T12:T18)</f>
+        <v>3.4251250315107677</v>
+      </c>
+      <c r="AE12">
+        <f>AVERAGE(V12:V18)</f>
+        <v>5.4444444444444438</v>
+      </c>
+      <c r="AF12">
+        <f>_xlfn.STDEV.S(V12:V18)</f>
+        <v>0.91792842454768508</v>
+      </c>
+    </row>
+    <row r="13" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B13">
+        <v>84</v>
+      </c>
+      <c r="C13">
+        <v>16</v>
+      </c>
+      <c r="D13">
+        <v>18</v>
+      </c>
+      <c r="E13">
+        <v>82</v>
+      </c>
+      <c r="G13">
+        <v>94</v>
+      </c>
+      <c r="H13">
+        <v>6</v>
+      </c>
+      <c r="I13">
+        <v>21</v>
+      </c>
+      <c r="J13">
+        <v>79</v>
+      </c>
+      <c r="L13">
+        <v>83</v>
+      </c>
+      <c r="M13">
+        <v>17</v>
+      </c>
+      <c r="N13">
+        <v>33</v>
+      </c>
+      <c r="O13">
+        <v>67</v>
+      </c>
+      <c r="Q13">
+        <f t="shared" si="6"/>
+        <v>17</v>
+      </c>
+      <c r="R13">
+        <f t="shared" si="7"/>
+        <v>13.5</v>
+      </c>
+      <c r="S13">
+        <f t="shared" si="8"/>
+        <v>25</v>
+      </c>
+      <c r="T13">
+        <f t="shared" si="9"/>
+        <v>18.5</v>
+      </c>
+      <c r="U13">
+        <f t="shared" si="10"/>
+        <v>13.5</v>
+      </c>
+      <c r="V13">
+        <f t="shared" si="11"/>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B14">
+        <v>84</v>
+      </c>
+      <c r="C14">
+        <v>16</v>
+      </c>
+      <c r="D14">
+        <v>19</v>
+      </c>
+      <c r="E14">
+        <v>81</v>
+      </c>
+      <c r="G14">
+        <v>86</v>
+      </c>
+      <c r="H14">
+        <v>14</v>
+      </c>
+      <c r="I14">
+        <v>31</v>
+      </c>
+      <c r="J14">
+        <v>69</v>
+      </c>
+      <c r="L14">
+        <v>77</v>
+      </c>
+      <c r="M14">
+        <v>23</v>
+      </c>
+      <c r="N14">
+        <v>31</v>
+      </c>
+      <c r="O14">
+        <v>69</v>
+      </c>
+      <c r="Q14">
+        <f t="shared" si="6"/>
+        <v>17.5</v>
+      </c>
+      <c r="R14">
+        <f t="shared" si="7"/>
+        <v>22.5</v>
+      </c>
+      <c r="S14">
+        <f t="shared" si="8"/>
+        <v>27</v>
+      </c>
+      <c r="T14">
+        <f t="shared" si="9"/>
+        <v>22.333333333333332</v>
+      </c>
+      <c r="U14">
+        <f t="shared" si="10"/>
+        <v>17.5</v>
+      </c>
+      <c r="V14">
+        <f t="shared" si="11"/>
+        <v>4.8333333333333321</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/DataAnalysis/LC/0.05/Results.xlsx
+++ b/DataAnalysis/LC/0.05/Results.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Utente\Desktop\CultureAwarenessTest\DataAnalysis\LC\0.05\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AFAE925B-A7D7-47D6-8A9F-E66DAB51D19C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{464AABD0-BBCD-42C3-B3FB-D182EE653F1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -697,7 +697,7 @@
         <v>3.1224989991991992</v>
       </c>
       <c r="X3">
-        <v>21.277777777777775</v>
+        <v>21.2777777777778</v>
       </c>
       <c r="Y3">
         <v>1.9743728493240953</v>
@@ -822,10 +822,10 @@
         <v>4.5772687149531643</v>
       </c>
       <c r="O7">
-        <v>2.7777777777777777</v>
+        <v>8.3333333333333321</v>
       </c>
       <c r="P7">
-        <v>0.93623886368626152</v>
+        <v>2.8087165910587908</v>
       </c>
     </row>
     <row r="8" spans="1:27" x14ac:dyDescent="0.3">
@@ -865,10 +865,10 @@
         <v>3.476108935769068</v>
       </c>
       <c r="O9">
-        <v>2.2916666666666665</v>
+        <v>6.875</v>
       </c>
       <c r="P9">
-        <v>0.36111111111111049</v>
+        <v>1.0833333333333304</v>
       </c>
     </row>
     <row r="10" spans="1:27" x14ac:dyDescent="0.3">
@@ -7660,8 +7660,8 @@
         <v>11</v>
       </c>
       <c r="V3">
-        <f>(1/3)*(T3-U3)</f>
-        <v>2.833333333333333</v>
+        <f>(T3-U3)</f>
+        <v>8.5</v>
       </c>
       <c r="W3">
         <f>AVERAGE(Q3:Q4)</f>
@@ -7697,11 +7697,11 @@
       </c>
       <c r="AE3">
         <f>AVERAGE(V3:V4)</f>
-        <v>3.0555555555555554</v>
+        <v>9.1666666666666661</v>
       </c>
       <c r="AF3">
         <f>_xlfn.STDEV.S(V3:V4)</f>
-        <v>0.31426968052735427</v>
+        <v>0.94280904158206247</v>
       </c>
       <c r="AH3" t="s">
         <v>46</v>
@@ -7768,8 +7768,8 @@
         <v>11.5</v>
       </c>
       <c r="V4">
-        <f t="shared" ref="V4" si="5">(1/3)*(T4-U4)</f>
-        <v>3.2777777777777772</v>
+        <f t="shared" ref="V4:V14" si="5">(T4-U4)</f>
+        <v>9.8333333333333321</v>
       </c>
       <c r="AH4" t="s">
         <v>48</v>
@@ -7794,6 +7794,10 @@
       <c r="A5" t="s">
         <v>73</v>
       </c>
+      <c r="V5">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="6" spans="1:44" x14ac:dyDescent="0.3">
       <c r="B6">
@@ -7853,8 +7857,8 @@
         <v>13.5</v>
       </c>
       <c r="V6">
-        <f t="shared" ref="V6:V14" si="11">(1/3)*(T6-U6)</f>
-        <v>2.9444444444444438</v>
+        <f t="shared" si="5"/>
+        <v>8.8333333333333321</v>
       </c>
       <c r="W6">
         <f>AVERAGE(Q6:Q9)</f>
@@ -7890,11 +7894,11 @@
       </c>
       <c r="AE6">
         <f>AVERAGE(V6:V9)</f>
-        <v>3.3888888888888884</v>
+        <v>10.166666666666666</v>
       </c>
       <c r="AF6">
         <f>_xlfn.STDEV.S(V6:V9)</f>
-        <v>0.57197945227705749</v>
+        <v>1.7159383568311648</v>
       </c>
       <c r="AI6" t="s">
         <v>6</v>
@@ -7985,8 +7989,8 @@
         <v>12</v>
       </c>
       <c r="V7">
-        <f t="shared" si="11"/>
-        <v>3.1111111111111107</v>
+        <f t="shared" si="5"/>
+        <v>9.3333333333333321</v>
       </c>
       <c r="AH7" t="s">
         <v>48</v>
@@ -8086,8 +8090,8 @@
         <v>13.5</v>
       </c>
       <c r="V8">
-        <f t="shared" si="11"/>
-        <v>3.2777777777777772</v>
+        <f t="shared" si="5"/>
+        <v>9.8333333333333321</v>
       </c>
     </row>
     <row r="9" spans="1:44" x14ac:dyDescent="0.3">
@@ -8148,14 +8152,18 @@
         <v>12</v>
       </c>
       <c r="V9">
-        <f t="shared" si="11"/>
-        <v>4.2222222222222223</v>
+        <f t="shared" si="5"/>
+        <v>12.666666666666668</v>
       </c>
     </row>
     <row r="10" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>74</v>
       </c>
+      <c r="V10">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="11" spans="1:44" x14ac:dyDescent="0.3">
       <c r="B11">
@@ -8215,8 +8223,8 @@
         <v>12</v>
       </c>
       <c r="V11">
-        <f t="shared" si="11"/>
-        <v>2.7777777777777772</v>
+        <f t="shared" si="5"/>
+        <v>8.3333333333333321</v>
       </c>
       <c r="W11">
         <f>AVERAGE(Q11:Q14)</f>
@@ -8252,11 +8260,11 @@
       </c>
       <c r="AE11">
         <f>AVERAGE(V11:V14)</f>
-        <v>2.2916666666666665</v>
+        <v>6.875</v>
       </c>
       <c r="AF11">
         <f>_xlfn.STDEV.S(V11:V14)</f>
-        <v>0.36111111111111049</v>
+        <v>1.0833333333333304</v>
       </c>
     </row>
     <row r="12" spans="1:44" x14ac:dyDescent="0.3">
@@ -8317,8 +8325,8 @@
         <v>18.5</v>
       </c>
       <c r="V12">
-        <f t="shared" si="11"/>
-        <v>1.944444444444444</v>
+        <f t="shared" si="5"/>
+        <v>5.8333333333333321</v>
       </c>
     </row>
     <row r="13" spans="1:44" x14ac:dyDescent="0.3">
@@ -8379,8 +8387,8 @@
         <v>13.5</v>
       </c>
       <c r="V13">
-        <f t="shared" si="11"/>
-        <v>2.333333333333333</v>
+        <f t="shared" si="5"/>
+        <v>7</v>
       </c>
     </row>
     <row r="14" spans="1:44" x14ac:dyDescent="0.3">
@@ -8441,8 +8449,8 @@
         <v>9.5</v>
       </c>
       <c r="V14">
-        <f t="shared" si="11"/>
-        <v>2.1111111111111112</v>
+        <f t="shared" si="5"/>
+        <v>6.3333333333333339</v>
       </c>
     </row>
   </sheetData>
@@ -8599,8 +8607,8 @@
         <v>14</v>
       </c>
       <c r="V3">
-        <f>(1/3)*(T3-U3)</f>
-        <v>2.333333333333333</v>
+        <f>(T3-U3)</f>
+        <v>7</v>
       </c>
       <c r="W3">
         <f>AVERAGE(Q3:Q4)</f>
@@ -8636,11 +8644,11 @@
       </c>
       <c r="AE3">
         <f>AVERAGE(V3:V4)</f>
-        <v>2.5277777777777777</v>
+        <v>7.5833333333333339</v>
       </c>
       <c r="AF3">
         <f>_xlfn.STDEV.S(V3:V4)</f>
-        <v>0.27498597046143541</v>
+        <v>0.8249579113843063</v>
       </c>
       <c r="AH3" t="s">
         <v>46</v>
@@ -8707,8 +8715,8 @@
         <v>14</v>
       </c>
       <c r="V4">
-        <f t="shared" ref="V4" si="5">(1/3)*(T4-U4)</f>
-        <v>2.7222222222222223</v>
+        <f t="shared" ref="V4:V14" si="5">(T4-U4)</f>
+        <v>8.1666666666666679</v>
       </c>
       <c r="AH4" t="s">
         <v>48</v>
@@ -8733,6 +8741,10 @@
       <c r="A5" t="s">
         <v>73</v>
       </c>
+      <c r="V5">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="6" spans="1:44" x14ac:dyDescent="0.3">
       <c r="B6">
@@ -8792,8 +8804,8 @@
         <v>16.5</v>
       </c>
       <c r="V6">
-        <f t="shared" ref="V6:V14" si="11">(1/3)*(T6-U6)</f>
-        <v>1.5555555555555558</v>
+        <f t="shared" si="5"/>
+        <v>4.6666666666666679</v>
       </c>
       <c r="W6">
         <f>AVERAGE(Q6:Q9)</f>
@@ -8829,11 +8841,11 @@
       </c>
       <c r="AE6">
         <f>AVERAGE(V6:V9)</f>
-        <v>2.2777777777777772</v>
+        <v>6.833333333333333</v>
       </c>
       <c r="AF6">
         <f>_xlfn.STDEV.S(V6:V9)</f>
-        <v>1.0071758993249744</v>
+        <v>3.0215276979749199</v>
       </c>
       <c r="AI6" t="s">
         <v>6</v>
@@ -8924,8 +8936,8 @@
         <v>11.5</v>
       </c>
       <c r="V7">
-        <f t="shared" si="11"/>
-        <v>3</v>
+        <f t="shared" si="5"/>
+        <v>9</v>
       </c>
       <c r="AH7" t="s">
         <v>48</v>
@@ -9025,8 +9037,8 @@
         <v>11</v>
       </c>
       <c r="V8">
-        <f t="shared" si="11"/>
-        <v>3.2777777777777772</v>
+        <f t="shared" si="5"/>
+        <v>9.8333333333333321</v>
       </c>
     </row>
     <row r="9" spans="1:44" x14ac:dyDescent="0.3">
@@ -9087,14 +9099,18 @@
         <v>17</v>
       </c>
       <c r="V9">
-        <f t="shared" si="11"/>
-        <v>1.2777777777777772</v>
+        <f t="shared" si="5"/>
+        <v>3.8333333333333321</v>
       </c>
     </row>
     <row r="10" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>74</v>
       </c>
+      <c r="V10">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="11" spans="1:44" x14ac:dyDescent="0.3">
       <c r="B11">
@@ -9154,8 +9170,8 @@
         <v>11</v>
       </c>
       <c r="V11">
-        <f t="shared" si="11"/>
-        <v>1.3888888888888886</v>
+        <f t="shared" si="5"/>
+        <v>4.1666666666666661</v>
       </c>
       <c r="W11">
         <f>AVERAGE(Q11:Q14)</f>
@@ -9191,11 +9207,11 @@
       </c>
       <c r="AE11">
         <f>AVERAGE(V11:V14)</f>
-        <v>2.7777777777777777</v>
+        <v>8.3333333333333321</v>
       </c>
       <c r="AF11">
         <f>_xlfn.STDEV.S(V11:V14)</f>
-        <v>0.93623886368626152</v>
+        <v>2.8087165910587908</v>
       </c>
     </row>
     <row r="12" spans="1:44" x14ac:dyDescent="0.3">
@@ -9256,8 +9272,8 @@
         <v>11</v>
       </c>
       <c r="V12">
-        <f t="shared" si="11"/>
-        <v>3.3888888888888893</v>
+        <f t="shared" si="5"/>
+        <v>10.166666666666668</v>
       </c>
     </row>
     <row r="13" spans="1:44" x14ac:dyDescent="0.3">
@@ -9318,8 +9334,8 @@
         <v>11</v>
       </c>
       <c r="V13">
-        <f t="shared" si="11"/>
-        <v>3.0555555555555558</v>
+        <f t="shared" si="5"/>
+        <v>9.1666666666666679</v>
       </c>
     </row>
     <row r="14" spans="1:44" x14ac:dyDescent="0.3">
@@ -9380,8 +9396,8 @@
         <v>16.5</v>
       </c>
       <c r="V14">
-        <f t="shared" si="11"/>
-        <v>3.2777777777777772</v>
+        <f t="shared" si="5"/>
+        <v>9.8333333333333321</v>
       </c>
     </row>
   </sheetData>
